--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_ma_ratio_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_ma_ratio_20.xlsx
@@ -625,76 +625,76 @@
         <v>30</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>22.83024831138812</v>
+        <v>22.86348556579184</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>25.8164190198362</v>
+        <v>25.85007576636974</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21.08071654498433</v>
+        <v>21.11601002866063</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.43837881566154</v>
+        <v>10.47443064404516</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.763904928086227</v>
+        <v>6.829245504405158</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.26842499586157</v>
+        <v>10.33360637204208</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.13531053299571</v>
+        <v>16.2014568553892</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.911432570464974</v>
+        <v>5.97787469904938</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.6819226020977709</v>
+        <v>-0.6155270502935011</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.505228423294064</v>
+        <v>8.57260708589213</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.781453395151871</v>
+        <v>8.848551774539821</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.184810953955662</v>
+        <v>5.252254214443496</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.71017453236225</v>
+        <v>10.77898353223652</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.49285348397127</v>
+        <v>10.56195582656427</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>9.83894460326227</v>
+        <v>9.908847950983166</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>10.43536607368527</v>
+        <v>10.50461817296433</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>10.30468635433071</v>
+        <v>10.37413198715467</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>6.875712290063845</v>
+        <v>6.945310616785918</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>7.093763935922176</v>
+        <v>7.163149873503521</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.28270831610493</v>
+        <v>7.351915754133671</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>13.40294839632777</v>
+        <v>13.47283467867305</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>9.999747691773926</v>
+        <v>10.06975736185397</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>6.945142648232384</v>
+        <v>7.014868904844576</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.871345029240523</v>
+        <v>6.9411993769478</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>53</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.77779672513936</v>
+        <v>4.810882065525426</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.6990255992173431</v>
+        <v>0.7324796429884586</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.017866997404504</v>
+        <v>3.053020571997116</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.4353883334468023</v>
+        <v>0.4713633554771661</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.948242602208239</v>
+        <v>2.01354160960053</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.51789936112995</v>
+        <v>11.58308355334928</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.75251776096592</v>
+        <v>10.81862602692944</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>16.11201542160295</v>
+        <v>16.17851249930507</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>16.15862336284665</v>
+        <v>16.22510611609191</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19.15024260112784</v>
+        <v>19.21767228952881</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>21.30905143163618</v>
+        <v>21.37620649841744</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>19.157870216086</v>
+        <v>19.22537151371664</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>18.04292019758126</v>
+        <v>18.11175588734195</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>23.47096084041504</v>
+        <v>23.54010868019441</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>22.82116336642729</v>
+        <v>22.89110751610563</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>23.42160547445793</v>
+        <v>23.49089401329753</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>19.52952902316821</v>
+        <v>19.59899658413684</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>21.3141306777292</v>
+        <v>21.38375923289308</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>23.42056190616807</v>
+        <v>23.48997662692569</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>25.49904616515025</v>
+        <v>25.5682795175864</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>23.07923700978586</v>
+        <v>23.14913336761378</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>24.89608252044898</v>
+        <v>24.96610273136229</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>23.29225771223513</v>
+        <v>23.36198973631896</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>23.22354628710097</v>
+        <v>23.29340063480824</v>
       </c>
     </row>
     <row r="8">
@@ -789,76 +789,76 @@
         <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17.62282246203918</v>
+        <v>17.65601742625912</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14.45904788357547</v>
+        <v>14.4926125544188</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>21.54843202558015</v>
+        <v>21.58373046883111</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20.84729997059191</v>
+        <v>20.88342614842495</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>17.65017620231852</v>
+        <v>17.71558022812474</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.84186818593497</v>
+        <v>17.9070904846097</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22.76286754935514</v>
+        <v>22.82904861734233</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>16.80715735528089</v>
+        <v>16.87365496094714</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>19.69798962910501</v>
+        <v>19.76448929008167</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>13.24376243962154</v>
+        <v>13.31115777145128</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>19.21275121679477</v>
+        <v>19.27989403136818</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.78761024874206</v>
+        <v>21.855121498595</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.5211335662018</v>
+        <v>23.58999009366023</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>17.61119184732913</v>
+        <v>17.6803160108511</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>11.26149667449375</v>
+        <v>11.33139953424377</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>17.55859559200965</v>
+        <v>17.62786516448435</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>17.43050916431001</v>
+        <v>17.49996972092175</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>20.18307756730883</v>
+        <v>20.25270257234175</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>23.25809671754656</v>
+        <v>23.32751056448887</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>14.89143622443473</v>
+        <v>14.9606529229093</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>20.06259809342132</v>
+        <v>20.13249058312544</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>19.99305092114765</v>
+        <v>20.06306716947446</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>20.27413088739062</v>
+        <v>20.34386162868395</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>23.0618212197166</v>
+        <v>23.13167556742258</v>
       </c>
     </row>
     <row r="9">
@@ -871,322 +871,322 @@
         <v>53</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.591176590335557</v>
+        <v>-4.558182019868255</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.318762964585723</v>
+        <v>6.352257138294021</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.7334635465660497</v>
+        <v>-0.6983474159428056</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.0584682364616</v>
+        <v>6.094479676040358</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.697465587874483</v>
+        <v>5.762775680494094</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.885523000242344</v>
+        <v>5.950656365392305</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.11847627577815</v>
+        <v>5.184536539978126</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.089167818995172</v>
+        <v>1.155561825882842</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.009066729273059</v>
+        <v>3.075464348332375</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.118084210555189</v>
+        <v>4.185424406515374</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.392771611843514</v>
+        <v>4.459835424275234</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.236877348000299</v>
+        <v>2.304293637022191</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.757774635699711</v>
+        <v>6.82655659472109</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.30120956194961</v>
+        <v>10.37030230508653</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>7.766487932919183</v>
+        <v>7.836374883899147</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>6.480254310997829</v>
+        <v>6.549486703833693</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>10.11408460834656</v>
+        <v>10.18352308781797</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>15.66227783700403</v>
+        <v>15.73189096022992</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>13.99947448594477</v>
+        <v>14.0688693065349</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>14.1909772879178</v>
+        <v>14.26019172108164</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>15.53805574325308</v>
+        <v>15.60794226018573</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>11.69605756389445</v>
+        <v>11.76606681289507</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>10.08849328144074</v>
+        <v>10.15821977625497</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.468829305968903</v>
+        <v>2.538683653677033</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.09153</t>
+          <t>X ≈ -0.09152</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>83</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.903151105072382</v>
+        <v>8.936261824200386</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.592366673569423</v>
+        <v>2.625821496037069</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.359713129966202</v>
+        <v>2.394846103038283</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.44054192911485</v>
+        <v>6.476551022240741</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>12.06698877324428</v>
+        <v>12.13233586657199</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.05932822984914</v>
+        <v>11.12448781597834</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10.29420888653598</v>
+        <v>10.36029330718241</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.22023618799849</v>
+        <v>11.28668372885245</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.867446033305768</v>
+        <v>8.933867966157564</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>9.299299596143747</v>
+        <v>9.366658903641763</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.375925563169076</v>
+        <v>8.443000780699798</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.700944496237703</v>
+        <v>5.768367684549844</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9.384198214354122</v>
+        <v>9.452984210292009</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>7.965813994916722</v>
+        <v>8.034890765728008</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.110805459455996</v>
+        <v>6.180679633383143</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>3.101090993975269</v>
+        <v>3.170306006048257</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.170639394298142</v>
+        <v>4.240055981415232</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>6.47217348487419</v>
+        <v>6.541760830427464</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.28473807519169</v>
+        <v>4.354110017765365</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>8.083052328581559</v>
+        <v>8.15225456292859</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>8.746993098794526</v>
+        <v>8.816869709435871</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>7.470220641638001</v>
+        <v>7.540225173862957</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>7.747660237527747</v>
+        <v>7.817385115391033</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>7.674557880645118</v>
+        <v>7.744412228352665</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07948</t>
+          <t>X ≈ -0.07947</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>99</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.86982796235354</v>
+        <v>6.902913849490787</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.55741740063763</v>
+        <v>12.59095898842502</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>13.1378957482011</v>
+        <v>13.17311831483529</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>12.43368435638656</v>
+        <v>12.46973970118717</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.063147933992553</v>
+        <v>9.128456223305008</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8.24864081286826</v>
+        <v>8.313764330058675</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.4917928468304</v>
+        <v>9.557857542143999</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>9.219154960770211</v>
+        <v>9.285575770374592</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.238992765733364</v>
+        <v>4.30537015263134</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.470169150150895</v>
+        <v>3.537479439729978</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.756286748881152</v>
+        <v>5.823334609712226</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.505431393644699</v>
+        <v>9.57286204056615</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.355783633548356</v>
+        <v>3.424529863689528</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8902410356490549</v>
+        <v>-0.8212138803132163</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.474684946705757</v>
+        <v>1.544530368648118</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.9534013315357299</v>
+        <v>-0.8842108522945082</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.095010424569139</v>
+        <v>-2.02562188949981</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.200560733819209</v>
+        <v>-2.131003160043939</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.993339251292248</v>
+        <v>-2.923989559136665</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.798523874784749</v>
+        <v>-1.729343324247367</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.341362318699424</v>
+        <v>-2.271503546359732</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.408175862223338</v>
+        <v>-1.33818137793746</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.895733282968621</v>
+        <v>1.965454516850031</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.820839978734945</v>
+        <v>1.890694326441988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06742</t>
+          <t>X ≈ -0.06741</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>129</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.494070785675092</v>
+        <v>7.52715565446389</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.318414252385139</v>
+        <v>3.351857351409279</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.046436505339059</v>
+        <v>8.081607546655775</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.341212297787024</v>
+        <v>7.377216992073535</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.06136558059318</v>
+        <v>10.12666146914046</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.629666694429311</v>
+        <v>5.694745645404076</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.322154863161899</v>
+        <v>3.388149099839026</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.8064956693505394</v>
+        <v>-0.7401721307728337</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.863010619040075</v>
+        <v>3.929362043775114</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.865859151760169</v>
+        <v>3.933149428594731</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.282044212425042</v>
+        <v>0.3490384040155234</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.004843822282225574</v>
+        <v>0.07220420524301119</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3428044299566935</v>
+        <v>-0.2740964800065697</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2098922652580626</v>
+        <v>0.2789049356113509</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.991581821872217</v>
+        <v>-1.921768440826199</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.9205824507948037</v>
+        <v>0.9897641769214971</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.107345201888407</v>
+        <v>3.176736915051634</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.550701669651616</v>
+        <v>4.620266592459174</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.994879461383441</v>
+        <v>4.06423554428077</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.86095000723995</v>
+        <v>1.930129542126323</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.868180491850829</v>
+        <v>2.938040608103464</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.79372420585895</v>
+        <v>2.863718716519941</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.51992976240809</v>
+        <v>1.589649010157729</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.444988440092473</v>
+        <v>1.514842787799751</v>
       </c>
     </row>
     <row r="13">
@@ -1199,76 +1199,76 @@
         <v>154</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5.999203161174748</v>
+        <v>6.032260730033279</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.315382530259818</v>
+        <v>6.348843314696438</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.954371231723485</v>
+        <v>2.989475765051907</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.248165062324119</v>
+        <v>2.284104081342093</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.04865243693696897</v>
+        <v>0.016511307577602</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1396065122730903</v>
+        <v>0.2045972666622546</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6629492919170374</v>
+        <v>0.7288819190401483</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.262238062580153</v>
+        <v>4.328563518611318</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7.534556142450953</v>
+        <v>7.600904763563875</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.767725994709345</v>
+        <v>6.835007331937263</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.751741063874476</v>
+        <v>5.818740596557703</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.183812039989505</v>
+        <v>4.251168270433304</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>6.946108119475163</v>
+        <v>7.014830017409984</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.082099115720531</v>
+        <v>6.151116966286196</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>4.134465520532963</v>
+        <v>4.204282236866227</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>6.024166134552964</v>
+        <v>6.093349007774492</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3.949756458341966</v>
+        <v>4.019134401028907</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>3.846265386218072</v>
+        <v>3.91581449004849</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.416132921970551</v>
+        <v>3.485475807116089</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>5.549774153926052</v>
+        <v>5.618951698267438</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>5.009711609961762</v>
+        <v>5.079567913267944</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.585075573628608</v>
+        <v>5.655068224613167</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.862319618468582</v>
+        <v>5.932038681348246</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.43844459633933</v>
+        <v>6.508298944046608</v>
       </c>
     </row>
     <row r="14">
@@ -1281,158 +1281,158 @@
         <v>221</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.322477483947864</v>
+        <v>7.355538443634771</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.856344273631173</v>
+        <v>3.889754012704827</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.430027466590509</v>
+        <v>2.465096656143338</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.071336063501512</v>
+        <v>3.107254931549832</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.506707352997203</v>
+        <v>4.571854061583771</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.69695817379467</v>
+        <v>4.761932514711049</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.033109134708553</v>
+        <v>3.099002590096894</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.557850874486199</v>
+        <v>4.624126001638842</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.70116518351724</v>
+        <v>3.767434831138473</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.033963231095775</v>
+        <v>2.101160126224549</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.109748345820485</v>
+        <v>4.176693188502988</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.934470923826204</v>
+        <v>3.001776000497969</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.419886798094105</v>
+        <v>5.488564122793967</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.851008599276987</v>
+        <v>3.919979356446106</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.90307759700395</v>
+        <v>5.972871244399876</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.047329407223977</v>
+        <v>6.116485891810711</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.111805594388649</v>
+        <v>4.181158661334706</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.75163341255611</v>
+        <v>1.82115264834588</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.420742222802808</v>
+        <v>2.49006327075633</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.3500603747531486</v>
+        <v>0.4192110600546002</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.2603152189530817</v>
+        <v>0.3301518560337868</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.6373567714220485</v>
+        <v>0.707336222192545</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.008364590921146942</v>
+        <v>0.07807654105013739</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.424280913444996</v>
+        <v>-1.354426565737718</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03125</t>
+          <t>X ≈ -0.03124</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>267</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.783346108860954</v>
+        <v>5.81636714683156</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.60649028343223</v>
+        <v>3.639858994201134</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.811988226733916</v>
+        <v>1.847000200752497</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.006288315628381724</v>
+        <v>0.0295370935262369</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.225535009849295</v>
+        <v>-2.160587002442085</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-5.381161458672345</v>
+        <v>-5.316424885653305</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.431705262877891</v>
+        <v>-2.365982936821872</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8486284182210326</v>
+        <v>-0.7825082265055059</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.667411001842389</v>
+        <v>-2.601301262096939</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.946965463466071</v>
+        <v>-1.879899125256962</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5598302900244505</v>
+        <v>0.6266661431182925</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.08753486291739421</v>
+        <v>-0.02033081618110089</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.207645515293208</v>
+        <v>-1.139085685616301</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.053134701770055</v>
+        <v>-0.9842625912818903</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.2160083620470274</v>
+        <v>-0.1463090804491998</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.608730532694793</v>
+        <v>-2.539672788483543</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.8753082905123932</v>
+        <v>-0.8060249666271986</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.35333865318821</v>
+        <v>-1.28387362565303</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.631732168733478</v>
+        <v>-2.562463576695173</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.323741413160143</v>
+        <v>-1.254623827757641</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3698103916426163</v>
+        <v>-0.2999963390444407</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.07082811110986853</v>
+        <v>-0.0008636376913742083</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1696681584376662</v>
+        <v>-0.09996339538004406</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.368355345291981</v>
+        <v>-1.298500997584796</v>
       </c>
     </row>
     <row r="16">
@@ -1445,76 +1445,76 @@
         <v>304</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.72443463023658</v>
+        <v>-1.691294476634155</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.07710663748508</v>
+        <v>-1.043560658554782</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.7468771417231679</v>
+        <v>0.782149564359635</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3638743453043247</v>
+        <v>0.3999885520104343</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.305438667858589</v>
+        <v>1.370965846095764</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4616266471068613</v>
+        <v>-0.3962964446374002</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5801273254454884</v>
+        <v>-0.5138309296414221</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1220138015538055</v>
+        <v>0.1887148180331906</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1649102829288793</v>
+        <v>0.2316298396560796</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.334158210769189</v>
+        <v>2.40187427554104</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.789126616088467</v>
+        <v>2.678899862505389</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.021468155794047</v>
+        <v>2.72930697098068</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.250171460243912</v>
+        <v>0.9525019915974582</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.05210367922256864</v>
+        <v>-0.2507674402205211</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.7077099484847977</v>
+        <v>0.5891763395709688</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.301719162573178</v>
+        <v>1.370710380846667</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.48082102095713</v>
+        <v>2.550047076371015</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.72251894938146</v>
+        <v>1.791931850575246</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.925277540254505</v>
+        <v>2.994512510964199</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.4966870693572289</v>
+        <v>-0.4276143256676619</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.9321881941484804</v>
+        <v>1.001971280914539</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.172245019959831</v>
+        <v>2.242191249477479</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>2.449192415246877</v>
+        <v>2.518888480733594</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>5.007309941520383</v>
+        <v>5.077164289227746</v>
       </c>
     </row>
     <row r="17">
@@ -1527,76 +1527,76 @@
         <v>291</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.589211235479397</v>
+        <v>2.622076141362442</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.328317686441316</v>
+        <v>5.361625454525409</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.910224669866821</v>
+        <v>3.945159292758078</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.87367000812943</v>
+        <v>2.909400489346886</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.55560499122852</v>
+        <v>4.620338651488296</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.096427852618092</v>
+        <v>5.160987376475923</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.992771471328602</v>
+        <v>4.058274017431089</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.67443525055252</v>
+        <v>1.740294751963766</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.082994775830386</v>
+        <v>3.148911083288709</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.680870125174032</v>
+        <v>3.747774368786644</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.143425782465151</v>
+        <v>-0.07453847844336536</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.6058055819737049</v>
+        <v>0.677770779529439</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5144677875682291</v>
+        <v>0.5878036001541247</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.04110270142570727</v>
+        <v>0.03111022718960044</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.722856699540174</v>
+        <v>2.795815548609355</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>4.343563321122083</v>
+        <v>4.412457730734587</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.239959400468294</v>
+        <v>5.309104630186027</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.455761746449198</v>
+        <v>4.525101338270602</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.991179724657755</v>
+        <v>4.060344358549628</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>5.21118554375353</v>
+        <v>5.280219239882129</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.271947832251847</v>
+        <v>2.341685120592608</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.4826709168734737</v>
+        <v>0.5525796480930794</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.644635607595916</v>
+        <v>-1.574961646349415</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.06336287454031</v>
+        <v>-1.99350852683299</v>
       </c>
     </row>
     <row r="18">
@@ -1606,79 +1606,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.446769467907551</v>
+        <v>-2.427826561424396</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.133208971865365</v>
+        <v>-3.108633635155435</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-7.004413536260515</v>
+        <v>-6.961093621851511</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.555244394361701</v>
+        <v>-7.685667437421579</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.469451927598179</v>
+        <v>-4.581882558363205</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.290561454840912</v>
+        <v>-4.403168933758984</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.084583407943008</v>
+        <v>-1.391500170598214</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.017786689556779</v>
+        <v>-1.144527911282701</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.319242192821513</v>
+        <v>-1.444873701483615</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.054832647565028</v>
+        <v>-1.183169128665384</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.472191418509219</v>
+        <v>-1.413615200781251</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.102462721759167</v>
+        <v>-2.039030023815158</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.082259620101524</v>
+        <v>-4.203843122314474</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.112839500811951</v>
+        <v>-4.43190597675266</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-4.229613776811583</v>
+        <v>-4.745352392005138</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-4.330087673856418</v>
+        <v>-4.835871574702153</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.771021217530418</v>
+        <v>-4.085279523965802</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.91684790143487</v>
+        <v>-5.036948719733267</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-6.785622202580242</v>
+        <v>-6.704399866469977</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-6.253164186619209</v>
+        <v>-6.173341855242676</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-5.558243590961432</v>
+        <v>-5.676939685689597</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-5.635662496641181</v>
+        <v>-5.754283600160512</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.969728025306409</v>
+        <v>-4.093516681275787</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-3.349328606068013</v>
+        <v>-3.475467289719667</v>
       </c>
     </row>
     <row r="19">
@@ -1688,79 +1688,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.247441001814593</v>
+        <v>-4.240911096630875</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.894489603040377</v>
+        <v>-2.893461510332031</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.82077508786255</v>
+        <v>-1.818059775306807</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.860960037541162</v>
+        <v>-3.824423407107091</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-6.558354141413353</v>
+        <v>-6.695232941376098</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.596882931916383</v>
+        <v>-3.977896106924796</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.227115835130284</v>
+        <v>-5.601534854648676</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.856099895814182</v>
+        <v>-5.46058368457075</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.813680259761867</v>
+        <v>-5.1924725814537</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.308323308953668</v>
+        <v>-7.443788032793229</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.033964041838331</v>
+        <v>-7.169728390631306</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.894754990139184</v>
+        <v>-6.800899572591291</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-8.897453232870056</v>
+        <v>-8.785182832283091</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-8.705580395303002</v>
+        <v>-8.591779228616367</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-9.796005186603153</v>
+        <v>-9.676973607633876</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-12.38294724661277</v>
+        <v>-12.48553702500906</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-12.27559163172202</v>
+        <v>-12.61641518826899</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-12.82085138345148</v>
+        <v>-13.15047766903967</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-13.04684912633962</v>
+        <v>-13.36380806506497</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-11.14593918484961</v>
+        <v>-11.23289217630825</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-10.83191336296656</v>
+        <v>-10.68237343315442</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-10.48426244428337</v>
+        <v>-10.33842167515212</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-10.39435366302077</v>
+        <v>-10.49765626868972</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-9.364287154668325</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="20">
@@ -1770,79 +1770,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.784244592876377</v>
+        <v>-4.773645905664274</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.553508722082178</v>
+        <v>-5.529288884894633</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.988800119430415</v>
+        <v>-6.940599869114628</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-9.899293578872125</v>
+        <v>-9.816609018347826</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-13.78471608165862</v>
+        <v>-13.6591670365792</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-14.47635224901268</v>
+        <v>-14.35148245139973</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-13.92914602167311</v>
+        <v>-13.82031535449626</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-14.64716141830278</v>
+        <v>-14.53444967760826</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-13.29629392414841</v>
+        <v>-13.17998715437908</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-14.52198299308929</v>
+        <v>-14.38778436752702</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-13.80666988388423</v>
+        <v>-13.67571916451108</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-15.40950438607261</v>
+        <v>-15.26327854428342</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.21298013042335</v>
+        <v>-15.07529158781592</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-12.78993249758548</v>
+        <v>-12.67154810488837</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-11.68531208999704</v>
+        <v>-11.57270507567981</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-10.64868284757495</v>
+        <v>-10.54150267001748</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-11.22311503310276</v>
+        <v>-11.11662695157771</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-9.132080364947072</v>
+        <v>-9.02390156415035</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-8.484562055317269</v>
+        <v>-8.366489348581538</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-9.189118883096981</v>
+        <v>-9.059234617223957</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.849383986805378</v>
+        <v>-8.722189706579542</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-9.551677588534325</v>
+        <v>-9.685386793203385</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-11.04681392647702</v>
+        <v>-11.18047139335379</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-9.352843761320607</v>
+        <v>-9.50520297253896</v>
       </c>
     </row>
     <row r="21">
@@ -1855,158 +1855,158 @@
         <v>171</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.106966576607682</v>
+        <v>-5.089322178311043</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.865219898007965</v>
+        <v>-4.842248839070876</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.743092683821608</v>
+        <v>-5.703599743729285</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-9.975912658743546</v>
+        <v>-9.906856198225782</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.103110172597106</v>
+        <v>-5.029029128216386</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.43148507657672</v>
+        <v>-1.364876412680715</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.950375299020962</v>
+        <v>-3.883983247871015</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.397723444134265</v>
+        <v>-5.330988192218832</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.865351485493647</v>
+        <v>-4.120707510709387</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3453717857162246</v>
+        <v>-0.2412122816672237</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.127628160356402</v>
+        <v>-1.713176729895494</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.400325475345134</v>
+        <v>-2.002886141228835</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.560063512807538</v>
+        <v>1.281533628550761</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.090002277106478</v>
+        <v>3.159280341939201</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3.012868048774315</v>
+        <v>3.082934055063781</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.857124568330583</v>
+        <v>1.926517446941659</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.720078602572677</v>
+        <v>1.789648038355203</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>3.369047928846335</v>
+        <v>3.433150638258269</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.591755382109298</v>
+        <v>3.652486336059717</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.61330409356728</v>
+        <v>2.673277898276751</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.315717719657016</v>
+        <v>0.3853406981953995</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.994148628926688</v>
+        <v>2.059491979760914</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.684128473771395</v>
+        <v>1.752621350478847</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.1461988304094248</v>
+        <v>-0.07634448270214733</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.05315</t>
+          <t>X ≈ 0.05314</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>134</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.977056741112037</v>
+        <v>-2.984323179879567</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.254952234162104</v>
+        <v>-6.229764766178782</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.188281780271105</v>
+        <v>-6.145513661138935</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.9363107802499187</v>
+        <v>-0.8985522770079228</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.178502612979166</v>
+        <v>0.2362878237577064</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.084425822150521</v>
+        <v>-4.013663987240626</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.598090736667785</v>
+        <v>-5.531698685517838</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6751528448729331</v>
+        <v>-0.6084175929575011</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6389371332071292</v>
+        <v>-0.5722307643996274</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.898156075586563</v>
+        <v>-2.830529972046122</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.831596593022077</v>
+        <v>1.898923071609104</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.531598879470835</v>
+        <v>4.599269858084767</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.415436787687433</v>
+        <v>3.484436917932392</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.940936305809828</v>
+        <v>4.010214370642551</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.053551172689168</v>
+        <v>1.123617178978634</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.9025120864903968</v>
+        <v>0.9719049651014728</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.205377444225221</v>
+        <v>-2.135808008442694</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.055392438127669</v>
+        <v>-2.982961881400556</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.1392667582371345</v>
+        <v>0.2074825294272955</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.311567164179152</v>
+        <v>3.362823822605101</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.514635411897572</v>
+        <v>3.567133983795998</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.199874386105705</v>
+        <v>1.265490882449903</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.01788776084500654</v>
+        <v>0.05294561023049482</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8400977568298842</v>
+        <v>-0.7702434091226067</v>
       </c>
     </row>
     <row r="23">
@@ -2019,76 +2019,76 @@
         <v>120</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-18.13120553993694</v>
+        <v>-18.02561884576468</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-13.52283485508404</v>
+        <v>-13.43627773548291</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-10.84467769575298</v>
+        <v>-10.75431879665329</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.451808841955256</v>
+        <v>-2.401769065785714</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.130057544674933</v>
+        <v>-6.046534767713872</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-7.609457032196097</v>
+        <v>-7.526722927822718</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.895574047642313</v>
+        <v>-5.829181996492366</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-8.662892738104745</v>
+        <v>-8.596157486189313</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-9.446263188612647</v>
+        <v>-9.379556819805146</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-11.05035825714206</v>
+        <v>-10.98273215360162</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-13.26207646385578</v>
+        <v>-13.19474998526875</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-15.20639118230137</v>
+        <v>-15.13872020368743</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-15.50868245637278</v>
+        <v>-15.43968232612782</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-14.90380946631923</v>
+        <v>-14.83453140148651</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-12.24506028821009</v>
+        <v>-12.17499428192063</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-15.79525374238037</v>
+        <v>-15.72586086376929</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-15.0984161359907</v>
+        <v>-15.02884670020818</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-13.57390628194646</v>
+        <v>-13.47518301684547</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-10.89183102966303</v>
+        <v>-10.77254251931338</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-11.04166666666671</v>
+        <v>-11.41192651043316</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-9.918200408997912</v>
+        <v>-10.29865486233011</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-6.660822131307278</v>
+        <v>-7.072489323242991</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.886046964825098</v>
+        <v>-4.320143310728092</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-3.128654970760238</v>
+        <v>-3.05880062305296</v>
       </c>
     </row>
     <row r="24">
@@ -2101,158 +2101,158 @@
         <v>69</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-11.60221499185429</v>
+        <v>-11.433750754971</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-7.617927237868336</v>
+        <v>-8.950347631716006</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-7.597600945478654</v>
+        <v>-9.04081059333852</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.799891241298774</v>
+        <v>1.019614966681083</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-8.661124956916055</v>
+        <v>-8.557663631339331</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-5.575288355495211</v>
+        <v>-5.490534303495089</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.789720938366393</v>
+        <v>-7.723328887216447</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.181556739147545</v>
+        <v>-5.114821487232113</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-10.91347836359955</v>
+        <v>-10.84677199479205</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-14.56805604726794</v>
+        <v>-14.5004299437275</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-15.73645854533742</v>
+        <v>-15.66913206675039</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-14.56083753995073</v>
+        <v>-14.49316656133679</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-9.907109811492404</v>
+        <v>-9.838109681247445</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-13.00681826669036</v>
+        <v>-12.93754020185764</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-10.78620254719647</v>
+        <v>-10.716136540907</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-5.865247830755969</v>
+        <v>-5.795854952144893</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-8.886060369642202</v>
+        <v>-8.816490933859676</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-9.022428611509589</v>
+        <v>-8.9225269520485</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-7.388130752142082</v>
+        <v>-7.265069120307096</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-7.20108695652165</v>
+        <v>-7.083004567809773</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-4.845736640882087</v>
+        <v>-4.73883189103848</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-4.921691696524498</v>
+        <v>-4.834541920280152</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-8.994742616999012</v>
+        <v>-8.924997355336927</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-9.07068395626748</v>
+        <v>-9.000829608560203</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.08932</t>
+          <t>X ≈ 0.08931</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>77</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-12.04568708628659</v>
+        <v>-11.98298959835715</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-7.238171494097273</v>
+        <v>-7.192649246090348</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-7.360892150215108</v>
+        <v>-7.290104139599535</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.766881334142475</v>
+        <v>-6.686459168024705</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.96675684646415</v>
+        <v>-1.889447165576776</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.400033875863372</v>
+        <v>3.464252852279067</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.338932389894076</v>
+        <v>1.405324441044023</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.932199724430617</v>
+        <v>4.99893497634605</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.680143496806046</v>
+        <v>3.746849865613548</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.203438337838463</v>
+        <v>4.271064441378904</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.682259729016593</v>
+        <v>-0.6149332504295657</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.636464830266888</v>
+        <v>1.704135808880821</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.102676156228725</v>
+        <v>3.171676286473684</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.601978889165721</v>
+        <v>1.671256953998444</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.804195752719657</v>
+        <v>4.874261759009123</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.054373824276567</v>
+        <v>-0.984980945665491</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-2.480260831495407</v>
+        <v>-2.410691395712881</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.610509560022358</v>
+        <v>-2.51731107911143</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.120485354061991</v>
+        <v>-1.013184344271757</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-2.123468786105576</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.775343266140851</v>
+        <v>-2.664235974494325</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-5.448700919186052</v>
+        <v>-5.351402813855351</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.277821856600028</v>
+        <v>-1.208076594937943</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-5.249867091972391</v>
+        <v>-5.180012744265113</v>
       </c>
     </row>
     <row r="26">
@@ -2265,76 +2265,76 @@
         <v>46</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.716653306560801</v>
+        <v>0.6969344908154156</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-6.16934484918665</v>
+        <v>-7.179668558722</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.097205509059918</v>
+        <v>-1.058452957612282</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.682979788927796</v>
+        <v>4.694932845021484</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.155117735464685</v>
+        <v>-2.070717741440006</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.677465730900565</v>
+        <v>6.72817339265783</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.75315935666908</v>
+        <v>3.819551407819027</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.157594847325015</v>
+        <v>-5.090859595409583</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5.118722641279028</v>
+        <v>-5.052016272471526</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.727898514988119</v>
+        <v>-3.660272411447679</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.599691772097088</v>
+        <v>-5.532365293510061</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.544178883498326</v>
+        <v>-1.476507904884393</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.658094666079251</v>
+        <v>-2.589094535834292</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.765967376244724</v>
+        <v>5.835245441077447</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.085885265394985</v>
+        <v>5.155951271684451</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>5.688876891946002</v>
+        <v>5.758269770557078</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.398055237666505</v>
+        <v>3.467624673449031</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.113514877103817</v>
+        <v>1.203412150520691</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.307521421770879</v>
+        <v>1.414015813491908</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-5.027173913043484</v>
+        <v>-4.877253833861609</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-5.570374322041367</v>
+        <v>-5.417156142851056</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-5.646329377684047</v>
+        <v>-5.534945270814703</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-5.371554211201847</v>
+        <v>-5.301808949539762</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-7.621408593948523</v>
+        <v>-7.551554246241245</v>
       </c>
     </row>
     <row r="27">
@@ -2347,76 +2347,76 @@
         <v>50</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-5.555237990315661</v>
+        <v>-4.453388367557416</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-7.962052825906916</v>
+        <v>-6.928565088252384</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5476159419891644</v>
+        <v>-0.7067899225677579</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.683333045134667</v>
+        <v>2.431624724267849</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.286442706750933</v>
+        <v>4.064461702700996</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.4855824303122915</v>
+        <v>-0.620708551339348</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.685087448416702</v>
+        <v>1.751479499566649</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.394714229736479</v>
+        <v>1.461449481651911</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9.402535620943965</v>
+        <v>9.469241989751467</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.646584607309869</v>
+        <v>2.71421071085031</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.891397441521036</v>
+        <v>2.958723920108064</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.57684781856112</v>
+        <v>2.644518797175053</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.408917473552656</v>
+        <v>5.477917603797614</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.14012983247874</v>
+        <v>11.20940789731146</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.568076846484146</v>
+        <v>2.638142852773612</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>9.115706066066018</v>
+        <v>9.185098944677094</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>8.975703085336249</v>
+        <v>9.045272521118775</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>16.17955738531074</v>
+        <v>14.91072884700051</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>10.43795620437957</v>
+        <v>9.168141771383553</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.624999999999943</v>
+        <v>3.38469055164866</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.081799591001989</v>
+        <v>4.826334107002815</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>8.005844535359493</v>
+        <v>8.069289590955542</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>10.28061970184162</v>
+        <v>10.35036496350371</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>12.2046783625731</v>
+        <v>12.27453271028038</v>
       </c>
     </row>
     <row r="28">
@@ -2429,76 +2429,76 @@
         <v>40</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.847417033069441</v>
+        <v>-4.791837212441841</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.740703079604877</v>
+        <v>4.774376088218219</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.677240239281119</v>
+        <v>5.712594662949606</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.913941975592905</v>
+        <v>4.950135693011809</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-5.451327809431156</v>
+        <v>-5.385654779535479</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.838420622166964</v>
+        <v>-2.772946019180694</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.13603922946848</v>
+        <v>-1.069647178318533</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.439346350234572</v>
+        <v>-1.37261109831914</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-11.33594909709316</v>
+        <v>-11.26924272828566</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-9.671665695981368</v>
+        <v>-9.604039592440927</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.540812383015123</v>
+        <v>5.60813886160215</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.18746105379763</v>
+        <v>10.25513203241157</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.038217360063022</v>
+        <v>4.107217490307981</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.816860549028668</v>
+        <v>3.886138613861391</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>8.20743426048643</v>
+        <v>8.277500266775895</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.302494310107782</v>
+        <v>6.371887188718858</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>6.156024378335061</v>
+        <v>6.225593814117587</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.088169675111139</v>
+        <v>1.157881823167763</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.4379562043795957</v>
+        <v>-1.138603033531624</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.125000000000064</v>
+        <v>1.511114063565024</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>7.581799591002145</v>
+        <v>5.968567895599016</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>10.00584453535937</v>
+        <v>8.417474409437453</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>10.28061970184149</v>
+        <v>10.35036496350358</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.704678362572984</v>
+        <v>7.774532710280262</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>20</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.958072023034717</v>
+        <v>-8.640847113431967</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.9907030796048844</v>
+        <v>1.024376088218226</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.16279069767441</v>
+        <v>-1.126596980255506</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.659104130308322</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>2.952630049404242</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.60768335273573</v>
+        <v>12.67441860465117</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>12.64919941775837</v>
+        <v>12.71590578656587</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>21.87536400698894</v>
+        <v>21.94299011052938</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>22.14972327410428</v>
+        <v>22.2170497526913</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>26.87062937062937</v>
+        <v>26.93830034924331</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>30.7461381521423</v>
+        <v>30.81513828238726</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>25.52478134110788</v>
+        <v>25.5940594059406</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>24.86585010207057</v>
+        <v>24.93591610836004</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>30.46091015169203</v>
+        <v>30.5303030303031</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>30.3268164575431</v>
+        <v>30.39638589332563</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>25.22183304144782</v>
+        <v>25.29154518950445</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>20.4379562043795</v>
+        <v>20.50743657042863</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>20.625</v>
+        <v>20.69428238039673</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>20.08179959100197</v>
+        <v>20.15173621243063</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>20.00584453535944</v>
+        <v>20.0758902510216</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>20.28061970184157</v>
+        <v>20.35036496350365</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>15.2046783625731</v>
+        <v>15.27453271028038</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>25</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.325878594249232</v>
+        <v>2.359152886568062</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.009296920395123</v>
+        <v>-1.975623911781781</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.586357039187227</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.837209302325583</v>
+        <v>3.873403019744487</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11.47193951730154</v>
+        <v>11.53761254719721</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.65910413030832</v>
+        <v>11.72457873329459</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.88623799825429</v>
+        <v>10.95263004940424</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.392316647264259</v>
+        <v>-1.325581395348827</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.350800582241625</v>
+        <v>-1.284094213434123</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.124635993011125</v>
+        <v>-2.057009889470685</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.149723274104275</v>
+        <v>2.217049752691302</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.87062937062943</v>
+        <v>1.938300349243363</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.746138152142173</v>
+        <v>8.815138282387132</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.475218658892118</v>
+        <v>-3.405940594059395</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-4.13414989792949</v>
+        <v>-4.064083891640024</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-7.539089848308045</v>
+        <v>-7.469696969696969</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-3.673183542456961</v>
+        <v>-3.603614106674435</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.2218330414476952</v>
+        <v>0.2915451895043191</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-3.374999999999993</v>
+        <v>-3.305717619603264</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-3.91820040899789</v>
+        <v>-3.848263787569238</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-7.994155464640563</v>
+        <v>-7.924109748978402</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.719380298158427</v>
+        <v>-3.649635036496342</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-11.7953216374269</v>
+        <v>-11.72546728971962</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-13.67412140575083</v>
+        <v>-13.640847113432</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.16279069767442</v>
+        <v>-11.12659698025551</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.528060482698457</v>
+        <v>-1.46238745280278</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.340895869691671</v>
+        <v>-1.275421266705401</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.886237998254295</v>
+        <v>2.952630049404242</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.392316647264259</v>
+        <v>-2.325581395348827</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.350800582241675</v>
+        <v>-2.284094213434173</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.875364006989017</v>
+        <v>1.942990110529458</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.149723274104275</v>
+        <v>2.217049752691302</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.87062937062933</v>
+        <v>11.93830034924326</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.74613815214223</v>
+        <v>10.81513828238719</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.52478134110795</v>
+        <v>10.59405940594067</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.865850102070603</v>
+        <v>4.935916108360068</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>10.46091015169191</v>
+        <v>10.53030303030299</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>10.32681645754299</v>
+        <v>10.39638589332552</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.22183304144778</v>
+        <v>5.291545189504404</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.437956204379496</v>
+        <v>5.507436570428631</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.624999999999929</v>
+        <v>5.694282380396658</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-4.918200408998096</v>
+        <v>-4.848263787569444</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-4.994155464640556</v>
+        <v>-4.924109748978395</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.719380298158505</v>
+        <v>-4.64963503649642</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-4.795321637426831</v>
+        <v>-4.725467289719553</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>14</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.61159287996344</v>
+        <v>10.64486717228227</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.27641736531917</v>
+        <v>10.31009037393251</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.836716901233032</v>
+        <v>8.872071324901519</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.122923588039875</v>
+        <v>8.159117305458778</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.944818416022613</v>
+        <v>8.010293019008884</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.02909514111143352</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.350800582241575</v>
+        <v>-7.284094213434074</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.16107829270323</v>
+        <v>6.228704396243671</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>20.72115184553284</v>
+        <v>20.78847832411987</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.156343656343665</v>
+        <v>6.224014634957598</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>26.46042386642794</v>
+        <v>26.5294239966729</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>26.23906705539348</v>
+        <v>26.30834512022621</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>18.4372786734992</v>
+        <v>18.50734467978867</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>19.03233872312058</v>
+        <v>19.10173160173166</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>18.89824502897166</v>
+        <v>18.96781446475418</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>25.93611875573352</v>
+        <v>26.00583090379014</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>26.15224191866533</v>
+        <v>26.22172228471447</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>26.33928571428582</v>
+        <v>26.40856809468255</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>18.65322816243077</v>
+        <v>18.72316478385942</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>18.57727310678801</v>
+        <v>18.64731882245017</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>11.7091911304131</v>
+        <v>11.77893639207518</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.63324979114453</v>
+        <v>11.70310413885181</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>3</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>12.99254526091622</v>
+        <v>13.02581955323505</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.65736974627153</v>
+        <v>12.69104275488488</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-22.11566405114793</v>
+        <v>-22.08030962747944</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.50387596899224</v>
+        <v>10.54006968641114</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.13860618396819</v>
+        <v>10.20427921386387</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.32577079697498</v>
+        <v>10.39124539996125</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.274350019402164</v>
+        <v>9.341085271317596</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.315866084424798</v>
+        <v>9.382572453232299</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.542030673655596</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.816389940770932</v>
+        <v>8.88371641935796</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.537296037296286</v>
+        <v>8.604967015910219</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.412804818808887</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.191448007774305</v>
+        <v>7.260726072607028</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>7.063052559992215</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.888499708114409</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>7.10462287104648</v>
+        <v>7.174103237095615</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>6.748466257668248</v>
+        <v>6.818402879096901</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>6.672511202025866</v>
+        <v>6.742556917688027</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.947286368507996</v>
+        <v>7.017031630170081</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>6.871345029240011</v>
+        <v>6.941199376947289</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>10</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-13.67412140575083</v>
+        <v>-13.640847113432</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-14.00929692039512</v>
+        <v>-13.97562391178178</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.162790697674417</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.528060482698464</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.65910413030832</v>
+        <v>13.72457873329459</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>22.88623799825429</v>
+        <v>22.95263004940424</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>32.60768335273588</v>
+        <v>32.67441860465131</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.64919941775844</v>
+        <v>22.71590578656594</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>21.87536400698901</v>
+        <v>21.94299011052945</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>22.14972327410428</v>
+        <v>22.2170497526913</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.87062937062937</v>
+        <v>21.93830034924331</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.74613815214216</v>
+        <v>10.81513828238712</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>10.52478134110802</v>
+        <v>10.59405940594074</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>19.86585010207057</v>
+        <v>19.93591610836004</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>20.46091015169196</v>
+        <v>20.53030303030303</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>20.32681645754303</v>
+        <v>20.39638589332556</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>10.22183304144775</v>
+        <v>10.29154518950438</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>10.43795620437964</v>
+        <v>10.50743657042877</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>20.62500000000007</v>
+        <v>20.6942823803968</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>20.08179959100205</v>
+        <v>20.1517362124307</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>10.00584453535958</v>
+        <v>10.07589025102174</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>20.20467836257303</v>
+        <v>20.2745327102803</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.4699485294467749</v>
+        <v>-0.4702606293593234</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3420339508065737</v>
+        <v>-0.3425089624071518</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.4534709902074709</v>
+        <v>-0.4538574380245635</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3752011988677424</v>
+        <v>-0.3757030589205925</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4254045590935718</v>
+        <v>-0.4266199416254395</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2513436308857067</v>
+        <v>-0.2527617556738022</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2311104639732378</v>
+        <v>-0.2325772276610749</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1939892876465805</v>
+        <v>-0.1955097963034831</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1951387955669901</v>
+        <v>-0.1966576273404286</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1748451980319814</v>
+        <v>-0.1764128745452496</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.09242919226343815</v>
+        <v>-0.0940879003394457</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.08511225616489071</v>
+        <v>-0.08678925649145697</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.08545024151616332</v>
+        <v>-0.08716228528535908</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.04972494255460447</v>
+        <v>-0.05148751575695343</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.03238395958761231</v>
+        <v>-0.03418852542172601</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1079521237571441</v>
+        <v>-0.1096491228070136</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.134399475371012</v>
+        <v>-0.1360699846283779</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.1616301101400239</v>
+        <v>-0.1632722850617512</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.07747681929439665</v>
+        <v>-0.07921413295351698</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.112410071942449</v>
+        <v>-0.1141008531362004</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.008155431486706277</v>
+        <v>-0.00998885495474866</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.06614106751998605</v>
+        <v>-0.06790843082382736</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1334217022988469</v>
+        <v>-0.1351010239101953</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1614680960103314</v>
+        <v>-0.1631171698155498</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3302</v>
+        <v>3306</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.6816402027432744</v>
+        <v>-0.6820006129813834</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.579694032308474</v>
+        <v>-0.580191219474095</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.6491177576380451</v>
+        <v>-0.6495912625861351</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.4734469288604473</v>
+        <v>-0.4741616224683796</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4907223315391747</v>
+        <v>-0.4924626407727146</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3469199660772233</v>
+        <v>-0.3488268022048047</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.3798059908990652</v>
+        <v>-0.381706393568976</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>-0.2515296193103111</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1907161686148697</v>
+        <v>-0.1928566343916742</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2537071630955055</v>
+        <v>-0.2558050701935102</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1730519898474654</v>
+        <v>-0.1752370806922485</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1329916311811274</v>
+        <v>-0.1352379268266191</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1835328409154258</v>
+        <v>-0.1857661493282095</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.145508513964586</v>
+        <v>-0.147798253890528</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1220689556159229</v>
+        <v>-0.1244157166776674</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2037424162838803</v>
+        <v>-0.2059673378321563</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2292427748534607</v>
+        <v>-0.2314438682198698</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2255672003902163</v>
+        <v>-0.2277784819932123</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.142630430032284</v>
+        <v>-0.1449343145003184</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1795977011494259</v>
+        <v>-0.1818505501168701</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1300007115698207</v>
+        <v>-0.1323375258588158</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1575937212991505</v>
+        <v>-0.1599017683254402</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1977333105713939</v>
+        <v>-0.1999827836992552</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2253640359732429</v>
+        <v>-0.2275846520910747</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3249</v>
+        <v>3253</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.7706984228657134</v>
+        <v>-0.7714942440790935</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6005534168793787</v>
+        <v>-0.601578110255069</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.7089362224017464</v>
+        <v>-0.7099166321628019</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4882724963896194</v>
+        <v>-0.4895667327761331</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5305084631146215</v>
+        <v>-0.5332920982795599</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5404673419904285</v>
+        <v>-0.5432292764883471</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5614043777408071</v>
+        <v>-0.5641895224611986</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5163595262841767</v>
+        <v>-0.5192185932686897</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4574182293004512</v>
+        <v>-0.4603488033974088</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.5702381995694452</v>
+        <v>-0.5730796782676819</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5234833476001981</v>
+        <v>-0.5263672711911198</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.4476778970799131</v>
+        <v>-0.4506736170660304</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4808557128884416</v>
+        <v>-0.4838813254559469</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.530757167637141</v>
+        <v>-0.5337371003419662</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.4963352877391287</v>
+        <v>-0.4993996488441326</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5891359029595691</v>
+        <v>-0.5920520754927381</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.5515619208353471</v>
+        <v>-0.5545343520732118</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.5769380799040107</v>
+        <v>-0.5798877653897634</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.5270099910721768</v>
+        <v>-0.5300097156363677</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.5984860129111595</v>
+        <v>-0.601388482360413</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.5086063130570011</v>
+        <v>-0.5116544509599663</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.5662871164400087</v>
+        <v>-0.5692710393009861</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.5809187596968926</v>
+        <v>-0.5838698244496356</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.6078793474915329</v>
+        <v>-0.6108039020774498</v>
       </c>
     </row>
     <row r="9">
@@ -3430,161 +3430,161 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3214</v>
+        <v>3218</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.9710012327510995</v>
+        <v>-0.9719177706365301</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7645503196534662</v>
+        <v>-0.7657473685719012</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.9513157770624048</v>
+        <v>-0.9523894875185519</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.720613826926126</v>
+        <v>-0.7220262575872027</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7284935170319073</v>
+        <v>-0.7317726860434419</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.7406483449392027</v>
+        <v>-0.743900871155347</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.8154023607676848</v>
+        <v>-0.818621882589575</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.7050101457162796</v>
+        <v>-0.7083890638707828</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.6769077361592579</v>
+        <v>-0.6803206285284702</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7206706894175099</v>
+        <v>-0.7240890973914063</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.7384081172809118</v>
+        <v>-0.7417865209082066</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.6898170025882351</v>
+        <v>-0.6932785981251115</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.7422339408810217</v>
+        <v>-0.7457164714065527</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.7283203958648343</v>
+        <v>-0.731838983154816</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.6243763949818657</v>
+        <v>-0.6280752148503765</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.7867621015668931</v>
+        <v>-0.7902177384508491</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.747384101289633</v>
+        <v>-0.7509009283798704</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.8030116790491348</v>
+        <v>-0.8064696988330908</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.7860263989133855</v>
+        <v>-0.7894917572163536</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.7671690490988112</v>
+        <v>-0.770646235369874</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.7326237848139314</v>
+        <v>-0.7361867928471639</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.7901753651380758</v>
+        <v>-0.7936749663697071</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.8080272654990281</v>
+        <v>-0.811486543175441</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.8656389989701552</v>
+        <v>-0.8690347229079336</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.09756</t>
+          <t>X &gt; -0.09755</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3161</v>
+        <v>3165</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9103023102734156</v>
+        <v>-0.9118634245988488</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.8833151421984482</v>
+        <v>-0.884943020661602</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.9549684718476996</v>
+        <v>-0.9566435885591602</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.8342776514625356</v>
+        <v>-0.8361731184030816</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8362365833273913</v>
+        <v>-0.8405281563203744</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.851748339021654</v>
+        <v>-0.856005621088066</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9148947896626325</v>
+        <v>-0.9191487060954486</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7350928512302701</v>
+        <v>-0.7396021435412266</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7387099021408758</v>
+        <v>-0.7432137102894814</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8018013473417653</v>
+        <v>-0.8063021197317113</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8244418172630787</v>
+        <v>-0.8288910906063691</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.7388884358629042</v>
+        <v>-0.7434749104356371</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.8679854291944622</v>
+        <v>-0.8725191483432866</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9132508254011142</v>
+        <v>-0.9177516176814464</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.7650647244278446</v>
+        <v>-0.7698179811169581</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.9086070461622526</v>
+        <v>-0.9131259013074313</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.929496673770096</v>
+        <v>-0.9340050272293041</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.079082651637187</v>
+        <v>-1.083415390754212</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.033932614319106</v>
+        <v>-1.038304754492437</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.017969984202217</v>
+        <v>-1.022347471291496</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.005431761716032</v>
+        <v>-1.009879949185468</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.9995301089655726</v>
+        <v>-1.00399607673338</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.9907275467352861</v>
+        <v>-0.9951814673238886</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.9215475153136481</v>
+        <v>-0.9260992012520077</v>
       </c>
     </row>
     <row r="11">
@@ -3594,243 +3594,243 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3078</v>
+        <v>3082</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.17492759730191</v>
+        <v>-1.177078997489936</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9770388558789946</v>
+        <v>-0.9794898911632259</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.044350724268284</v>
+        <v>-1.046901098099262</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.030447250289008</v>
+        <v>-1.033108908044042</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.184179307367501</v>
+        <v>-1.189894708526751</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.172937213360925</v>
+        <v>-1.178647073157016</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.21715457040483</v>
+        <v>-1.222910447530253</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.057475018304991</v>
+        <v>-1.063476811746511</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.9977452961116597</v>
+        <v>-1.003822983211329</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.074183211639777</v>
+        <v>-1.080265703424111</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.072534894773106</v>
+        <v>-1.078588373318389</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.9125421504062246</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.144441323416203</v>
+        <v>-1.150590783244887</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.152679798788505</v>
+        <v>-1.158851331446208</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.9504764285416698</v>
+        <v>-0.9569988059071903</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.016730807478496</v>
+        <v>-1.023095027949388</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.067024709393763</v>
+        <v>-1.073345411303777</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.28270651756651</v>
+        <v>-1.288765691324642</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.177353558838078</v>
+        <v>-1.183525528696663</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.263384166125888</v>
+        <v>-1.269424683764001</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.268411379462087</v>
+        <v>-1.274519865365086</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.227921698406796</v>
+        <v>-1.234096778809786</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.226363084777461</v>
+        <v>-1.232508860693557</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.15334632878492</v>
+        <v>-1.159600969148563</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.07345</t>
+          <t>X &gt; -0.07344</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2979</v>
+        <v>2983</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.442275969375054</v>
+        <v>-1.445238330996837</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.426824411231507</v>
+        <v>-1.429866840234368</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.51566405114793</v>
+        <v>-1.518836036711569</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.477895732686086</v>
+        <v>-1.481242334900863</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.524724925660436</v>
+        <v>-1.532340817226505</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.486041014836829</v>
+        <v>-1.493681846512146</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.573041040463998</v>
+        <v>-1.580703283929097</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.398994443591477</v>
+        <v>-1.406941848833334</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.171775866142767</v>
+        <v>-1.180024833847746</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.225203984992348</v>
+        <v>-1.233519732647132</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.299474586858288</v>
+        <v>-1.307649846774652</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.258758793864104</v>
+        <v>-1.267041887818465</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.29399562712198</v>
+        <v>-1.302430187886692</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.161401328681357</v>
+        <v>-1.170056865359101</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.031070915332371</v>
+        <v>-1.040019720516966</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.018835412419193</v>
+        <v>-1.027704325096501</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.032862042122076</v>
+        <v>-1.041741196975444</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.252203809473521</v>
+        <v>-1.26081345887301</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.11700358114323</v>
+        <v>-1.125762894096063</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.245600067046595</v>
+        <v>-1.254160873704379</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.232754399608282</v>
+        <v>-1.241431905452764</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.221931378763344</v>
+        <v>-1.230642412294991</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.330118553191987</v>
+        <v>-1.338643079391787</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.2521863571315</v>
+        <v>-1.26083436984031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.06139</t>
+          <t>X &gt; -0.06138</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2850</v>
+        <v>2854</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.84676324355101</v>
+        <v>-1.850788024102805</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.641608898111002</v>
+        <v>-1.645999433339497</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.948474918441548</v>
+        <v>-1.952773395595379</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.877076411960132</v>
+        <v>-1.881642213380083</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.049147969627711</v>
+        <v>-2.059324452454717</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.808120416414127</v>
+        <v>-1.818596754170592</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.79461306557549</v>
+        <v>-1.80529401886465</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.42581280916238</v>
+        <v>-1.437079653188555</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.39966620178788</v>
+        <v>-1.41096768851255</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.455641579603238</v>
+        <v>-1.467051730474807</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.371059121983748</v>
+        <v>-1.38253169132684</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.315953438594946</v>
+        <v>-1.327575435822993</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.337049544467348</v>
+        <v>-1.348910583232353</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.223470407143878</v>
+        <v>-1.235549532606896</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.9875951585100466</v>
+        <v>-1.000164925520508</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.106619589385723</v>
+        <v>-1.118893335874468</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.22026089632466</v>
+        <v>-1.232415225164473</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.51486163642339</v>
+        <v>-1.526636628677444</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.348383550436544</v>
+        <v>-1.360349368710857</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.386212333566931</v>
+        <v>-1.398089907916777</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.418375663116429</v>
+        <v>-1.430342891524496</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.403692631540984</v>
+        <v>-1.415706387633861</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.459120740108624</v>
+        <v>-1.471001061014739</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.37426900584795</v>
+        <v>-1.386294199320183</v>
       </c>
     </row>
     <row r="14">
@@ -3840,161 +3840,161 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2696</v>
+        <v>2700</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.294937882396617</v>
+        <v>-2.300413767857236</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.096125470799841</v>
+        <v>-2.102001575264516</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.228533637701723</v>
+        <v>-2.234664644017471</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.112717059971914</v>
+        <v>-2.119244039079049</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.163419598720566</v>
+        <v>-2.177723973582488</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.919377815159621</v>
+        <v>-1.933993746469945</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.93499311121861</v>
+        <v>-1.949835905693298</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.750723726910287</v>
+        <v>-1.765934856320847</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.910003828276302</v>
+        <v>-1.924978191334681</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.92537400039113</v>
+        <v>-1.940576580701276</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.777925304707097</v>
+        <v>-1.793270925524695</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.630109181807853</v>
+        <v>-1.645770447216869</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.810197274529358</v>
+        <v>-1.825953565639367</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.640776678108679</v>
+        <v>-1.6568631032845</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.280175775933124</v>
+        <v>-1.297011171078864</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.513941919313964</v>
+        <v>-1.530258269549265</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.515580878749972</v>
+        <v>-1.531948055695501</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.821098120654398</v>
+        <v>-1.837057914708481</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.620540648637835</v>
+        <v>-1.636740878739509</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.782407407407405</v>
+        <v>-1.798321169899133</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.785558689842709</v>
+        <v>-1.801648915205256</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.802902684803641</v>
+        <v>-1.819002421073144</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.877333579582235</v>
+        <v>-1.893248512986546</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.820544189355687</v>
+        <v>-1.836578400830732</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.03728</t>
+          <t>X &gt; -0.03727</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2475</v>
+        <v>2479</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.153705072684346</v>
+        <v>-3.161230806477533</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.62763893080762</v>
+        <v>-2.636159697467505</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.644510204994077</v>
+        <v>-2.653642960812775</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.575616348977022</v>
+        <v>-2.585180413628862</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.759014772995172</v>
+        <v>-2.779441095717118</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.510169836799584</v>
+        <v>-2.530927874634926</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.378609513784227</v>
+        <v>-2.399934053159868</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.314034832731949</v>
+        <v>-2.335601435428991</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.41104154609706</v>
+        <v>-2.432450267965002</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.278914819849149</v>
+        <v>-2.300892761512337</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.303652931683509</v>
+        <v>-2.325486362878515</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.037693910432147</v>
+        <v>-2.060093869945781</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.455792660408051</v>
+        <v>-2.478034408375862</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.131154272574221</v>
+        <v>-2.154032197112841</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.921589511455991</v>
+        <v>-1.945112830546712</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.189109985239178</v>
+        <v>-2.211956720400629</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.01806670119992</v>
+        <v>-2.041264951404933</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.140117784831972</v>
+        <v>-2.163183180716956</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.981398634330112</v>
+        <v>-2.004640724257285</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.972821702299314</v>
+        <v>-1.996011618797787</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.968240764123053</v>
+        <v>-1.991696503121275</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.020800599884808</v>
+        <v>-2.044222606697062</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.045713092988805</v>
+        <v>-2.068989875206029</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.855927698032964</v>
+        <v>-1.879561682619986</v>
       </c>
     </row>
     <row r="16">
@@ -4004,79 +4004,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2208</v>
+        <v>2212</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.234408272626638</v>
+        <v>-4.244873959069551</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.381494229812169</v>
+        <v>-3.393708065765672</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.183407433830745</v>
+        <v>-3.196894192339862</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.886309548661849</v>
+        <v>-2.900790528642617</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.823525233484276</v>
+        <v>-2.854140030122373</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.162998295567689</v>
+        <v>-2.194703777916168</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.37218896803784</v>
+        <v>-2.404032130945694</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.491237510573619</v>
+        <v>-2.523067930357811</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.380040348323504</v>
+        <v>-2.412069067497896</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.31905543495526</v>
+        <v>-2.351708901150758</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.649916527786772</v>
+        <v>-2.681826651803078</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.273514773514776</v>
+        <v>-2.306303967303457</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.606723497249384</v>
+        <v>-2.639652540824684</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.261512617413317</v>
+        <v>-2.29522952295229</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.127835058055716</v>
+        <v>-2.162237876331538</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.138367826647389</v>
+        <v>-2.172399672399671</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.156253519883606</v>
+        <v>-2.190364895317977</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.235258196131298</v>
+        <v>-2.269320455220601</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.902757758566665</v>
+        <v>-1.937308580676401</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.05131103074141</v>
+        <v>-2.085501013105073</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.161529219490937</v>
+        <v>-2.195893584409028</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.256598903554597</v>
+        <v>-2.290866749881744</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.272571787520128</v>
+        <v>-2.306661697138011</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.914886854818214</v>
+        <v>-1.949698754457415</v>
       </c>
     </row>
     <row r="17">
@@ -4086,79 +4086,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1904</v>
+        <v>1908</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.635160366789762</v>
+        <v>-4.651733583105376</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.749421660519857</v>
+        <v>-3.768155032113732</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.810931861860361</v>
+        <v>-3.830871813952363</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.405246472908544</v>
+        <v>-3.426700822415427</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.482771570673471</v>
+        <v>-3.527322517737851</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.434645869691678</v>
+        <v>-2.481242472526617</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.658316457191248</v>
+        <v>-2.705196263648276</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.908479316711613</v>
+        <v>-2.955133944776513</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.786377003733548</v>
+        <v>-2.833287342013001</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.062005512844046</v>
+        <v>-3.109093222803956</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.518335181010549</v>
+        <v>-3.535946599575503</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.118932216009455</v>
+        <v>-3.108623529797363</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.222530255168479</v>
+        <v>-3.211987434879369</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.630913538724933</v>
+        <v>-2.620971909299485</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.580569134730261</v>
+        <v>-2.600618338404054</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.687625413161598</v>
+        <v>-2.736920351742896</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.896626765900194</v>
+        <v>-2.945650660199242</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.867172194154342</v>
+        <v>-2.916396294299183</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.673620537370034</v>
+        <v>-2.723091396115997</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.299528301886788</v>
+        <v>-2.349650673996571</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.655484100660253</v>
+        <v>-2.705406644712163</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.9637252442838</v>
+        <v>-3.013114984580497</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-3.026466912331664</v>
+        <v>-3.075512459230765</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-3.020111553393292</v>
+        <v>-3.069282803346461</v>
       </c>
     </row>
     <row r="18">
@@ -4168,79 +4168,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.938503290695721</v>
+        <v>-5.960749433334286</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.387129131050358</v>
+        <v>-5.411176752343785</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.203899345265576</v>
+        <v>-5.230268877683187</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.538020617968712</v>
+        <v>-4.566963952732578</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.932968458158584</v>
+        <v>-4.993599203108786</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.79332067018278</v>
+        <v>-3.856560274666215</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.858233746217458</v>
+        <v>-3.922369950595758</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.735279154947115</v>
+        <v>-3.80013688277986</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.845265526891083</v>
+        <v>-3.909861084599768</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.278482146857215</v>
+        <v>-4.343074960066083</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.127199802818808</v>
+        <v>-4.158871623230077</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.790909090909089</v>
+        <v>-3.790034008470279</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.896718990714909</v>
+        <v>-3.895808827083911</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.098139176452193</v>
+        <v>-3.098248286367095</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.53735581654842</v>
+        <v>-3.571776199332263</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-3.956116375143338</v>
+        <v>-4.023543123543121</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-4.364541567148329</v>
+        <v>-4.431200313570997</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.188296668249592</v>
+        <v>-4.255589745800613</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-3.876011657177912</v>
+        <v>-3.943858127475117</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-3.6545299938157</v>
+        <v>-3.722744146438565</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-3.544438032760333</v>
+        <v>-3.613695886334732</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-3.585486733990408</v>
+        <v>-3.654807710683158</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.27576195862931</v>
+        <v>-3.345555926483989</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-3.192717793657529</v>
+        <v>-3.262882255706025</v>
       </c>
     </row>
     <row r="19">
@@ -4250,161 +4250,161 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.694255633938717</v>
+        <v>-6.726348972168026</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.874968562186169</v>
+        <v>-5.910147721305592</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.814195293368485</v>
+        <v>-4.855191732220071</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.88497142956389</v>
+        <v>-3.891127531671309</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.033292171786655</v>
+        <v>-5.08281996585275</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.685697664755253</v>
+        <v>-3.738107833869591</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.45856379680928</v>
+        <v>-4.470820286667454</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.323454371815167</v>
+        <v>-4.375618736648313</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.391999084114296</v>
+        <v>-4.444034422701691</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-4.976210205904614</v>
+        <v>-5.027840106374136</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.701850938789278</v>
+        <v>-4.753780464212213</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.156357136117251</v>
+        <v>-4.169484081894417</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.856560498532438</v>
+        <v>-3.829056474167125</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.878517009716717</v>
+        <v>-2.809238944883994</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.38752321127275</v>
+        <v>-3.317457204983285</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.875173869313294</v>
+        <v>-3.847508064149736</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.493003362276788</v>
+        <v>-4.506162832311624</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.030608731655185</v>
+        <v>-4.086265904948391</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.246254321936227</v>
+        <v>-3.345636892839664</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.092080511662907</v>
+        <v>-3.191689112476496</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-3.108569107267328</v>
+        <v>-3.16658210588762</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.14174582608635</v>
+        <v>-3.19984228090928</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.125559650080056</v>
+        <v>-3.183469622962519</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-3.158820883279091</v>
+        <v>-3.216814167071014</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.02301</t>
+          <t>X &gt; 0.023</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-7.213141369453155</v>
+        <v>-7.257483641460901</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-6.507026257361517</v>
+        <v>-6.554809432143777</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-5.504222670957702</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.890063424947144</v>
+        <v>-3.90538211171517</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.709878664516644</v>
+        <v>-4.738249521768303</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.704532233328038</v>
+        <v>-3.68686540839478</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.295580183563885</v>
+        <v>-4.229188132413938</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.210498465446079</v>
+        <v>-4.143763213530647</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.302574922551003</v>
+        <v>-4.28409421343413</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.481648743466437</v>
+        <v>-4.511555344016081</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.2072894763511</v>
+        <v>-4.237495701854158</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.575636567439844</v>
+        <v>-3.607154196211241</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.787559479916055</v>
+        <v>-2.769939060651936</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.642796072371176</v>
+        <v>-1.573518007538453</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.028503267692628</v>
+        <v>-1.958437261403162</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.070965986741555</v>
+        <v>-2.001573108130479</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.842582449560794</v>
+        <v>-2.773013013778268</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.166498772590529</v>
+        <v>-2.149256267690525</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.167883211678834</v>
+        <v>-1.204767436857267</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.384132420091319</v>
+        <v>-1.473295033082323</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.470711824523072</v>
+        <v>-1.560467794855271</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.584649066103083</v>
+        <v>-1.674337643235468</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.584096934355877</v>
+        <v>-1.620437956204377</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.842853630114284</v>
+        <v>-1.825923910724192</v>
       </c>
     </row>
     <row r="21">
@@ -4417,76 +4417,76 @@
         <v>868</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.845549977179367</v>
+        <v>-7.907058717527534</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-6.755292343736087</v>
+        <v>-6.823004321804561</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.048081004183437</v>
+        <v>-5.128580247015741</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.325448200538105</v>
+        <v>-2.359473692584274</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.347075373878305</v>
+        <v>-2.40524459565993</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8998878513640705</v>
+        <v>-0.8978468959960253</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.787301520646047</v>
+        <v>-1.7209094694961</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.493118480024862</v>
+        <v>-1.42638322810943</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.960892325360895</v>
+        <v>-1.957633732334472</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.867460332850335</v>
+        <v>-1.928716647775317</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.707911628306746</v>
+        <v>-1.769204542841344</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.494468218348814</v>
+        <v>-0.5588359623260004</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4476306894556572</v>
+        <v>0.4481658053229651</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.259568941567117</v>
+        <v>1.32884700639984</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.4858271399580616</v>
+        <v>0.5558931462475272</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.1624026890053827</v>
+        <v>0.2317955676164587</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.6605543805740766</v>
+        <v>-0.5909849447915505</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.3528796022304022</v>
+        <v>-0.351393960897461</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.7371506807892345</v>
+        <v>0.6681713580291557</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.6480414746543843</v>
+        <v>0.5105854802819181</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.4504631854720955</v>
+        <v>0.3124710000311524</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.4897155031013725</v>
+        <v>0.4207178372284943</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.879698042855388</v>
+        <v>0.879709037151521</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1125124639555821</v>
+        <v>0.1823668116628596</v>
       </c>
     </row>
     <row r="22">
@@ -4499,158 +4499,158 @@
         <v>697</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.517426249055639</v>
+        <v>-8.598354195584939</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-7.218997348355181</v>
+        <v>-7.308957245115117</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.87756881305269</v>
+        <v>-4.987506597176406</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4485049833887018</v>
+        <v>-0.5078203088472577</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.670917625555603</v>
+        <v>-1.761532751948081</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.769467298263109</v>
+        <v>-0.7832672010848611</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.256619144602844</v>
+        <v>-1.190227093452897</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.5351737901214051</v>
+        <v>-0.468438538205973</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.493657725098771</v>
+        <v>-1.426951356291269</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.410350278725346</v>
+        <v>-2.342724175184905</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.850276725895718</v>
+        <v>-1.78295024730869</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2722277722277653</v>
+        <v>-0.2045567936138326</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1747095807136603</v>
+        <v>0.243709710958619</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8104956268221599</v>
+        <v>0.8797736916548828</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.2533755625937602</v>
+        <v>-0.1839826839826841</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.244612113885537</v>
+        <v>-1.175042678103011</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.266006729653824</v>
+        <v>-1.279883381924193</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.03681007257441138</v>
+        <v>-0.06399200099986757</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.1658895265423297</v>
+        <v>-0.02000333388898667</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.483521255277509</v>
+        <v>0.2945933552878373</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.1206221537238577</v>
+        <v>0.01866564444076602</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.6823413661170292</v>
+        <v>0.6655512099219933</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.1759839579819982</v>
+        <v>0.2458383056892757</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.05918</t>
+          <t>X &gt; 0.05917</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>563</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-9.836093236736708</v>
+        <v>-9.93455340713826</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.448450359548566</v>
+        <v>-7.565816556265148</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.565605158332858</v>
+        <v>-4.711888574847855</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.332402005094913</v>
+        <v>-0.4148219363187877</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.111099351956419</v>
+        <v>-2.237035340126724</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.0195281585768754</v>
+        <v>-0.01439833901581267</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.2233026377881018</v>
+        <v>-0.1569105866381548</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5018572833066628</v>
+        <v>-0.4351220313912307</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.697090334891811</v>
+        <v>-1.63038396608431</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.294247300431557</v>
+        <v>-2.226621196891116</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.726601814234947</v>
+        <v>-2.659275335647919</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.415589710642706</v>
+        <v>-1.347918732028774</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5966180316033558</v>
+        <v>-0.527617901358397</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.06541738351070592</v>
+        <v>0.1346954483434288</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.4168354102969118</v>
+        <v>-0.3467694040074463</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.5284891415942639</v>
+        <v>-0.4590962629831878</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.015939726202554</v>
+        <v>-0.9463702904200275</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.8401138612071151</v>
+        <v>-0.8745325490115263</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.0124242894859492</v>
+        <v>-0.1286058323981507</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.5828152753108355</v>
+        <v>-0.825152248578533</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2379162171684754</v>
+        <v>-0.4843061903961541</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.1362513793830118</v>
+        <v>-0.2780920498633606</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.8490033608113734</v>
+        <v>0.8113578713050629</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.4178222346867742</v>
+        <v>0.4876765823940516</v>
       </c>
     </row>
     <row r="24">
@@ -4663,240 +4663,240 @@
         <v>443</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.58911022006847</v>
+        <v>-7.742842678842166</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.803018893489295</v>
+        <v>-5.975623911781781</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.864727721559916</v>
+        <v>-3.075112893997627</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2417036843480602</v>
+        <v>0.1234030197444866</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.022442505170375</v>
+        <v>-1.205116759290483</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.08607042244315</v>
+        <v>2.02054285885513</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.313204290389123</v>
+        <v>1.37959634153907</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.708806948241353</v>
+        <v>1.775542200156785</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4020084065224125</v>
+        <v>0.4687147753299143</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.07761119800017724</v>
+        <v>0.1452373015406181</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1272513639919168</v>
+        <v>0.1945778425789442</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.320067572876567</v>
+        <v>2.3877385514905</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.442767365625379</v>
+        <v>3.511767495870338</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.120286959085405</v>
+        <v>4.189565023918128</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.787198416677313</v>
+        <v>2.857264422966779</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.606977567422291</v>
+        <v>3.676370446033367</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.798726569902584</v>
+        <v>2.86829600568511</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.609220428835137</v>
+        <v>2.538736200740331</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.966172908668511</v>
+        <v>2.754627581664657</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.250282167042897</v>
+        <v>2.042596987138303</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.384282660979466</v>
+        <v>2.174208122543064</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.631126702402334</v>
+        <v>1.562376737508089</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.131635503195966</v>
+        <v>2.201380764858051</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.378493260992961</v>
+        <v>1.448347608700239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.08329</t>
+          <t>X &gt; 0.08328</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>374</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-6.848724580353974</v>
+        <v>-7.061899745010912</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.468182862039683</v>
+        <v>-5.426811246874131</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.991550575970628</v>
+        <v>-1.974489521659329</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.04576942107866699</v>
+        <v>-0.04194089559943137</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.3868331343228135</v>
+        <v>0.151369160953827</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.499529662223217</v>
+        <v>3.406276346026694</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.992620976977697</v>
+        <v>3.059013028127644</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.980023778267643</v>
+        <v>3.046759030183075</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.489624949673264</v>
+        <v>2.556331318480765</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.779619326137876</v>
+        <v>2.847245429678317</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.053978593253213</v>
+        <v>3.12130507184024</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.434459157863415</v>
+        <v>5.502130136477348</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.905712620227327</v>
+        <v>5.974712750472285</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.280100490044042</v>
+        <v>7.349378554876765</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>5.291382016964199</v>
+        <v>5.361448023253665</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>5.354527172968552</v>
+        <v>5.423920051579628</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.954476032011115</v>
+        <v>5.024045467793641</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.755166374781084</v>
+        <v>4.653247317163945</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.876458878176358</v>
+        <v>4.603181251279771</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.99398395721925</v>
+        <v>3.726197274013757</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.718163227365679</v>
+        <v>3.449608552856233</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.840069134289912</v>
+        <v>2.742556917688269</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.18436301734959</v>
+        <v>4.254108279011675</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.306282640647964</v>
+        <v>3.376136988355242</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.09535</t>
+          <t>X &gt; 0.09534</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>297</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-5.501363930667743</v>
+        <v>-5.786061634884113</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-5.009296920395123</v>
+        <v>-4.96900139522549</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5994990567220668</v>
+        <v>-0.5963672133044611</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.696741074900828</v>
+        <v>1.680711989844156</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.9970231293416632</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.52532486609428</v>
+        <v>3.391245399961264</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.421355055110489</v>
+        <v>3.487747106260436</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.473904088521692</v>
+        <v>2.540639340437124</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.180971993009209</v>
+        <v>2.24767836181671</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.410481063845133</v>
+        <v>2.478107167385573</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.022632973100933</v>
+        <v>4.08995945168796</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.419124353906966</v>
+        <v>6.486795332520899</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.632425777560293</v>
+        <v>6.701425907805252</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.752206090271748</v>
+        <v>8.821484155104471</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.41768956695352</v>
+        <v>5.487755573242985</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>7.016094098180254</v>
+        <v>7.08548697679133</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>6.882000404031331</v>
+        <v>6.951569839813857</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>6.664786061581978</v>
+        <v>6.512280975457557</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>6.43122219764556</v>
+        <v>6.059276035311647</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5.608164983164983</v>
+        <v>5.242777363674321</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.401664910867375</v>
+        <v>5.034679356243409</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.989009518524419</v>
+        <v>4.84099092216254</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.600485021706895</v>
+        <v>5.67023028336898</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.524543682438427</v>
+        <v>5.594398030145705</v>
       </c>
     </row>
     <row r="27">
@@ -4909,158 +4909,158 @@
         <v>251</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.007454739084132</v>
+        <v>-6.974180446765303</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.796698495198271</v>
+        <v>-4.563859205899426</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5082859220306588</v>
+        <v>-0.5116821764990434</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.149462266752465</v>
+        <v>1.128304980528796</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.574706315720505</v>
+        <v>1.184671370726619</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.947641679715439</v>
+        <v>2.779696843530807</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.360546298649545</v>
+        <v>3.426938349799492</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.872505487123085</v>
+        <v>3.939240739038517</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.51876463514968</v>
+        <v>3.585471003957181</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.535443058372337</v>
+        <v>3.603069161912778</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.786086910467908</v>
+        <v>5.853413389054936</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.878534508969295</v>
+        <v>7.946205487583228</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.335070958466339</v>
+        <v>8.404071088711298</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.299484898420125</v>
+        <v>9.368762963252848</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.478498323414449</v>
+        <v>5.548564329703915</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.259329124023971</v>
+        <v>7.328722002635047</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>7.520492346871094</v>
+        <v>7.590061782653621</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>7.682150501765221</v>
+        <v>7.485221078832438</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>7.370227120714226</v>
+        <v>6.910598625764671</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.557270916334659</v>
+        <v>7.097444435732697</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>7.412476881838693</v>
+        <v>6.950155184762714</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.938115451694095</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.611296992678213</v>
+        <v>7.681042254340298</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>7.933762027911733</v>
+        <v>8.003616375619011</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.1195</t>
+          <t>X &gt; 0.1194</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>201</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.368702686538974</v>
+        <v>-7.601243153035924</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4985023349763082</v>
+        <v>-0.4631479113078214</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7679023716325091</v>
+        <v>0.8040960890514128</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.4026325866084619</v>
+        <v>0.4683056165041393</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.560094229318217</v>
+        <v>3.625568832304488</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.777327107165185</v>
+        <v>3.843719158315132</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.488871471547611</v>
+        <v>4.555606723463043</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.05514001181777</v>
+        <v>2.121846380625271</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.756552125800816</v>
+        <v>3.824178229341257</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.506158917668628</v>
+        <v>6.573485396255656</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.197362043896703</v>
+        <v>9.265033022510636</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.062969835310547</v>
+        <v>9.131969965555506</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.841613024276192</v>
+        <v>8.910891089108915</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.202483765436916</v>
+        <v>6.272549771726382</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.797543815058297</v>
+        <v>6.866936693669373</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.158499625859861</v>
+        <v>7.228069061642387</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>5.568367694913107</v>
+        <v>5.638079842969731</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.607110433235285</v>
+        <v>6.349020728844543</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>8.286691542288565</v>
+        <v>8.021015053664058</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>7.743491133290611</v>
+        <v>7.478468885698028</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.41252391438794</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="29">
@@ -5073,76 +5073,76 @@
         <v>161</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-7.995109060071783</v>
+        <v>-8.299232206599669</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.03284831615828</v>
+        <v>-1.997493892489793</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2621695796620003</v>
+        <v>-0.2259758622430965</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.857032685003396</v>
+        <v>1.922705714899074</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.149787360121991</v>
+        <v>5.215261963108262</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.998039240490314</v>
+        <v>5.064431291640261</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.961720619816475</v>
+        <v>6.028455871731907</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.382118672416752</v>
+        <v>5.448825041224254</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.092755311336767</v>
+        <v>7.160381414877207</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.745996566029746</v>
+        <v>6.813323044616773</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.951374712244288</v>
+        <v>9.019045690858221</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.31135554344657</v>
+        <v>10.38035567369153</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.08999873241222</v>
+        <v>10.15927679724494</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.70435941884076</v>
+        <v>5.774425425130225</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6.920537480884512</v>
+        <v>6.989930359495588</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>7.407561799157946</v>
+        <v>7.477131234940472</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.681460370640309</v>
+        <v>6.751172518696933</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>8.139819558416825</v>
+        <v>8.209299924465959</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>9.569099378881987</v>
+        <v>9.638381759278715</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>7.783662945039303</v>
+        <v>7.853599566467956</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>5.844353852129622</v>
+        <v>5.914399567791783</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>6.119129018611751</v>
+        <v>6.188874280273836</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.664305691765655</v>
+        <v>6.734160039472933</v>
       </c>
     </row>
     <row r="30">
@@ -5155,76 +5155,76 @@
         <v>141</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-8.284050483764979</v>
+        <v>-8.25077619144615</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.200786282097248</v>
+        <v>-7.167113273483906</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.548288164623102</v>
+        <v>-1.512933740954615</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1344219033481764</v>
+        <v>-0.09822818592927263</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.046407602407918</v>
+        <v>3.112080632303595</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.361231789882787</v>
+        <v>5.426706392869058</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.297585515984792</v>
+        <v>5.363977567134739</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.019030870466231</v>
+        <v>5.085766122381663</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.351327077332833</v>
+        <v>4.418033446140335</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>4.995931382875469</v>
+        <v>5.06355748641591</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.561070791834773</v>
+        <v>4.6283972704218</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.409636462827962</v>
+        <v>6.477307441441894</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.412804818808887</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.900667865930565</v>
+        <v>7.969945930763288</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>2.986417477957104</v>
+        <v>3.05648348424657</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>3.581477527578485</v>
+        <v>3.650870406189561</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.156603691585588</v>
+        <v>4.226173127368114</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.051620275490308</v>
+        <v>4.121332423546932</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>6.395403012890206</v>
+        <v>6.464883378939341</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>8.00088652482269</v>
+        <v>8.070168905219418</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.039246399512685</v>
+        <v>6.109183020941337</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.835631769401992</v>
+        <v>3.905677485064153</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>4.110406935884122</v>
+        <v>4.180152197546207</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>5.452905312927719</v>
+        <v>5.522759660634996</v>
       </c>
     </row>
     <row r="31">
@@ -5237,76 +5237,76 @@
         <v>116</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-10.57067312988873</v>
+        <v>-10.5373988375699</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.319641747981329</v>
+        <v>-8.285968739367988</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.862790487929537</v>
+        <v>-2.82743606426105</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.9903769045709723</v>
+        <v>-0.9541831871520685</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.23056020695671</v>
+        <v>1.296233236852387</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.003931716515218</v>
+        <v>4.069406319501489</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.09313454997843</v>
+        <v>4.159526601128377</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.400786801011598</v>
+        <v>6.467522052927031</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.580233900516987</v>
+        <v>5.646940269324489</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.530536420782049</v>
+        <v>6.59816252432249</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.080757756862894</v>
+        <v>5.148084235449922</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>7.387870749939722</v>
+        <v>7.455541728553655</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.125448496969817</v>
+        <v>7.194448627214776</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.35236754800443</v>
+        <v>10.42164561283715</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.521022515863685</v>
+        <v>4.59108852215315</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>5.978151531002304</v>
+        <v>6.04754440961338</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.844057836853381</v>
+        <v>5.913627272635907</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>4.877005455240862</v>
+        <v>4.946717603297486</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.679335514724393</v>
+        <v>7.748815880773527</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>10.45258620689656</v>
+        <v>10.52186858729328</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>8.18524786686411</v>
+        <v>8.255184488292763</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.385154880187024</v>
+        <v>6.455200595849185</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.797861081151915</v>
+        <v>5.867606342814</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.170195603952415</v>
+        <v>9.240049951659692</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>96</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-9.924121405750796</v>
+        <v>-9.890847113431967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-9.217630253728451</v>
+        <v>-9.18395724511511</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.32399738448126</v>
+        <v>-2.288642960812773</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.128875968992247</v>
+        <v>1.165069686411151</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.805272850634871</v>
+        <v>1.870945880530549</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>5.117437463641657</v>
+        <v>5.182912066627928</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.34457133158763</v>
+        <v>4.410963382737577</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.232683352735734</v>
+        <v>8.299418604651166</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.232532751091711</v>
+        <v>7.299239119899212</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.500364006988939</v>
+        <v>7.567990110529379</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.691389940770939</v>
+        <v>5.758716419357967</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.453962703962716</v>
+        <v>6.521633682576649</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.37113815214223</v>
+        <v>6.440138282387188</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.31644800777453</v>
+        <v>10.38572607260726</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.449183435403917</v>
+        <v>4.519249441693383</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>5.044243485025298</v>
+        <v>5.113636363636374</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.910149790876375</v>
+        <v>4.979719226658901</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>4.805166374781095</v>
+        <v>4.874878522837719</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.14628953771291</v>
+        <v>8.215769903762045</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>11.45833333333334</v>
+        <v>11.52761571373007</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>10.91513292433539</v>
+        <v>10.98506954576404</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>8.755844535359437</v>
+        <v>8.825890251021598</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>7.988953035174909</v>
+        <v>8.058698296836994</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>12.0796783625731</v>
+        <v>12.14953271028038</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>82</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-13.4302189667264</v>
+        <v>-13.39694467440757</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-12.54588228624878</v>
+        <v>-12.51220927763544</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.229485189359309</v>
+        <v>-4.194130765690822</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.06522972206465738</v>
+        <v>-0.02903600464575362</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.008524883155189</v>
+        <v>2.074197913050867</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.634713886405883</v>
+        <v>4.700188489392154</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.081359949473807</v>
+        <v>5.147752000623754</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.680854084443055</v>
+        <v>9.747589336358487</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.722370149465689</v>
+        <v>9.789076518273191</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.72902254357431</v>
+        <v>7.79664864711475</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.125333030201837</v>
+        <v>3.192659508788864</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.504775712092794</v>
+        <v>6.572446690706727</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.941260103361742</v>
+        <v>3.010260233606701</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.597952072815197</v>
+        <v>7.66723013764792</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2.060972053290087</v>
+        <v>2.131038059579552</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>2.656032102911468</v>
+        <v>2.725424981522544</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.521938408762544</v>
+        <v>2.59150784454507</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.197442797545314</v>
+        <v>1.267154945601938</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.072102545842988</v>
+        <v>5.141582911892122</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>8.917682926829272</v>
+        <v>8.986965307226001</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>9.593994712953254</v>
+        <v>9.663931334381907</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>7.079015267066758</v>
+        <v>7.149060982728919</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>7.353790433548888</v>
+        <v>7.423535695210973</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>12.15589787476822</v>
+        <v>12.2257522224755</v>
       </c>
     </row>
     <row r="34">
@@ -5483,158 +5483,158 @@
         <v>79</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.43361507663688</v>
+        <v>-14.40034078431805</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-13.50296780647107</v>
+        <v>-13.46929479785773</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.55026320726607</v>
+        <v>-3.514908783597583</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4665881660288491</v>
+        <v>-0.4303944486099454</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.699787618567356</v>
+        <v>1.765460648463034</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.418597801194402</v>
+        <v>4.484072404180672</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.911554453950494</v>
+        <v>4.977946505100441</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.696290947672452</v>
+        <v>9.763026199587884</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.737807012695086</v>
+        <v>9.804513381502588</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.698148817115516</v>
+        <v>7.765774920655957</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.909216944990355</v>
+        <v>2.976543423577382</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.427591395945825</v>
+        <v>6.495262374559758</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.771454607838429</v>
+        <v>2.840454738083388</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.613388936044593</v>
+        <v>7.682667000877316</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.891166557766773</v>
+        <v>1.961232564056239</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>2.486226607388154</v>
+        <v>2.55561948599923</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.352132913239231</v>
+        <v>2.421702349021757</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.9813267123338321</v>
+        <v>1.051038860390456</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>4.994918229696019</v>
+        <v>5.064398595745153</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>8.97943037974683</v>
+        <v>9.048712760143559</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.702052755559016</v>
+        <v>9.771989376987669</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>7.094452130296155</v>
+        <v>7.164497845958316</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>7.369227296778284</v>
+        <v>7.438972558440369</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>12.35657709675031</v>
+        <v>12.42643144445758</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2039</t>
+          <t>X &gt; 0.2038</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-14.5436866231421</v>
+        <v>-14.51041233082327</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-13.42958677546758</v>
+        <v>-13.39591376685424</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.275084341003001</v>
+        <v>-3.239729917334515</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3589484327603643</v>
+        <v>0.395142150179268</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.892229372373997</v>
+        <v>2.957902402269674</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.079393985380783</v>
+        <v>3.144868588367054</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.306527853326756</v>
+        <v>2.372919904476703</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.375799294764711</v>
+        <v>6.442534546680143</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.866590722106196</v>
+        <v>7.933297090913698</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.643479949017916</v>
+        <v>5.711106052558357</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1207377668578999</v>
+        <v>0.1880642454449273</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4.189469950339515</v>
+        <v>4.257140928953447</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.615703369533541</v>
+        <v>1.6847034997785</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.7138600428569646</v>
+        <v>-0.643794036567499</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.1187999932355837</v>
+        <v>-0.04940711462450764</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2528936873845069</v>
+        <v>-0.1833242516019808</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3578771034797867</v>
+        <v>-0.2881649554231629</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.206072146408545</v>
+        <v>4.275552512457679</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.197741619987561</v>
+        <v>8.267678241416213</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>8.396561730827081</v>
+        <v>8.466306992489166</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>11.21917111619629</v>
+        <v>11.28902546390356</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.89109598555355</v>
+        <v>15.92437027787238</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.860268296996189</v>
+        <v>6.89394130560953</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.2176692821854</v>
+        <v>11.25302370585388</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.156049882035724</v>
+        <v>6.192243599454628</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.180843260743103</v>
+        <v>0.2463178637293737</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.319852879148321</v>
+        <v>-2.253117627232889</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.278336814125687</v>
+        <v>-2.211630445318185</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.052172224895116</v>
+        <v>-2.984546121354676</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.125639044736303</v>
+        <v>-7.058312566149276</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-7.404732948211205</v>
+        <v>-7.337061969597272</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.079948804379512</v>
+        <v>-7.010948674134553</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.750580977732703</v>
+        <v>-8.68130291289998</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-9.409512216770004</v>
+        <v>-9.339446210480538</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-5.915901442510936</v>
+        <v>-5.84650856389986</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-4.600719774341023</v>
+        <v>-4.531150338558497</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-3.256427828117467</v>
+        <v>-3.186715680060843</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-7.388130752142175</v>
+        <v>-7.31865038609304</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.751811594202891</v>
+        <v>-5.682529213806163</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-10.64283809015737</v>
+        <v>-10.57290146872872</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-7.820242421162305</v>
+        <v>-7.750196705500144</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-4.646916530042489</v>
+        <v>-4.577171268380404</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.27358250699212</v>
+        <v>-3.203728159284843</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>99</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>18.04305031142091</v>
+        <v>18.07632460373974</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.65736974627153</v>
+        <v>12.69104275488488</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.24797231248844</v>
+        <v>14.28332673615693</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.473572938689216</v>
+        <v>7.50976665610812</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.118404163766186</v>
+        <v>8.184077193661864</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.255063726267913</v>
+        <v>3.320538329254184</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.502399614415907</v>
+        <v>4.568791665565854</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1834409284933116</v>
+        <v>0.2501761804087437</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.795245026686075</v>
+        <v>-1.728538657878573</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.4612225928475269</v>
+        <v>0.5288486963879677</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.294721170340168</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-3.583916083916087</v>
+        <v>-3.516245105302154</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.678104272100192</v>
+        <v>-1.609104141855234</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.909562093235564</v>
+        <v>-2.840284028402841</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-3.568493332272865</v>
+        <v>-3.4984273259834</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.9532312624494566</v>
+        <v>-0.8838383838383805</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.07722394649737652</v>
+        <v>-0.00765451071485046</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1822073625926564</v>
+        <v>-0.1124952145360325</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.996387229963872</v>
+        <v>-2.926906863914738</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.799242424242422</v>
+        <v>-1.729960043845693</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-3.352543843341394</v>
+        <v>-3.282607221912741</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-2.418397888882986</v>
+        <v>-2.348352173220825</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.133521712299846</v>
+        <v>-1.063776450637761</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1993620414673103</v>
+        <v>-0.1295076937600328</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>152</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13.43114175214394</v>
+        <v>13.46441604446277</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.490703079604877</v>
+        <v>8.524376088218219</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.34047629972927</v>
+        <v>10.37583072339776</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.02141982864137</v>
+        <v>5.057613546060274</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.971939517301536</v>
+        <v>6.037612547197213</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.159104130308322</v>
+        <v>6.224578733294592</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.702027471938507</v>
+        <v>6.768419523088454</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.765578089577836</v>
+        <v>5.832313341493268</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.491304680916265</v>
+        <v>4.558011049723767</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.006942954357363</v>
+        <v>7.074569057897804</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.965512747788488</v>
+        <v>6.032839226375515</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.370629370629374</v>
+        <v>4.438300349243306</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.219822362668545</v>
+        <v>5.288822492913503</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.31425502531841</v>
+        <v>6.383533090151133</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.655323786281109</v>
+        <v>5.725389792570574</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.566173309586695</v>
+        <v>7.635566188197771</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.774184878595662</v>
+        <v>6.843754314378188</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>7.327096199342492</v>
+        <v>7.396808347399116</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>6.227429888590102</v>
+        <v>6.296910254639236</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>7.73026315789474</v>
+        <v>7.799545538291468</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.87127327521258</v>
+        <v>5.941209896641233</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>7.111107693254176</v>
+        <v>7.181153408916337</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>7.385882859736306</v>
+        <v>7.455628121398391</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>7.967836257309948</v>
+        <v>8.037690605017225</v>
       </c>
     </row>
     <row r="9">
@@ -6077,158 +6077,158 @@
         <v>187</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.24031709692301</v>
+        <v>14.27359138924184</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.62706671596851</v>
+        <v>9.660739724581852</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.46544111819254</v>
+        <v>12.50079554186103</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.00833229697799</v>
+        <v>8.044526014396894</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.17782187024271</v>
+        <v>8.243494900138387</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.364986483249496</v>
+        <v>8.430461086235766</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.73115778435055</v>
+        <v>9.797549835500497</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.848325063965689</v>
+        <v>7.915060315881121</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.355081770699542</v>
+        <v>7.421788139507044</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.185524434796427</v>
+        <v>8.253150538336868</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.459883701911764</v>
+        <v>8.527210180498791</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.646030440148081</v>
+        <v>7.713701418762014</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.660576654816033</v>
+        <v>8.729576785060992</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>8.439219843781679</v>
+        <v>8.508497908614402</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6.71076988816683</v>
+        <v>6.780835894456295</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>9.444867370943292</v>
+        <v>9.514260249554368</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>8.776014318505588</v>
+        <v>8.845583754288114</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.740549618987856</v>
+        <v>9.81026176704448</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>9.421913423630905</v>
+        <v>9.491393789680039</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>9.074197860962556</v>
+        <v>9.143480241359285</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>8.530997451964602</v>
+        <v>8.600934073393255</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>9.524561112899541</v>
+        <v>9.594606828561702</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>9.79933627938167</v>
+        <v>9.869081541043755</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>10.79291365669075</v>
+        <v>10.86276800439803</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.09756</t>
+          <t>X &lt; -0.09755</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>240</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10.0758785942492</v>
+        <v>10.10915288656803</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.907369746271542</v>
+        <v>8.941042754884883</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.55100261551874</v>
+        <v>9.586357039187227</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.587209302325576</v>
+        <v>7.62340301974448</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.638606183968207</v>
+        <v>7.704279213863884</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.825770796974993</v>
+        <v>7.891245399961264</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.719571331587623</v>
+        <v>8.78596338273757</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.357683352735727</v>
+        <v>6.424418604651159</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.399199417758361</v>
+        <v>6.465905786565862</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.29203067365561</v>
+        <v>7.359656777196051</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.566389940770947</v>
+        <v>7.633716419357974</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.453962703962716</v>
+        <v>6.521633682576649</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>8.24613815214223</v>
+        <v>8.315138282387188</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.858114674441204</v>
+        <v>8.927392739273927</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.949183435403903</v>
+        <v>7.019249441693368</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>8.794243485025284</v>
+        <v>8.86363636363636</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>9.076816457543032</v>
+        <v>9.146385893325558</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>11.05516637478109</v>
+        <v>11.12487852283772</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>10.43795620437957</v>
+        <v>10.5074365704287</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>10.20833333333333</v>
+        <v>10.27761571373006</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.08179959100205</v>
+        <v>10.1517362124307</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>10.00584453535944</v>
+        <v>10.0758902510216</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>9.863953035174895</v>
+        <v>9.93369829683698</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>8.954678362573098</v>
+        <v>9.024532710280376</v>
       </c>
     </row>
     <row r="11">
@@ -6241,240 +6241,240 @@
         <v>323</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.793370854311121</v>
+        <v>9.82664514662995</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.291012677128094</v>
+        <v>7.324685685741436</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.708897352360843</v>
+        <v>7.74425177602933</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.3047015623875</v>
+        <v>7.340895279806404</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.797016916682338</v>
+        <v>8.862689946578016</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8.674584006469303</v>
+        <v>8.740058609455573</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.140107967294547</v>
+        <v>9.206500018444494</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>7.623163228896715</v>
+        <v>7.689898480812147</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.045484247479735</v>
+        <v>7.112190616287236</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.81963645280937</v>
+        <v>7.88726255634981</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.784398196704899</v>
+        <v>7.851724675291926</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.26691420035074</v>
+        <v>6.334585178964673</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.547995737281546</v>
+        <v>8.616995867526505</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.636236449467013</v>
+        <v>8.705514514299736</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6.738915117550441</v>
+        <v>6.808981123839907</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>7.333975167171822</v>
+        <v>7.403368045782898</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>7.819076519462541</v>
+        <v>7.888645955245067</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>9.881275765905968</v>
+        <v>9.950987913962592</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>8.859008835958512</v>
+        <v>8.928489202007647</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>9.665247678018574</v>
+        <v>9.734530058415302</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>9.741242315460262</v>
+        <v>9.811178936888915</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>9.355689736597832</v>
+        <v>9.425735452259993</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>9.32086737986014</v>
+        <v>9.390612641522225</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>8.625730994152043</v>
+        <v>8.695585341859321</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.07345</t>
+          <t>X &lt; -0.07344</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>422</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.12208712505489</v>
+        <v>9.155361417373719</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.549944785766016</v>
+        <v>8.583617794379357</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.005978918836277</v>
+        <v>9.041333342504764</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.52915243028766</v>
+        <v>8.565346147706563</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>8.874783119197275</v>
+        <v>8.940456149092952</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8.588014082914967</v>
+        <v>8.653488685901237</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.236948898728222</v>
+        <v>9.303340949878169</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>8.010526954631473</v>
+        <v>8.077262206546905</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.393275247142249</v>
+        <v>6.459981615949751</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.804273959595584</v>
+        <v>6.871900063136025</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.31560005135546</v>
+        <v>7.382926529942488</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.036506147880559</v>
+        <v>7.104177126494491</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>7.333815877260712</v>
+        <v>7.40281600750567</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.401558592292709</v>
+        <v>6.470836657125432</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>5.505660528610854</v>
+        <v>5.575726534900319</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>5.3898201042986</v>
+        <v>5.459212982909676</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.492693234794217</v>
+        <v>5.562262670576743</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>7.046477591210788</v>
+        <v>7.116189739267412</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.077766630919847</v>
+        <v>6.147246996968981</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>6.975710900473928</v>
+        <v>7.044993280870656</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>6.906444140765082</v>
+        <v>6.976380762193735</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>6.830489085122473</v>
+        <v>6.900534800784634</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>7.579197900893696</v>
+        <v>7.648943162555781</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>7.029322912336134</v>
+        <v>7.099177260043412</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.06139</t>
+          <t>X &lt; -0.06138</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>551</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8.757820518024161</v>
+        <v>8.79109481034299</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.333715783779105</v>
+        <v>7.367388792392447</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.797826571961579</v>
+        <v>8.833180995630066</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.265521462035203</v>
+        <v>8.301715179454106</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>9.170669099878666</v>
+        <v>9.236342129774343</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.90592808675116</v>
+        <v>7.971402689737431</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.859014767764272</v>
+        <v>7.925406818914219</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.947066292844625</v>
+        <v>6.013801544760057</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.80709415460047</v>
+        <v>5.873800523407972</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.122187963431777</v>
+        <v>6.189814066972218</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.670594417479954</v>
+        <v>5.737920896066981</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.391500514005052</v>
+        <v>5.459171492618985</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.537426718385426</v>
+        <v>5.606426848630385</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.953093500817495</v>
+        <v>5.022371565650218</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.74969765197983</v>
+        <v>3.819763658269295</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>4.34475770160121</v>
+        <v>4.414150580212286</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.936616820519447</v>
+        <v>5.006186256301973</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>6.465027233825253</v>
+        <v>6.534739381881877</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>5.592221177156325</v>
+        <v>5.66170154320546</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>5.779264972776758</v>
+        <v>5.848547353173487</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>5.962017376845971</v>
+        <v>6.031953998274624</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.886062321203362</v>
+        <v>5.956108036865523</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.160837487685491</v>
+        <v>6.230582749347576</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>5.721919741883447</v>
+        <v>5.791774089590724</v>
       </c>
     </row>
     <row r="14">
@@ -6487,158 +6487,158 @@
         <v>705</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.16985022545488</v>
+        <v>8.203124517773709</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7.125454852654521</v>
+        <v>7.159127861267862</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.52972601977406</v>
+        <v>7.565080443442547</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.957776678212113</v>
+        <v>6.993970395631017</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.159882779712888</v>
+        <v>7.225555809608565</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.212295619670023</v>
+        <v>6.277770222656294</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.290493317403232</v>
+        <v>6.356885368553179</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.586406756991053</v>
+        <v>5.653142008906485</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.195298708538516</v>
+        <v>6.262005077346018</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.272527127556323</v>
+        <v>6.340153231096764</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.695822564884423</v>
+        <v>5.763149043471451</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.133040718147107</v>
+        <v>5.20071169676104</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.852521130865632</v>
+        <v>5.921521261110591</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.205632404937667</v>
+        <v>5.27491046977039</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.837481307744333</v>
+        <v>3.907547314033799</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.716229300628136</v>
+        <v>4.785622179239212</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.723979578110416</v>
+        <v>4.793549013892942</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>5.895591906695969</v>
+        <v>5.965304054752593</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.118807268209359</v>
+        <v>5.188287634258494</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.731382978723403</v>
+        <v>5.800665359120131</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>5.755558456250263</v>
+        <v>5.825495077678916</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.821447372238858</v>
+        <v>5.891493087901019</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>6.096222538720987</v>
+        <v>6.165967800383072</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.878437227821316</v>
+        <v>5.948291575528593</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.03728</t>
+          <t>X &lt; -0.03727</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>926</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7.988945548892836</v>
+        <v>8.022219841211665</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.357873705954773</v>
+        <v>6.391546714568115</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6.32206093085351</v>
+        <v>6.357415354521997</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.040233060424931</v>
+        <v>6.076426777843835</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.538894160930049</v>
+        <v>6.604567190825726</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5.86212788840767</v>
+        <v>5.927602491393941</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.521227199118229</v>
+        <v>5.587619250268176</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>5.350663914290806</v>
+        <v>5.417399166206238</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.608162700695729</v>
+        <v>5.674869069503231</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.266292732690886</v>
+        <v>5.333918836231327</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>5.324669278423926</v>
+        <v>5.391995757010953</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.613609932184445</v>
+        <v>4.681280910798378</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.756937288211354</v>
+        <v>5.825937418456313</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.887632313030117</v>
+        <v>4.95691037786284</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4.336692434683961</v>
+        <v>4.406758440973427</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>5.039743844996487</v>
+        <v>5.109136723607563</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.581676068774129</v>
+        <v>4.651245504556655</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.908658095443428</v>
+        <v>4.978370243500052</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.47683309422839</v>
+        <v>4.546313460277524</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>4.447894168466526</v>
+        <v>4.517176548863254</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.444650562924288</v>
+        <v>4.514587184352941</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.584678228663968</v>
+        <v>4.654723944326129</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.643470673763808</v>
+        <v>4.713215935425893</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.135563891730762</v>
+        <v>4.205418239438039</v>
       </c>
     </row>
     <row r="16">
@@ -6651,76 +6651,76 @@
         <v>1193</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>7.516155207828412</v>
+        <v>7.549429500147241</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.756000648758274</v>
+        <v>5.789673657371615</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.322167745443302</v>
+        <v>5.357522169111789</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.692196728981074</v>
+        <v>4.728390446399978</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.578393834149814</v>
+        <v>4.644066864045492</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.340579402730789</v>
+        <v>3.40605400571706</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.741225424909786</v>
+        <v>3.807617476059733</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.965604559776814</v>
+        <v>4.032339811692246</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.755653734606646</v>
+        <v>3.822360103414148</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.652396697684658</v>
+        <v>3.720022801225099</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.262045151723726</v>
+        <v>4.329371630310753</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.563839764594164</v>
+        <v>3.631510743208096</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.199616777456562</v>
+        <v>4.268616907701521</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.559148482767561</v>
+        <v>3.628426547600284</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3.319328727384907</v>
+        <v>3.389394733674372</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>3.327632699889776</v>
+        <v>3.397025578500852</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.361183599202718</v>
+        <v>3.430753034985244</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.507667073300226</v>
+        <v>3.57737922135685</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.885567268922742</v>
+        <v>2.955047634971876</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.156433361274104</v>
+        <v>3.225715741670832</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.36763362285452</v>
+        <v>3.437570244283172</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.543145457404698</v>
+        <v>3.613191173066859</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.56645373369404</v>
+        <v>3.636198995356125</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.90375631730906</v>
+        <v>2.973610665016338</v>
       </c>
     </row>
     <row r="17">
@@ -6733,76 +6733,76 @@
         <v>1497</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5.632082730339924</v>
+        <v>5.665357022658753</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.362951245048507</v>
+        <v>4.396624253661848</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.390895877693524</v>
+        <v>4.42625030136201</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.810524846021373</v>
+        <v>3.846718563440277</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.912233046320885</v>
+        <v>3.977906076216563</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.565041421836007</v>
+        <v>2.630516024822278</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.859553541950085</v>
+        <v>2.925945593100032</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.181399163276097</v>
+        <v>3.248134415191529</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.022781806017207</v>
+        <v>3.089488174824709</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.383035788176393</v>
+        <v>3.450661891716834</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.965477613223101</v>
+        <v>3.991566096920792</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.460475730014807</v>
+        <v>3.445972130430761</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.605189588347976</v>
+        <v>3.590321738024286</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.849430639705062</v>
+        <v>2.835553735493633</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.791701805477381</v>
+        <v>2.81976123519582</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.919159984691291</v>
+        <v>2.988552863302367</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.185867893748778</v>
+        <v>3.255437329531304</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.147684744854558</v>
+        <v>3.217396892911182</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.896206037378903</v>
+        <v>2.965686403428037</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.415247160988642</v>
+        <v>2.484529541385371</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.874050760006725</v>
+        <v>2.943987381435377</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.2656975747716</v>
+        <v>3.335743290433761</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.340071939650521</v>
+        <v>3.409817201312606</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>3.330930867583113</v>
+        <v>3.400785215290391</v>
       </c>
     </row>
     <row r="18">
@@ -6815,76 +6815,76 @@
         <v>1788</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5.152694236707298</v>
+        <v>5.185968529026127</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.538189113124439</v>
+        <v>4.57186212173778</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.3275389283679</v>
+        <v>4.362893352036387</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.669611536962456</v>
+        <v>3.70580525438136</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.030598735178636</v>
+        <v>4.096271765074313</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.988713068855809</v>
+        <v>3.05418767184208</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.053835763617421</v>
+        <v>3.120227814767368</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.942878883461994</v>
+        <v>3.009614135377426</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.040260870272327</v>
+        <v>3.106967239079829</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.439609817044804</v>
+        <v>3.507235920585245</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.301204548559276</v>
+        <v>3.334368188445488</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.000383285618192</v>
+        <v>2.999752863209793</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.106317123059455</v>
+        <v>3.105641075683273</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.381604607327112</v>
+        <v>2.381768903147297</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2.785313189318892</v>
+        <v>2.820209009422086</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>3.156659592407841</v>
+        <v>3.226052471018917</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.525921602956899</v>
+        <v>3.595491038739425</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>3.365009775228515</v>
+        <v>3.434721923285139</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.077777233462342</v>
+        <v>3.147257599511477</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.873322147651002</v>
+        <v>2.942604528047731</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.777549031717932</v>
+        <v>2.847485653146585</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.813450799341545</v>
+        <v>2.883496515003706</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.528941849492568</v>
+        <v>2.598687111154653</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.453000510224101</v>
+        <v>2.522854857931378</v>
       </c>
     </row>
     <row r="19">
@@ -6894,161 +6894,161 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.079119112732165</v>
+        <v>4.112393405050994</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.455897510713854</v>
+        <v>3.489570519327195</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.736312265062665</v>
+        <v>2.771666688731152</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.098496526148828</v>
+        <v>2.106720350517413</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.837933753612774</v>
+        <v>2.875106546237063</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.968422093804968</v>
+        <v>2.005903745296507</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.472975143857369</v>
+        <v>2.482154773360072</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.386635779453655</v>
+        <v>2.42465875834953</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.42815184447629</v>
+        <v>2.466145940264234</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.807608120395955</v>
+        <v>2.845968016389122</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.630492504873502</v>
+        <v>2.668755663311195</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.284289784289783</v>
+        <v>2.293898619305779</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.103212261863121</v>
+        <v>2.08375913774519</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.478079367106915</v>
+        <v>1.430195878790187</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.811900198409688</v>
+        <v>1.76283918528312</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.117942906990599</v>
+        <v>2.098364598364604</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.513714338082536</v>
+        <v>2.523431129129214</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.216052694626946</v>
+        <v>2.255916879441791</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.709632504957604</v>
+        <v>1.779112871006738</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.607658959537574</v>
+        <v>1.676941339934302</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.623968265700839</v>
+        <v>1.664260297209118</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.644398752226905</v>
+        <v>1.684753449480169</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.630017292203007</v>
+        <v>1.67021082092176</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.650461495103215</v>
+        <v>1.690717681378636</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.02301</t>
+          <t>X &lt; 0.023</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2307</v>
+        <v>2310</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.216490136023531</v>
+        <v>3.24976442834236</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.795181977107028</v>
+        <v>2.828854985720369</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.259874277878779</v>
+        <v>2.295228701547266</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.484775006763321</v>
+        <v>1.496142037832342</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.877111931094639</v>
+        <v>1.892479041598591</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.399509477440702</v>
+        <v>1.390384073518533</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.686928248469997</v>
+        <v>1.652027120894331</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.649547832666684</v>
+        <v>1.614530625331909</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.691063897689318</v>
+        <v>1.681423027945172</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.780413640135251</v>
+        <v>1.796375190305149</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.648859716245894</v>
+        <v>1.664849580128745</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.352270839311871</v>
+        <v>1.368598148121166</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9881433379676352</v>
+        <v>0.9791434614981114</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4469603294347237</v>
+        <v>0.4127905237653735</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.6357462958421962</v>
+        <v>0.600855659309957</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.6513039206231497</v>
+        <v>0.6166961188559483</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.019457150183733</v>
+        <v>0.9841127731872703</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.6980235176382266</v>
+        <v>0.6892970269449279</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.2215059879293477</v>
+        <v>0.2392704804633041</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.3219696969696955</v>
+        <v>0.3654204158791998</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.3676376161211437</v>
+        <v>0.4114764721709534</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.4216089355326673</v>
+        <v>0.4655006406319941</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.4192678820842062</v>
+        <v>0.436945050083736</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.5427797930022251</v>
+        <v>0.5342729700206306</v>
       </c>
     </row>
     <row r="21">
@@ -7058,79 +7058,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2533</v>
+        <v>2537</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.504772278046772</v>
+        <v>2.538046570365601</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.05190355037773</v>
+        <v>2.085576558991072</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.4360555774646</v>
+        <v>1.471410001133087</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4698623635500709</v>
+        <v>0.4838384846326704</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4801845114122614</v>
+        <v>0.5011276511595497</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.01725093646308551</v>
+        <v>-0.01806544089136253</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2929177624979147</v>
+        <v>0.2692247924407312</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1941613401571161</v>
+        <v>0.1704939578693754</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3536019334816416</v>
+        <v>0.3523408081599015</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3266218686241587</v>
+        <v>0.3483318230195565</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.2700535926257075</v>
+        <v>0.2917059412964136</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1435327064752698</v>
+        <v>-0.1214480784296512</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4581121430171535</v>
+        <v>-0.4584466232731899</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.735061178577169</v>
+        <v>-0.7581418519210317</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.4649888108872844</v>
+        <v>-0.4887791334803069</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.358632795510573</v>
+        <v>-0.3823641608850181</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.07523320741558592</v>
+        <v>-0.0994818752694826</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1802166235108658</v>
+        <v>-0.1808957553775201</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.5553429678711197</v>
+        <v>-0.5323428702959987</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.5259657075285773</v>
+        <v>-0.4798704958838087</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4544780115216156</v>
+        <v>-0.4079799878057955</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4675282457056511</v>
+        <v>-0.4444093153954327</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6033581987109145</v>
+        <v>-0.6035175749275652</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.3401301648647248</v>
+        <v>-0.364016757595067</v>
       </c>
     </row>
     <row r="22">
@@ -7140,161 +7140,161 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2704</v>
+        <v>2708</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.020220989546786</v>
+        <v>2.053495281865615</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.611570089156679</v>
+        <v>1.64524309777002</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9800988682740694</v>
+        <v>1.015453291942556</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1907216054289123</v>
+        <v>-0.1750907348477213</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1263512820074197</v>
+        <v>0.1503972643169789</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1069863441308101</v>
+        <v>-0.1034888640602958</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.0238391755905667</v>
+        <v>0.006267080998661356</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1600752044965077</v>
+        <v>-0.1774740818611491</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.08660737063023305</v>
+        <v>0.06884696303645654</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3284026810220908</v>
+        <v>0.3100368188780394</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1821477398375109</v>
+        <v>0.1640696202409657</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2229939246157429</v>
+        <v>-0.2405734085778164</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3305580130495116</v>
+        <v>-0.3483374171709812</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4932931701425858</v>
+        <v>-0.5109129697500094</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.2448510049404931</v>
+        <v>-0.2630522040939027</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.2183072717115166</v>
+        <v>-0.2363759228853226</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.03878100702603859</v>
+        <v>0.02027969863529222</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.04458045651421827</v>
+        <v>0.04809258898796287</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.2932107084712428</v>
+        <v>-0.2674711786487904</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.327732644017722</v>
+        <v>-0.2802469662256399</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4058250857618972</v>
+        <v>-0.3578649692531997</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.311967733672347</v>
+        <v>-0.2860004432176879</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.4587518323543662</v>
+        <v>-0.4546571930694583</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.327866016125121</v>
+        <v>-0.345851336986982</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.05918</t>
+          <t>X &lt; 0.05917</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2838</v>
+        <v>2842</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.788063468198786</v>
+        <v>1.821337760517615</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.242803919941018</v>
+        <v>1.276476928554359</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.6434395903086596</v>
+        <v>0.6787940139771464</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2258379831385113</v>
+        <v>-0.2092300334767998</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1292625726624337</v>
+        <v>0.1552596060207421</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2946287824151312</v>
+        <v>-0.2880263087222161</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.241391735266042</v>
+        <v>-0.2546528637610237</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.1843194532972348</v>
+        <v>-0.197735510935523</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.05270818968818958</v>
+        <v>0.03896114746285662</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1765223081472342</v>
+        <v>0.1624082668560547</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2606783302840583</v>
+        <v>0.2465027681190719</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.001995721173805975</v>
+        <v>-0.0118925655234392</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1533699293756925</v>
+        <v>-0.1673178579636883</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2836545112647073</v>
+        <v>-0.2974814856002936</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.1833763395609296</v>
+        <v>-0.1975108579320874</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.1651890393034705</v>
+        <v>-0.1792157614075407</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.0672722124077012</v>
+        <v>-0.08147777498083286</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.101882651726072</v>
+        <v>-0.09509804423903745</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.2728108610673061</v>
+        <v>-0.2450247516528776</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.1561400422237824</v>
+        <v>-0.1076873698670795</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.2209107222679307</v>
+        <v>-0.1719794807431256</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.240634337879996</v>
+        <v>-0.212638953763765</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.4379431724099305</v>
+        <v>-0.4307750787201314</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.352051729040717</v>
+        <v>-0.3658613783895746</v>
       </c>
     </row>
     <row r="24">
@@ -7304,243 +7304,243 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2958</v>
+        <v>2962</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.9782131592475238</v>
+        <v>1.011487451566353</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.6430376446031971</v>
+        <v>0.6767106532165386</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1774722157874677</v>
+        <v>0.2128266394559546</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3160165041260328</v>
+        <v>-0.2985822002756606</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1246991381606506</v>
+        <v>-0.09691886025995444</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.5910639934307511</v>
+        <v>-0.5817699398663052</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4706405755768515</v>
+        <v>-0.4803561783418075</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5282520443032936</v>
+        <v>-0.5379469867466824</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3329614708313358</v>
+        <v>-0.3429177428458914</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2795181478932207</v>
+        <v>-0.2896931443462094</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.288808217980602</v>
+        <v>-0.2989273747893648</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.615893540421844</v>
+        <v>-0.6256296642156443</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.7772861822022321</v>
+        <v>-0.7870158744623552</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8777810324592252</v>
+        <v>-0.8874220755408899</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.6737789029884453</v>
+        <v>-0.6838211769212066</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8008982153795756</v>
+        <v>-0.8106673201012882</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.6789209707391208</v>
+        <v>-0.6888854245038942</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.6489060743133024</v>
+        <v>-0.6390010006507154</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.7027795364236695</v>
+        <v>-0.6730018781379101</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.5971471978392984</v>
+        <v>-0.5675259866748021</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.6139113174748232</v>
+        <v>-0.5840045908092648</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.5009122213973214</v>
+        <v>-0.4911026615669982</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.5777784056271784</v>
+        <v>-0.5878733085179491</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.46469283418147</v>
+        <v>-0.4749608751348902</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.08329</t>
+          <t>X &lt; 0.08328</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3027</v>
+        <v>3031</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.692260734761355</v>
+        <v>0.7226699469354827</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.455575042835342</v>
+        <v>0.4535099464859371</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0007728059323994785</v>
+        <v>-0.0002571340411208212</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2678810096612807</v>
+        <v>-0.2683757790740202</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3191248716603639</v>
+        <v>-0.2903585624547844</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.7050102305198109</v>
+        <v>-0.6943313126673232</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6377593718969194</v>
+        <v>-0.6455314739050095</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6346711359193122</v>
+        <v>-0.6424943674342174</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5744847927679473</v>
+        <v>-0.5823859348533134</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6057152954131624</v>
+        <v>-0.6136973689316747</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.641586798311792</v>
+        <v>-0.6494854215361769</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9347706952250832</v>
+        <v>-0.9423310220161554</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9864046673571139</v>
+        <v>-0.9940722439285992</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.155614046042039</v>
+        <v>-1.163097553585565</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.9054089618714158</v>
+        <v>-0.9133268146155942</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.9172632739592075</v>
+        <v>-0.9250805719360145</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.8671149408738543</v>
+        <v>-0.8750238563450594</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.8401722355971017</v>
+        <v>-0.8287184019289029</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.8549197850663433</v>
+        <v>-0.8241389074882335</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.7474843286044219</v>
+        <v>-0.7168617013704974</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.7102796169187471</v>
+        <v>-0.6793983522131057</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6016166729601338</v>
+        <v>-0.5903366619071662</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7695784487528883</v>
+        <v>-0.777603374227219</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.6608650797790645</v>
+        <v>-0.669050265635164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.09535</t>
+          <t>X &lt; 0.09534</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3104</v>
+        <v>3108</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.3764709733718448</v>
+        <v>0.4071528865680278</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2654389105366732</v>
+        <v>0.2643760882182207</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1816262669660489</v>
+        <v>-0.1816429608127663</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4292865336769793</v>
+        <v>-0.4287736767984072</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3601655772194547</v>
+        <v>-0.3304630211665369</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6037163825121894</v>
+        <v>-0.5917837386874822</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5892349097290293</v>
+        <v>-0.5952405878035663</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4968708486754281</v>
+        <v>-0.5030317476870749</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4691836428768568</v>
+        <v>-0.475379058035216</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4866385604051615</v>
+        <v>-0.4929073253680585</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6432141255747013</v>
+        <v>-0.6492535496491882</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.871824065465681</v>
+        <v>-0.8776072838548288</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8857282147064751</v>
+        <v>-0.8916310470962827</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.088329198737881</v>
+        <v>-1.094002211517683</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7641723987330238</v>
+        <v>-0.7703439237426863</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.9217265042566041</v>
+        <v>-0.9276288900566385</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.9083073764872012</v>
+        <v>-0.9142469367419039</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.8846320598710022</v>
+        <v>-0.871693885045751</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.8614969960064016</v>
+        <v>-0.8297540435218025</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.784266409266408</v>
+        <v>-0.7526629572238477</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.7614575702467477</v>
+        <v>-0.7295761066429591</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.721779418278679</v>
+        <v>-0.7089280185184492</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.782182230525585</v>
+        <v>-0.7882648209929783</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.774703080725871</v>
+        <v>-0.7808083450606773</v>
       </c>
     </row>
     <row r="27">
@@ -7550,161 +7550,161 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3150</v>
+        <v>3154</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4123412007496796</v>
+        <v>0.4089480331170421</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1718327735146232</v>
+        <v>0.1542625951539094</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1949740332663623</v>
+        <v>-0.1944691985926497</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3547098895936074</v>
+        <v>-0.3537263177949441</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3866016888872821</v>
+        <v>-0.3563603149043928</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4975604306518804</v>
+        <v>-0.4849510868379383</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5260842766272233</v>
+        <v>-0.531118767257162</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.5655151301972623</v>
+        <v>-0.570530890298329</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5376485114227947</v>
+        <v>-0.5426985708701864</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.53450316568658</v>
+        <v>-0.5396378111383342</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.7164583140007608</v>
+        <v>-0.7213388729011143</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.882535186332646</v>
+        <v>-0.887236945320538</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9126146177216512</v>
+        <v>-0.9173941235565337</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9888348716850288</v>
+        <v>-0.9935433771081037</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.6789709305553373</v>
+        <v>-0.6841408356450174</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8255283780925851</v>
+        <v>-0.8304564633678524</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8459252223301803</v>
+        <v>-0.850844242793471</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.8558214751924993</v>
+        <v>-0.8420836895329913</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.8298726387266129</v>
+        <v>-0.7975998565589464</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.8461477488903029</v>
+        <v>-0.8139558959023887</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.831616203479399</v>
+        <v>-0.7991354198989313</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.7936478504273694</v>
+        <v>-0.7798942180750714</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.8491803616303457</v>
+        <v>-0.8540724374472148</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8746867167919845</v>
+        <v>-0.8795573341077088</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.1195</t>
+          <t>X &lt; 0.1194</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3200</v>
+        <v>3204</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3153228662144301</v>
+        <v>0.3269148208519752</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.04223986942169944</v>
+        <v>0.03987996418721451</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2005501795123195</v>
+        <v>-0.2027248466688505</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3069348418185669</v>
+        <v>-0.3090357019433796</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2819448829470659</v>
+        <v>-0.2860994329393449</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4813994444507728</v>
+        <v>-0.4852939770438098</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4906276733875004</v>
+        <v>-0.4945749195398577</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5338407530185449</v>
+        <v>-0.5377590902851495</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3812921814948922</v>
+        <v>-0.3853993719176572</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4838018815887182</v>
+        <v>-0.4878460722496101</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.6584959039779221</v>
+        <v>-0.6623034811395385</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8263497635967241</v>
+        <v>-0.8299733677084831</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8114942466116659</v>
+        <v>-0.8152288613589178</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7965025479541339</v>
+        <v>-0.8002761060419772</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.6266686011713247</v>
+        <v>-0.6307090473062047</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.6678706403255035</v>
+        <v>-0.6718146900333082</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.6900269610471099</v>
+        <v>-0.6939567858021647</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5893994078502232</v>
+        <v>-0.5934657173201856</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.6540874773677032</v>
+        <v>-0.639695599147359</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.7607677902621717</v>
+        <v>-0.7463163099681012</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.7236952575774112</v>
+        <v>-0.7091496266210768</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.6562416607679893</v>
+        <v>-0.6417384541266031</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.675331563388049</v>
+        <v>-0.6792762221437769</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.6703216374268948</v>
+        <v>-0.6742812722414726</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3240</v>
+        <v>3244</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2498516169346701</v>
+        <v>0.2618158801401123</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.09861233772873135</v>
+        <v>0.09663573304369066</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1285435359685323</v>
+        <v>-0.1303351507055766</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2425452989014119</v>
+        <v>-0.2442440390790424</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3451822992065985</v>
+        <v>-0.3483819364068239</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5090972202134765</v>
+        <v>-0.5120858896361256</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4972437334006017</v>
+        <v>-0.5002985001204436</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5434222983699115</v>
+        <v>-0.5464402910543527</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5151631014428588</v>
+        <v>-0.5182151094144984</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5954411558875208</v>
+        <v>-0.5984463535590194</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5800646139990135</v>
+        <v>-0.5830730597127456</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.6877962136264699</v>
+        <v>-0.6906922797493138</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.748786486430518</v>
+        <v>-0.7516819941105055</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7367571204305889</v>
+        <v>-0.7396836794927211</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.5158057920506991</v>
+        <v>-0.5190485396571702</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.5797302423967139</v>
+        <v>-0.5828581013082896</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6032728556691609</v>
+        <v>-0.6063824856347608</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5668299283612441</v>
+        <v>-0.5699932720340826</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.6406262301350765</v>
+        <v>-0.6436868521628583</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7128545006165226</v>
+        <v>-0.7158161417707518</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.6212531379526212</v>
+        <v>-0.6243648038920639</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.5246921703777616</v>
+        <v>-0.5279298352384174</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.5401146394111294</v>
+        <v>-0.5433176250941969</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.5669265756985027</v>
+        <v>-0.5701035412609343</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3260</v>
+        <v>3264</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2095216036917904</v>
+        <v>0.2076469541068207</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1040486006286443</v>
+        <v>0.1022823572383018</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1609754399521535</v>
+        <v>-0.1625014083013525</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2481565513329471</v>
+        <v>-0.2496176867110549</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3828942734883327</v>
+        <v>-0.3856283909690958</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4836658513878405</v>
+        <v>-0.4862683111904786</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.4765938601527822</v>
+        <v>-0.4792504748261734</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4631347180823369</v>
+        <v>-0.465825297787859</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4347700478904812</v>
+        <v>-0.4374946403935738</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.458172950860785</v>
+        <v>-0.4609147094828288</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4411719290732421</v>
+        <v>-0.4439206470645658</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.519346179492878</v>
+        <v>-0.522017111074156</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5562158680350819</v>
+        <v>-0.5589075191395239</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.5761360900847876</v>
+        <v>-0.5788178084760176</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3605188180885008</v>
+        <v>-0.3635033844600031</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3897630429224819</v>
+        <v>-0.3926798547825499</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4139242831977157</v>
+        <v>-0.4168210770199039</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4089079260966457</v>
+        <v>-0.4118187248687164</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5115078078715811</v>
+        <v>-0.5142826097487259</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.5821078431372584</v>
+        <v>-0.5847873870451252</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.494357319816217</v>
+        <v>-0.4971771637554028</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3988151826050057</v>
+        <v>-0.4017582486722233</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.4124192432672942</v>
+        <v>-0.415331820569854</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.47016826319377</v>
+        <v>-0.4730163093274697</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3285</v>
+        <v>3289</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2255158372963635</v>
+        <v>0.2238871860849372</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.08807229641769254</v>
+        <v>0.08659294113274285</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1253434219888234</v>
+        <v>-0.12663389736867</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.217253632621464</v>
+        <v>-0.2184676360427602</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2931936546112937</v>
+        <v>-0.2955192544956589</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3917587216444431</v>
+        <v>-0.3939577045644995</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.390563939964963</v>
+        <v>-0.3928024974802113</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.470171842659596</v>
+        <v>-0.4723287478450544</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4417096731507257</v>
+        <v>-0.4439005088336501</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4708014977094592</v>
+        <v>-0.4729953572272123</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4215320321419398</v>
+        <v>-0.4237739904946523</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5012238292492981</v>
+        <v>-0.5033839888360632</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4856579643626304</v>
+        <v>-0.4878920206431232</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.5981321642032</v>
+        <v>-0.6002418974846861</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.3891590053975449</v>
+        <v>-0.3915550863033914</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4440397420219853</v>
+        <v>-0.4463424049411344</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4386756445225828</v>
+        <v>-0.4409927474511406</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4041165179566875</v>
+        <v>-0.4064821246079191</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.504293035742009</v>
+        <v>-0.5065282140278882</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6033368805107955</v>
+        <v>-0.6054443125883893</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.5203901900198602</v>
+        <v>-0.522625877484252</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.456583210305304</v>
+        <v>-0.4589016055569459</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.4375787156873372</v>
+        <v>-0.4399085927273561</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.5563566450372477</v>
+        <v>-0.5585472532343729</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3305</v>
+        <v>3309</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1419843634799776</v>
+        <v>0.1406654916100507</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.0634412821897925</v>
+        <v>0.06220256675320002</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1573557729358654</v>
+        <v>-0.1583877055575229</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2830914495541208</v>
+        <v>-0.2840016062693351</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3006236595937679</v>
+        <v>-0.3025316835720133</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3974712533811129</v>
+        <v>-0.3992565537507957</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3708360535217423</v>
+        <v>-0.3726856451237239</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.4817475415732133</v>
+        <v>-0.483476132190944</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.453210220795853</v>
+        <v>-0.4549726731212544</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4566637122035928</v>
+        <v>-0.4584543673520542</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4060332057028404</v>
+        <v>-0.4078749914387387</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4266271865005606</v>
+        <v>-0.428456651660035</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4179149238529476</v>
+        <v>-0.4198014766489635</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5310255970520004</v>
+        <v>-0.5327860294314988</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.3574450095769848</v>
+        <v>-0.359442541428983</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.378208471912032</v>
+        <v>-0.3801582298718245</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.3736666342444082</v>
+        <v>-0.375628581945854</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.3701331319137751</v>
+        <v>-0.372104885910403</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.468388206496563</v>
+        <v>-0.4702339184065494</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5656920519794468</v>
+        <v>-0.5674139673243701</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5469791272567193</v>
+        <v>-0.5487468793567416</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4840254374255579</v>
+        <v>-0.4858735665561724</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4634819315522591</v>
+        <v>-0.4653450062848634</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.5820084755509569</v>
+        <v>-0.5837326266794349</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3319</v>
+        <v>3323</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.185842687606474</v>
+        <v>0.1846161262572181</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1062373507811714</v>
+        <v>0.1050935770074588</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1196560671159972</v>
+        <v>-0.1205807598558408</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2478461034845409</v>
+        <v>-0.2486430466629272</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2967842693970937</v>
+        <v>-0.2984137843407879</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3624721357989671</v>
+        <v>-0.364017495379457</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3691576851989424</v>
+        <v>-0.3707232440089285</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4807724193782121</v>
+        <v>-0.4822151180202923</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4821743074965852</v>
+        <v>-0.4836148844946493</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.42886641605336</v>
+        <v>-0.4303991612716445</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.317263520613615</v>
+        <v>-0.318921470330281</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.3989593414690944</v>
+        <v>-0.4005302354643376</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3049128989088175</v>
+        <v>-0.3066373624838405</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4184448529443969</v>
+        <v>-0.4200420042004112</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2783806671601994</v>
+        <v>-0.2801703262137849</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.2965289826633253</v>
+        <v>-0.298276975701171</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.292546140171936</v>
+        <v>-0.2943047973651289</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2593699660710413</v>
+        <v>-0.2611733445899489</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3562676223352383</v>
+        <v>-0.3579480449559114</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4523397532350302</v>
+        <v>-0.4538991645386545</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4660631422911479</v>
+        <v>-0.4676263852842695</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.403670670903729</v>
+        <v>-0.4053127564971959</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4121513824957859</v>
+        <v>-0.4137746273507332</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5304828305573679</v>
+        <v>-0.5319674401860723</v>
       </c>
     </row>
     <row r="34">
@@ -8124,161 +8124,161 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3322</v>
+        <v>3326</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1973285195107906</v>
+        <v>0.1961191451526858</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1174973379780795</v>
+        <v>0.1163713092456931</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1393952307271462</v>
+        <v>-0.1402638153093392</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2381946474051162</v>
+        <v>-0.2389699629213808</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2874139696784113</v>
+        <v>-0.2889943287370116</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3528719175958699</v>
+        <v>-0.3543686351264554</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3602429840757466</v>
+        <v>-0.3617582246011466</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4720050834536025</v>
+        <v>-0.4733970745828273</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4733657605454908</v>
+        <v>-0.4747556920333551</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4207990625554316</v>
+        <v>-0.4222793505484717</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3090473405883785</v>
+        <v>-0.3106531523700937</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3909183198325366</v>
+        <v>-0.3924366190011455</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.297966258298807</v>
+        <v>-0.2996354664890433</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4115932087120555</v>
+        <v>-0.4131348386637157</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2722465655967952</v>
+        <v>-0.273978944113729</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2898405990587989</v>
+        <v>-0.291532602570399</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2859801780832782</v>
+        <v>-0.2876825135151222</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2529265739368611</v>
+        <v>-0.2546732978905837</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3495400384818623</v>
+        <v>-0.3511644502858005</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.4453547805171354</v>
+        <v>-0.4468587607444192</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.459553792456596</v>
+        <v>-0.4610604231956117</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.397284225170047</v>
+        <v>-0.3988693643630157</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4055072918388376</v>
+        <v>-0.4070741708516294</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5237984586189484</v>
+        <v>-0.5252267605554621</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2039</t>
+          <t>X &lt; 0.2038</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1559829161568018</v>
+        <v>0.154925437922607</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.0753780945124447</v>
+        <v>0.07440586784895231</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1552306084597888</v>
+        <v>-0.1559724216408966</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2558694566242963</v>
+        <v>-0.2565135475975922</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3060372060646301</v>
+        <v>-0.3073949043676194</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.311045123423014</v>
+        <v>-0.3123920478622324</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2908297831729953</v>
+        <v>-0.2922253040106142</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3732007571806406</v>
+        <v>-0.3745074096686452</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4042813112526815</v>
+        <v>-0.4055504951410782</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3541637873924088</v>
+        <v>-0.3555173521571859</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2419060233546233</v>
+        <v>-0.243386198338861</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3243467059256488</v>
+        <v>-0.3257378825368562</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2649297509388404</v>
+        <v>-0.2664272987302283</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3788691675695617</v>
+        <v>-0.380238262917743</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2119709096025773</v>
+        <v>-0.2135607227311382</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2277126027990661</v>
+        <v>-0.2292663476873997</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2242467350295883</v>
+        <v>-0.2258097393397094</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2215462275756224</v>
+        <v>-0.2231166896099239</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3172131093753023</v>
+        <v>-0.3186633996401369</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.3821942446043138</v>
+        <v>-0.3835619309805125</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.3979605289379862</v>
+        <v>-0.3993269801419217</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.3660810795175848</v>
+        <v>-0.3674890180017769</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4034487049991142</v>
+        <v>-0.4048043502512186</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4615881440295482</v>
+        <v>-0.4628773616620734</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_ma_ratio_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_ma_ratio_20.xlsx
@@ -618,821 +618,821 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.1398</t>
+          <t>X ≈ -0.1396</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>22.86348556579184</v>
+        <v>22.16327611406457</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>25.85007576636974</v>
+        <v>25.35277837773795</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21.11601002866063</v>
+        <v>20.68637258701397</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.47443064404516</v>
+        <v>13.24936129831953</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.829245504405158</v>
+        <v>6.121469883401559</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.33360637204208</v>
+        <v>9.709975889058548</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.2014568553892</v>
+        <v>15.78335041704241</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.97787469904938</v>
+        <v>8.621373792238188</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.6155270502935011</v>
+        <v>1.885933965914987</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.57260708589213</v>
+        <v>11.39539247640059</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.848551774539821</v>
+        <v>11.67039942016285</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.252254214443496</v>
+        <v>4.526487786191169</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>10.77898353223652</v>
+        <v>10.2905227205535</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>10.56195582656427</v>
+        <v>10.04625417291057</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>9.908847950983166</v>
+        <v>9.368999798513734</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>10.50461817296433</v>
+        <v>9.931498235924465</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>10.37413198715467</v>
+        <v>9.830563115376684</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>6.945310616785918</v>
+        <v>6.258646590268256</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>7.163149873503521</v>
+        <v>6.47489793992186</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>7.351915754133671</v>
+        <v>6.690978734721227</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>13.47283467867305</v>
+        <v>13.01649744262815</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>10.06975736185397</v>
+        <v>9.498911702410062</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>7.014868904844576</v>
+        <v>6.298019222274739</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.9411993769478</v>
+        <v>6.137711080673064</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.1277</t>
+          <t>X ≈ -0.1276</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>53</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.810882065525426</v>
+        <v>4.908931303586861</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.7324796429884586</v>
+        <v>0.9191702290899499</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.053020571997116</v>
+        <v>3.422156451301532</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.4713633554771661</v>
+        <v>0.9605805692829819</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.01354160960053</v>
+        <v>2.562789046454284</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>11.58308355334928</v>
+        <v>12.10279737652503</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>10.81862602692944</v>
+        <v>11.31522879819245</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>16.17851249930507</v>
+        <v>16.64881502880321</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>16.22510611609191</v>
+        <v>16.78177635583203</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19.21767228952881</v>
+        <v>19.75148343677807</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>21.37620649841744</v>
+        <v>21.90843782798076</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>19.22537151371664</v>
+        <v>19.75985298349778</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>18.11175588734195</v>
+        <v>18.65459378296726</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>23.54010868019441</v>
+        <v>24.05613004807868</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>22.89110751610563</v>
+        <v>23.38326012043483</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>23.49089401329753</v>
+        <v>23.95005320259706</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>19.59899658413684</v>
+        <v>20.08791526563868</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>21.38375923289308</v>
+        <v>21.84467390820534</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>23.48997662692569</v>
+        <v>23.94963631352141</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>25.5682795175864</v>
+        <v>26.05557175043788</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>23.14913336761378</v>
+        <v>23.61158973377864</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>24.96610273136229</v>
+        <v>25.42919574518213</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>23.36198973631896</v>
+        <v>23.79426249318305</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>23.29340063480824</v>
+        <v>23.63933762589102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1157</t>
+          <t>X ≈ -0.1155</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17.65601742625912</v>
+        <v>17.75477293798648</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14.4926125544188</v>
+        <v>14.68001452923602</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>21.58373046883111</v>
+        <v>21.95376308270068</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20.88342614842495</v>
+        <v>21.37356935909001</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>17.71558022812474</v>
+        <v>18.26548859806881</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.9070904846097</v>
+        <v>18.4270501245149</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>22.82904861734233</v>
+        <v>23.32611160948277</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>16.87365496094714</v>
+        <v>17.34397335944759</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>19.76448929008167</v>
+        <v>20.32127240801055</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>13.31115777145128</v>
+        <v>13.84476713359402</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>19.27989403136818</v>
+        <v>19.81206289454089</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>21.855121498595</v>
+        <v>22.38967999071397</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23.58999009366023</v>
+        <v>24.13297389694761</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>17.6803160108511</v>
+        <v>18.1962109355858</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>11.33139953424377</v>
+        <v>11.8233190342163</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>17.62786516448435</v>
+        <v>18.08692899361765</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>17.49996972092175</v>
+        <v>17.98885922106775</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>20.25270257234175</v>
+        <v>20.71360743922392</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>23.32751056448887</v>
+        <v>23.78717870369755</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>14.9606529229093</v>
+        <v>15.44785012341708</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>20.13249058312544</v>
+        <v>20.59493132574534</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>20.06306716947446</v>
+        <v>20.52614020684121</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>20.34386162868395</v>
+        <v>20.77612947147401</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>23.13167556742258</v>
+        <v>23.47761255850558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1036</t>
+          <t>X ≈ -0.1035</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>53</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.558182019868255</v>
+        <v>-4.460639428806616</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.352257138294021</v>
+        <v>6.539249572807392</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.6983474159428056</v>
+        <v>-0.329444864077665</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.094479676040358</v>
+        <v>6.583901236605278</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.762775680494094</v>
+        <v>6.312112973854646</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.950656365392305</v>
+        <v>6.470075336142578</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.184536539978126</v>
+        <v>5.680860887695005</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.155561825882842</v>
+        <v>1.625251740797395</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.075464348332375</v>
+        <v>3.631623952989052</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.185424406515374</v>
+        <v>4.718703858011324</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.459835424275234</v>
+        <v>4.991529032312194</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2.304293637022191</v>
+        <v>2.838280036152412</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.82655659472109</v>
+        <v>7.369096109835233</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.37030230508653</v>
+        <v>10.88602377331949</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>7.836374883899147</v>
+        <v>8.328219573735645</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>6.549486703833693</v>
+        <v>7.008343394102297</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>10.18352308781797</v>
+        <v>10.67229069996967</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>15.73189096022992</v>
+        <v>16.19273496437135</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>14.0688693065349</v>
+        <v>14.52843408880553</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>14.26019172108164</v>
+        <v>14.74738340154039</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>15.60794226018573</v>
+        <v>16.07035472234759</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>11.76606681289507</v>
+        <v>12.22910127819683</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>10.15821977625497</v>
+        <v>10.59046448740074</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>2.538683653677033</v>
+        <v>2.88462064475894</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.09152</t>
+          <t>X ≈ -0.09148</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>83</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>8.936261824200386</v>
+        <v>9.034570130847953</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.625821496037069</v>
+        <v>2.812614589919079</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.394846103038283</v>
+        <v>2.763851926376496</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.476551022240741</v>
+        <v>6.965940381813539</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>12.13233586657199</v>
+        <v>12.68191994131001</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>11.12448781597834</v>
+        <v>11.64408589522798</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10.36029330718241</v>
+        <v>10.8567830982641</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>11.28668372885245</v>
+        <v>11.75672681770257</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>8.933867966157564</v>
+        <v>9.49019219188542</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>9.366658903641763</v>
+        <v>9.900075688102959</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>8.443000780699798</v>
+        <v>8.974788086626631</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.768367684549844</v>
+        <v>6.302423180868971</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>9.452984210292009</v>
+        <v>9.995577503253976</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.034890765728008</v>
+        <v>8.550547878624236</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.180679633383143</v>
+        <v>6.672483916349442</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>3.170306006048257</v>
+        <v>3.629092873137061</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>4.240055981415232</v>
+        <v>4.728712293323923</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>6.541760830427464</v>
+        <v>7.002466000136081</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>4.354110017765365</v>
+        <v>4.813556797333561</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>8.15225456292859</v>
+        <v>8.639384591148499</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>8.816869709435871</v>
+        <v>9.279235051009778</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>7.540225173862957</v>
+        <v>8.003238239211818</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>7.817385115391033</v>
+        <v>8.249624990225151</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>7.744412228352665</v>
+        <v>8.090349219435005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.07947</t>
+          <t>X ≈ -0.07942</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.902913849490787</v>
+        <v>7.651410291230285</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.59095898842502</v>
+        <v>12.30428969552753</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>13.17311831483529</v>
+        <v>13.9445402032669</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>12.46973970118717</v>
+        <v>13.3212621819888</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>9.128456223305008</v>
+        <v>9.10083283986377</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8.313764330058675</v>
+        <v>8.28458425264531</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.557857542143999</v>
+        <v>10.41197040015606</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>9.285575770374592</v>
+        <v>9.09800475064084</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>4.30537015263134</v>
+        <v>3.307198551488618</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.537479439729978</v>
+        <v>2.471613841340087</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.823334609712226</v>
+        <v>3.746336445932762</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.57286204056615</v>
+        <v>6.408914433961989</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.424529863689528</v>
+        <v>1.859774529782904</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8212138803132163</v>
+        <v>-2.354512606860339</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>1.544530368648118</v>
+        <v>-0.1149433151900325</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.8842108522945082</v>
+        <v>-1.913246414227409</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.02562188949981</v>
+        <v>-2.428767151231135</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.131003160043939</v>
+        <v>-1.982995067775626</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.923989559136665</v>
+        <v>-2.181654977554743</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.729343324247367</v>
+        <v>-0.4033596091506837</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.271503546359732</v>
+        <v>-0.969981055341627</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.33818137793746</v>
+        <v>-0.05568252395340068</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>1.965454516850031</v>
+        <v>3.157501821812446</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.890694326441988</v>
+        <v>2.996707325125094</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06741</t>
+          <t>X ≈ -0.06738</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>7.52715565446389</v>
+        <v>8.469302603788876</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.351857351409279</v>
+        <v>5.886432529982542</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.081607546655775</v>
+        <v>9.280335248565144</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.377216992073535</v>
+        <v>6.343522475143423</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.12666146914046</v>
+        <v>9.179830578409479</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.694745645404076</v>
+        <v>5.449329647850142</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.388149099839026</v>
+        <v>3.085088962774094</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.7401721307728337</v>
+        <v>-1.125820214774379</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.929362043775114</v>
+        <v>3.675984996615966</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.933149428594731</v>
+        <v>3.645227895763284</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3490384040155234</v>
+        <v>0.8045824402134514</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.07220420524301119</v>
+        <v>0.5200483618817771</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2740964800065697</v>
+        <v>-1.399048405210699</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2789049356113509</v>
+        <v>-0.4228582442786362</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.921768440826199</v>
+        <v>-2.218301009947353</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.9897641769214971</v>
+        <v>0.6881321183085589</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.176736915051634</v>
+        <v>2.92556114774959</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.620266592459174</v>
+        <v>4.354448748840902</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>4.06423554428077</v>
+        <v>3.788474495597818</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>1.930129542126323</v>
+        <v>1.664672422285243</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.938040608103464</v>
+        <v>3.109927734885709</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.863718716519941</v>
+        <v>3.036180733719185</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.589649010157729</v>
+        <v>1.719156989877725</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>1.514842787799751</v>
+        <v>1.557969701362893</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05536</t>
+          <t>X ≈ -0.05532</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.032260730033279</v>
+        <v>6.966615969894619</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.348843314696438</v>
+        <v>7.354844560312266</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.989475765051907</v>
+        <v>4.171035657753457</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.284104081342093</v>
+        <v>4.206771346207056</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.016511307577602</v>
+        <v>2.013186795482753</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2045972666622546</v>
+        <v>1.531593438661574</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7288819190401483</v>
+        <v>2.004419661313392</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.328563518611318</v>
+        <v>5.528735758222687</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7.600904763563875</v>
+        <v>8.8610459653272</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.835007331937263</v>
+        <v>8.054861191368914</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.818740596557703</v>
+        <v>7.051827470143536</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.251168270433304</v>
+        <v>5.848419149372909</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.014830017409984</v>
+        <v>8.564009381895438</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>6.151116966286196</v>
+        <v>7.670232082015907</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>4.204282236866227</v>
+        <v>5.694830764616405</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>6.093349007774492</v>
+        <v>7.546357076880099</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.019134401028907</v>
+        <v>5.521402251890656</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>3.91581449004849</v>
+        <v>4.750320467595571</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.485475807116089</v>
+        <v>4.323560373537887</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>5.618951698267438</v>
+        <v>5.82404819479838</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>5.079567913267944</v>
+        <v>5.249258134104139</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.655068224613167</v>
+        <v>5.817197144846681</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.932038681348246</v>
+        <v>6.435969460162688</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.508298944046608</v>
+        <v>7.28713636802923</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.0433</t>
+          <t>X ≈ -0.04327</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7.355538443634771</v>
+        <v>7.672027464709188</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3.889754012704827</v>
+        <v>4.284173601518049</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>2.465096656143338</v>
+        <v>3.024897192280029</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.107254931549832</v>
+        <v>3.777271894756225</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.571854061583771</v>
+        <v>5.300553750767762</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.761932514711049</v>
+        <v>5.460003786940284</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.099002590096894</v>
+        <v>3.76242542608005</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.624126001638842</v>
+        <v>5.255756905471358</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3.767434831138473</v>
+        <v>4.487639629815597</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.101160126224549</v>
+        <v>2.786056749701309</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.176693188502988</v>
+        <v>5.111684903222624</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.001776000497969</v>
+        <v>3.932051531561164</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.488564122793967</v>
+        <v>6.416296560805186</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.919979356446106</v>
+        <v>4.814726056061332</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.972871244399876</v>
+        <v>6.830477071310433</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.116485891810711</v>
+        <v>6.944969974938687</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.181158661334706</v>
+        <v>4.588837310961317</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.82115264834588</v>
+        <v>2.204528075197132</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.49006327075633</v>
+        <v>2.869109904133616</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.4192110600546002</v>
+        <v>0.833429188899629</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.3301518560337868</v>
+        <v>1.164073374810847</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.707336222192545</v>
+        <v>1.349785021184516</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.07807654105013739</v>
+        <v>0.6925186055620856</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.354426565737718</v>
+        <v>-0.820971740078825</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03124</t>
+          <t>X ≈ -0.03123</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5.81636714683156</v>
+        <v>6.133902667086808</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.639858994201134</v>
+        <v>3.461704914044113</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.847000200752497</v>
+        <v>1.825508793256617</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.0295370935262369</v>
+        <v>0.1095719346496935</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.160587002442085</v>
+        <v>-2.029848744305525</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-5.316424885653305</v>
+        <v>-5.229978375703546</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.365982936821872</v>
+        <v>-2.10272255768389</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7825082265055059</v>
+        <v>-0.5449759207945704</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.601301262096939</v>
+        <v>-2.078634783031305</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.879899125256962</v>
+        <v>-1.179095857702457</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6266661431182925</v>
+        <v>1.33194512705105</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.02033081618110089</v>
+        <v>0.6822288442214557</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.139085685616301</v>
+        <v>-0.4326632732292239</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.9842625912818903</v>
+        <v>-0.3077630063042065</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1463090804491998</v>
+        <v>0.502619925243657</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.539672788483543</v>
+        <v>-1.921150682802356</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.8060249666271986</v>
+        <v>-0.1593594527362399</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.28387362565303</v>
+        <v>-0.6653778862560458</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.562463576695173</v>
+        <v>-1.943452972543277</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.254623827757641</v>
+        <v>-0.6094635424095785</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.2999963390444407</v>
+        <v>0.315629269642514</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.0008636376913742083</v>
+        <v>0.6136010760455335</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.09996339538004406</v>
+        <v>0.4841012329656067</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.298500997584796</v>
+        <v>-0.7974407463983937</v>
       </c>
     </row>
     <row r="16">
@@ -1442,79 +1442,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.691294476634155</v>
+        <v>-1.75960142331261</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.043560658554782</v>
+        <v>-0.7109078820509467</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.782149564359635</v>
+        <v>0.9509007002257661</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3999885520104343</v>
+        <v>0.6827985482501902</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.370965846095764</v>
+        <v>1.706178223897936</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3962964446374002</v>
+        <v>0.2405345115339088</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5138309296414221</v>
+        <v>0.09320376281602449</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1887148180331906</v>
+        <v>0.9379509379509372</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.2316298396560796</v>
+        <v>1.065879847635046</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.40187427554104</v>
+        <v>3.191906274493554</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.678899862505389</v>
+        <v>3.464141289097952</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.72930697098068</v>
+        <v>3.512234659301917</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9525019915974582</v>
+        <v>1.747991892500636</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2507674402205211</v>
+        <v>0.5257318570416345</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5891763395709688</v>
+        <v>1.142278773857797</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.370710380846667</v>
+        <v>1.703582792677381</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.550047076371015</v>
+        <v>2.898403679653676</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.791931850575246</v>
+        <v>2.11616892514143</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.994512510964199</v>
+        <v>3.304657126313252</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.4276143256676619</v>
+        <v>-0.05218500005641147</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.001971280914539</v>
+        <v>1.328422446614731</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.242191249477479</v>
+        <v>2.551961223360742</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>2.518888480733594</v>
+        <v>2.795595708639269</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>5.077164289227746</v>
+        <v>5.230859311752319</v>
       </c>
     </row>
     <row r="17">
@@ -1524,817 +1524,817 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.622076141362442</v>
+        <v>2.050925202322965</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.361625454525409</v>
+        <v>5.18407711173132</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.945159292758078</v>
+        <v>3.757114773358651</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.909400489346886</v>
+        <v>3.166328548736026</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4.620338651488296</v>
+        <v>4.928081200757241</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>5.160987376475923</v>
+        <v>5.601677804774305</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4.058274017431089</v>
+        <v>4.467612741694133</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.740294751963766</v>
+        <v>2.467777044048219</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.148911083288709</v>
+        <v>4.290621207969622</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.747774368786644</v>
+        <v>5.189484966987571</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.07453847844336536</v>
+        <v>1.39392337142241</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.677770779529439</v>
+        <v>2.134290569493601</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.5878036001541247</v>
+        <v>2.036347604585011</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.03111022718960044</v>
+        <v>1.449130492304448</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.795815548609355</v>
+        <v>4.156806618893974</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>4.412457730734587</v>
+        <v>5.735059790256031</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.309104630186027</v>
+        <v>6.309145480225943</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.525101338270602</v>
+        <v>5.498295273369465</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.060344358549628</v>
+        <v>5.373774449667778</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>5.280219239882129</v>
+        <v>6.266326996421682</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.341685120592608</v>
+        <v>3.326001139108826</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.5525796480930794</v>
+        <v>1.555923362916175</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-1.574961646349415</v>
+        <v>-0.2343404568902656</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.99350852683299</v>
+        <v>-0.7354625020271186</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.004921</t>
+          <t>X ≈ 0.004916</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.427826561424396</v>
+        <v>-3.011544568138987</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.108633635155435</v>
+        <v>-3.609033387667324</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-6.961093621851511</v>
+        <v>-8.012285610622385</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-7.685667437421579</v>
+        <v>-7.912003797329881</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.581882558363205</v>
+        <v>-4.862236955662524</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.403168933758984</v>
+        <v>-5.404604048965169</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.391500170598214</v>
+        <v>-2.003881865393701</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.144527911282701</v>
+        <v>-1.959151959151967</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.444873701483615</v>
+        <v>-2.180873399118212</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.183169128665384</v>
+        <v>-1.578323495736143</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.413615200781251</v>
+        <v>-2.005389180432516</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.039030023815158</v>
+        <v>-2.281971134903813</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.203843122314474</v>
+        <v>-3.746513602004974</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.43190597675266</v>
+        <v>-3.295446964137341</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-4.745352392005138</v>
+        <v>-2.928650297071343</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-4.835871574702153</v>
+        <v>-3.066646977552345</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-4.085279523965802</v>
+        <v>-2.820877039627</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.036948719733267</v>
+        <v>-4.352362543390043</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-6.704399866469977</v>
+        <v>-5.536501714845663</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-6.173341855242676</v>
+        <v>-5.671565619437033</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-5.676939685689597</v>
+        <v>-4.840408722216374</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-5.754283600160512</v>
+        <v>-5.964522293122698</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-4.093516681275787</v>
+        <v>-3.972636059592581</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-3.475467289719667</v>
+        <v>-3.435474354581338</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.01698</t>
+          <t>X ≈ 0.01697</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-4.240911096630875</v>
+        <v>-5.046300336581169</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.893461510332031</v>
+        <v>-3.576076600000349</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.818059775306807</v>
+        <v>-1.826972947039835</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.824423407107091</v>
+        <v>-4.562668491123716</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-6.695232941376098</v>
+        <v>-7.413333927360341</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.977896106924796</v>
+        <v>-4.681293025224917</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.601534854648676</v>
+        <v>-6.33474413617008</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.46058368457075</v>
+        <v>-5.781295480866255</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5.1924725814537</v>
+        <v>-5.653366571182197</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.443788032793229</v>
+        <v>-8.595340813182695</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.169728390631306</v>
+        <v>-7.893921249222139</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-6.800899572591291</v>
+        <v>-7.312134104980935</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-8.785182832283091</v>
+        <v>-9.285395321144058</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-8.591779228616367</v>
+        <v>-9.104444833221045</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-9.676973607633876</v>
+        <v>-10.21578376446232</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-12.48553702500906</v>
+        <v>-13.08795614049244</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-12.61641518826899</v>
+        <v>-13.1918365522175</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-13.15047766903967</v>
+        <v>-13.75390520673528</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-13.36380806506497</v>
+        <v>-13.96862752894573</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-11.23289217630825</v>
+        <v>-11.60811833710563</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-10.68237343315442</v>
+        <v>-10.8880091904177</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-10.33842167515212</v>
+        <v>-10.53398716301675</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-10.49765626868972</v>
+        <v>-10.29035267773838</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>-9.594122573315396</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.02903</t>
+          <t>X ≈ 0.02901</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.773645905664274</v>
+        <v>-4.633089756714369</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.529288884894633</v>
+        <v>-5.325457167679289</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.940599869114628</v>
+        <v>-7.032984163479682</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-9.816609018347826</v>
+        <v>-10.06040862557622</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-13.6591670365792</v>
+        <v>-13.43331189841896</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-14.35148245139973</v>
+        <v>-14.60381192073949</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-13.82031535449626</v>
+        <v>-14.07146030465363</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-14.53444967760826</v>
+        <v>-14.81885862416843</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-13.17998715437908</v>
+        <v>-13.36349608616565</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-14.38778436752702</v>
+        <v>-14.60202545749115</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-13.67571916451108</v>
+        <v>-13.88731256678065</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-15.26327854428342</v>
+        <v>-15.49132814957061</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-15.07529158781592</v>
+        <v>-15.27878663870285</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-12.67154810488837</v>
+        <v>-12.87215344349869</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-11.57270507567981</v>
+        <v>-11.78439632095896</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-10.54150267001748</v>
+        <v>-10.78061442603311</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-11.11662695157771</v>
+        <v>-11.32697271386426</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-9.02390156415035</v>
+        <v>-9.247467438494986</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-8.366489348581538</v>
+        <v>-8.590527335242967</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-9.059234617223957</v>
+        <v>-9.260896642396375</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-8.722189706579542</v>
+        <v>-8.943385391564718</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-9.685386793203385</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-11.18047139335379</v>
+        <v>-10.9873028087726</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-9.50520297253896</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.04109</t>
+          <t>X ≈ 0.04107</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.089322178311043</v>
+        <v>-4.987713433312877</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.842248839070876</v>
+        <v>-4.655585586935857</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.703599743729285</v>
+        <v>-5.332245006746511</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-9.906856198225782</v>
+        <v>-9.392855298040281</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.029029128216386</v>
+        <v>-4.466101299411292</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.364876412680715</v>
+        <v>-0.8409596009276257</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.883983247871015</v>
+        <v>-3.370145659403128</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.330988192218832</v>
+        <v>-4.831135466973592</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.120707510709387</v>
+        <v>-3.547137193127703</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.2412122816672237</v>
+        <v>0.2810887683003997</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.713176729895494</v>
+        <v>-1.180780263338015</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.002886141228835</v>
+        <v>-1.457362217809376</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.281533628550761</v>
+        <v>1.473988439306432</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.159280341939201</v>
+        <v>2.959858424116021</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3.082934055063781</v>
+        <v>2.855738724311898</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.926517446941659</v>
+        <v>1.682938696888783</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.789648038355203</v>
+        <v>1.579058285163775</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>3.433150638258269</v>
+        <v>3.180278226245015</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.652486336059717</v>
+        <v>3.394740453390725</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.673277898276751</v>
+        <v>2.453257534287857</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.3853406981953995</v>
+        <v>0.151708986664346</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.059491979760914</v>
+        <v>1.810650510951838</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.752621350478847</v>
+        <v>1.47625031414929</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.07634448270214733</v>
+        <v>-0.4199927263829437</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.05314</t>
+          <t>X ≈ 0.05311</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.984323179879567</v>
+        <v>-2.807332610463561</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-6.229764766178782</v>
+        <v>-6.729710034402657</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.145513661138935</v>
+        <v>-6.513815901000207</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8985522770079228</v>
+        <v>-1.223865158631924</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.2362878237577064</v>
+        <v>-0.02883506343713549</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.013663987240626</v>
+        <v>-3.548372045674306</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.531698685517838</v>
+        <v>-5.814042293201226</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6084175929575011</v>
+        <v>-0.9719039130804319</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.5722307643996274</v>
+        <v>-0.843975003396281</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.830529972046122</v>
+        <v>-3.110614733909742</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.898923071609104</v>
+        <v>1.573384986576905</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.599269858084767</v>
+        <v>4.237979502693968</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.484436917932392</v>
+        <v>3.12308738524316</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.010214370642551</v>
+        <v>3.610147441457066</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.123617178978634</v>
+        <v>0.7221107066308292</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.9719049651014728</v>
+        <v>1.283414725450491</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.135808008442694</v>
+        <v>-1.761642156862706</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.982961881400556</v>
+        <v>-2.629820379671408</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.2074825294272955</v>
+        <v>0.5258183180625977</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.362823822605101</v>
+        <v>3.681581233709821</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>3.567133983795998</v>
+        <v>3.849430849976144</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.265490882449903</v>
+        <v>2.303680092726744</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.05294561023049482</v>
+        <v>0.3414322250639401</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.7702434091226067</v>
+        <v>0.1792932307744763</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.0652</t>
+          <t>X ≈ 0.06516</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-18.02561884576468</v>
+        <v>-17.40817294659799</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-13.43627773548291</v>
+        <v>-13.45239911003301</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-10.75431879665329</v>
+        <v>-10.50541253965558</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.401769065785714</v>
+        <v>-1.854117259472282</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.046534767713872</v>
+        <v>-6.331356071840496</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-7.526722927822718</v>
+        <v>-7.01475860029624</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-5.829181996492366</v>
+        <v>-4.448496074713695</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-8.596157486189313</v>
+        <v>-7.27442492148375</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-9.379556819805146</v>
+        <v>-7.986832146253427</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-10.98273215360162</v>
+        <v>-9.623219775926543</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-13.19474998526875</v>
+        <v>-11.87199316468346</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-15.13872020368743</v>
+        <v>-13.82924738806246</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-15.43968232612782</v>
+        <v>-14.10380337105945</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-14.83453140148651</v>
+        <v>-14.35203743249256</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-12.17499428192063</v>
+        <v>-11.67284727656244</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-15.72586086376929</v>
+        <v>-15.31322393001169</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-15.02884670020818</v>
+        <v>-14.57676820728296</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-13.47518301684547</v>
+        <v>-13.028980043537</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-10.77254251931338</v>
+        <v>-10.29350941302988</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-11.41192651043316</v>
+        <v>-10.91925910242463</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-10.29865486233011</v>
+        <v>-9.806031334897803</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-7.072489323242991</v>
+        <v>-6.519849319037959</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-4.320143310728092</v>
+        <v>-3.755206430398239</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-3.05880062305296</v>
+        <v>-3.077009290233924</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.07726</t>
+          <t>X ≈ 0.0772</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-11.433750754971</v>
+        <v>-13.81659933085037</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-8.950347631716006</v>
+        <v>-9.952917125458306</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-9.04081059333852</v>
+        <v>-9.83774821365126</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.019614966681083</v>
+        <v>-0.8411093165690247</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-8.557663631339331</v>
+        <v>-9.335845538860184</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-5.490534303495089</v>
+        <v>-5.06932289176617</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.723328887216447</v>
+        <v>-9.973993945094897</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.114821487232113</v>
+        <v>-7.539188361106092</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-10.84677199479205</v>
+        <v>-12.89071150621659</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-14.5004299437275</v>
+        <v>-16.42648902883319</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-15.66913206675039</v>
+        <v>-17.52411702792756</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-14.49316656133679</v>
+        <v>-16.43083596870015</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-9.838109681247445</v>
+        <v>-12.0662760313564</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-12.93754020185764</v>
+        <v>-13.68437310648807</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-10.716136540907</v>
+        <v>-11.62680146097594</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-5.795854952144893</v>
+        <v>-6.955908401060341</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-8.816490933859676</v>
+        <v>-9.799514840182653</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-8.9225269520485</v>
+        <v>-8.562535931645542</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-7.265069120307096</v>
+        <v>-6.978210690801177</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-7.083004567809773</v>
+        <v>-6.763624245742236</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-4.73883189103848</v>
+        <v>-4.591342719725709</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-4.834541920280152</v>
+        <v>-4.666505241680952</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-8.924997355336927</v>
+        <v>-8.532459797498504</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-9.000829608560203</v>
+        <v>-8.694598791787968</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.08931</t>
+          <t>X ≈ 0.08926</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-11.98298959835715</v>
+        <v>-9.792626728110598</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-7.192649246090348</v>
+        <v>-6.288533563814468</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-7.290104139599535</v>
+        <v>-6.293227665706048</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.686459168024705</v>
+        <v>-6.885629864514307</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.889447165576776</v>
+        <v>-2.161188004613606</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.464252852279067</v>
+        <v>1.745745601384442</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1.405324441044023</v>
+        <v>-0.2993364108482766</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.99893497634605</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.746849865613548</v>
+        <v>2.023672055427248</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.271064441378904</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6149332504295657</v>
+        <v>-2.25014442518772</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.704135808880821</v>
+        <v>-0.02672637965905977</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.171676286473684</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.671256953998444</v>
+        <v>-0.139852558542934</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4.874261759009123</v>
+        <v>2.92799305957201</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.984980945665491</v>
+        <v>-2.760702921608328</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-2.410691395712881</v>
+        <v>-4.1145833333333</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-2.51731107911143</v>
+        <v>-2.997467438494972</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.013184344271757</v>
+        <v>-1.533005211349121</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-2.123468786105576</v>
+        <v>-2.568418766290179</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-2.664235974494325</v>
+        <v>-3.135863267670914</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-5.351402813855351</v>
+        <v>-5.711025789626234</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.208076594937943</v>
+        <v>-0.4673913043478208</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-5.180012744265113</v>
+        <v>-4.379530298637277</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.1014</t>
+          <t>X ≈ 0.1013</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.6969344908154156</v>
+        <v>1.776522208059617</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-7.179668558722</v>
+        <v>-6.980022925516593</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.058452957612282</v>
+        <v>-1.851738304003923</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.694932845021484</v>
+        <v>6.066497795060251</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.070717741440006</v>
+        <v>-2.719698642911482</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.72817339265783</v>
+        <v>3.82021368649086</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.819551407819027</v>
+        <v>0.8974720997901144</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.090859595409583</v>
+        <v>-7.918086641490902</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-5.052016272471526</v>
+        <v>-7.790157731806794</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.660272411447679</v>
+        <v>-6.458549652558048</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.532365293510061</v>
+        <v>-8.313974212421861</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.476507904884393</v>
+        <v>-4.335237017956928</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.589094535834292</v>
+        <v>-5.4501291354077</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.835245441077447</v>
+        <v>2.812275101031531</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.155951271684451</v>
+        <v>2.130120719146475</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>5.758269770557078</v>
+        <v>2.691424737966088</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.467624673449031</v>
+        <v>0.4598847517729894</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.203412150520691</v>
+        <v>0.3270006466115092</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.414015813491908</v>
+        <v>0.5414628737572187</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-4.877253833861609</v>
+        <v>-5.626929404588054</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-5.417156142851056</v>
+        <v>-6.194373905968789</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-5.534945270814703</v>
+        <v>-6.269536427924074</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-5.301808949539762</v>
+        <v>-6.025901942645696</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-7.551554246241245</v>
+        <v>-8.315700511403243</v>
       </c>
     </row>
     <row r="27">
@@ -2344,489 +2344,489 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.453388367557416</v>
+        <v>-5.394478579962453</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.928565088252384</v>
+        <v>-5.640385415666323</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7067899225677579</v>
+        <v>0.5123278898495087</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.431624724267849</v>
+        <v>3.623629394744981</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.064461702700996</v>
+        <v>5.199923106497508</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.620708551339348</v>
+        <v>1.653153008791904</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.751479499566649</v>
+        <v>2.709922848411011</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.461449481651911</v>
+        <v>2.405002405002392</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>9.469241989751467</v>
+        <v>8.088486870242058</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.71421071085031</v>
+        <v>1.736879819467163</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.958723920108064</v>
+        <v>2.009114834071497</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.644518797175053</v>
+        <v>1.7325328796002</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.477917603797614</v>
+        <v>4.321344465853137</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.20940789731146</v>
+        <v>9.628665959975585</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.638142852773612</v>
+        <v>1.539104170683068</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>9.185098944677094</v>
+        <v>7.655963745058287</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>9.045272521118775</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>14.91072884700051</v>
+        <v>11.12290293187537</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>9.168141771383553</v>
+        <v>5.781809603465646</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>3.38469055164866</v>
+        <v>0.4408404929690732</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.826334107002815</v>
+        <v>1.725247843440201</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>8.069289590955542</v>
+        <v>3.501937173336714</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>10.35036496350371</v>
+        <v>5.597423510466932</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>12.27453271028038</v>
+        <v>7.28713636802933</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.1255</t>
+          <t>X ≈ 0.1254</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>40</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-4.791837212441841</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.774376088218219</v>
+        <v>6.211466436185496</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.712594662949606</v>
+        <v>7.456772334293952</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4.950135693011809</v>
+        <v>6.864370135485728</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-5.385654779535479</v>
+        <v>-3.411188004613606</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.772946019180694</v>
+        <v>-0.754254398615565</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.069647178318533</v>
+        <v>0.9506635891517519</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.37261109831914</v>
+        <v>0.6457431457431326</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-11.26924272828566</v>
+        <v>-9.226327944572752</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-9.604039592440927</v>
+        <v>-7.52237943979209</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.60813886160215</v>
+        <v>7.749855574812244</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.25513203241157</v>
+        <v>12.47327362034099</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.107217490307981</v>
+        <v>6.358381502890175</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.886138613861391</v>
+        <v>6.110147441457066</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>8.277500266775895</v>
+        <v>10.42799305957208</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.371887188718858</v>
+        <v>8.489297078391715</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>6.225593814117587</v>
+        <v>8.385416666666707</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.157881823167763</v>
+        <v>3.252532561505099</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.138603033531624</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>1.511114063565024</v>
+        <v>3.681581233709821</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.968567895599016</v>
+        <v>8.114136732329086</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>8.417474409437453</v>
+        <v>10.53897421037387</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>10.35036496350358</v>
+        <v>10.78260869565225</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.774532710280262</v>
+        <v>8.120469701362758</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.1376</t>
+          <t>X ≈ 0.1374</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-8.640847113431967</v>
+        <v>-10.68548387096774</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.024376088218226</v>
+        <v>-1.407581182862017</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-7.424180046658435</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.126596980255506</v>
+        <v>-3.254677483561885</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-8.292140385565993</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.952630049404242</v>
+        <v>0.5935207320088978</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.67441860465117</v>
+        <v>9.812409812409797</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>12.71590578656587</v>
+        <v>9.940338722093905</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>21.94299011052938</v>
+        <v>18.6680967506841</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>22.2170497526913</v>
+        <v>18.94033176528843</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>26.93830034924331</v>
+        <v>23.42565457272177</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>30.81513828238726</v>
+        <v>27.07266721717597</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>25.5940594059406</v>
+        <v>22.06252839383802</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>24.93591610836004</v>
+        <v>21.38037401195296</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>30.5303030303031</v>
+        <v>26.70358279267747</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>30.39638589332563</v>
+        <v>26.5997023809523</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>25.29154518950445</v>
+        <v>21.70491351388608</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>20.50743657042863</v>
+        <v>17.15747097912703</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>20.69428238039673</v>
+        <v>17.37205742418601</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>20.15173621243063</v>
+        <v>16.80461292280528</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>20.0758902510216</v>
+        <v>16.72945040084999</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>20.35036496350365</v>
+        <v>16.97308488612837</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>15.27453271028038</v>
+        <v>12.04904112993415</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.1496</t>
+          <t>X ≈ 0.1495</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>25</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.359152886568062</v>
+        <v>2.457373271889431</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-1.975623911781781</v>
+        <v>-1.788533563814468</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.586357039187227</v>
+        <v>4.956772334293952</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.873403019744487</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>11.53761254719721</v>
+        <v>12.08881199538639</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.72457873329459</v>
+        <v>12.24574560138448</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.95263004940424</v>
+        <v>11.45066358915176</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.325581395348827</v>
+        <v>-0.8542568542568532</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.284094213434123</v>
+        <v>-0.7263279445727449</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.057009889470685</v>
+        <v>-1.522379439792154</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.217049752691302</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.938300349243363</v>
+        <v>2.473273620341004</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>8.815138282387132</v>
+        <v>9.358381502890118</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.405940594059395</v>
+        <v>-2.889852558542927</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-4.064083891640024</v>
+        <v>-3.572006940428054</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-7.469696969696969</v>
+        <v>-7.010702921608328</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-3.603614106674435</v>
+        <v>-3.114583333333329</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>0.2915451895043191</v>
+        <v>0.7525325615050065</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-3.305717619603264</v>
+        <v>-2.818418766290172</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-3.848263787569238</v>
+        <v>-3.38586326767085</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-7.924109748978402</v>
+        <v>-7.461025789626198</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.649635036496342</v>
+        <v>-3.217391304347814</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-11.72546728971962</v>
+        <v>-11.37953029863728</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.1616</t>
+          <t>X ≈ 0.1615</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-13.640847113432</v>
+        <v>-13.54262672811063</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.12659698025551</v>
+        <v>-10.63562986451427</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.46238745280278</v>
+        <v>-0.9111880046135994</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.275421266705401</v>
+        <v>-0.7542543986155152</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.952630049404242</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.325581395348827</v>
+        <v>-1.854256854256853</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.284094213434173</v>
+        <v>-1.726327944572795</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.942990110529458</v>
+        <v>2.477620560207988</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.217049752691302</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.93830034924326</v>
+        <v>12.4732736203409</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.81513828238719</v>
+        <v>11.35838150289018</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.59405940594067</v>
+        <v>11.11014744145714</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.935916108360068</v>
+        <v>5.427993059572039</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>10.53030303030299</v>
+        <v>10.98929707839163</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>10.39638589332552</v>
+        <v>10.88541666666662</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.291545189504404</v>
+        <v>5.752532561505092</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.507436570428631</v>
+        <v>5.966994788650766</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.694282380396658</v>
+        <v>6.18158123370975</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-4.848263787569444</v>
+        <v>-4.385863267671056</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-4.924109748978395</v>
+        <v>-4.461025789626191</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.64963503649642</v>
+        <v>-4.217391304347892</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-4.725467289719553</v>
+        <v>-4.379530298637214</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.1737</t>
+          <t>X ≈ 0.1736</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>14</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>10.64486717228227</v>
+        <v>10.74308755760364</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.31009037393251</v>
+        <v>10.49718072189982</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>8.872071324901519</v>
+        <v>9.242486620008243</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>8.159117305458778</v>
+        <v>8.65008442120002</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.010293019008884</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.5935207320088978</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.284094213434074</v>
+        <v>-6.726327944572695</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.228704396243671</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>20.78847832411987</v>
+        <v>21.32128414624081</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.224014634957598</v>
+        <v>6.758987906055239</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>26.5294239966729</v>
+        <v>27.07266721717588</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>26.30834512022621</v>
+        <v>26.82443315574267</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>18.50734467978867</v>
+        <v>18.99942163100064</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>19.10173160173166</v>
+        <v>19.5607256498203</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>18.96781446475418</v>
+        <v>19.45684523809529</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>26.00583090379014</v>
+        <v>26.46681827579083</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>26.22172228471447</v>
+        <v>26.6812805029366</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>26.40856809468255</v>
+        <v>26.89586694799564</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>18.72316478385942</v>
+        <v>19.18556530375781</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>18.64731882245017</v>
+        <v>19.11040278180237</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>11.77893639207518</v>
+        <v>12.21118012422371</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.70310413885181</v>
+        <v>12.04904112993415</v>
       </c>
     </row>
     <row r="33">
@@ -2839,158 +2839,158 @@
         <v>3</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>13.02581955323505</v>
+        <v>13.12403993855641</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>12.69104275488488</v>
+        <v>12.87813310285219</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-22.08030962747944</v>
+        <v>-21.70989433237272</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.54006968641114</v>
+        <v>11.03103680215239</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.20427921386387</v>
+        <v>10.75547866205305</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.39124539996125</v>
+        <v>10.91241226805113</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>10.11733025581842</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.341085271317596</v>
+        <v>9.81240981240957</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.382572453232299</v>
+        <v>9.940338722093678</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.88371641935796</v>
+        <v>9.416522241478901</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>8.604967015910219</v>
+        <v>9.13994028700786</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.260726072607028</v>
+        <v>7.776814108123496</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>7.063052559992215</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>7.174103237095615</v>
+        <v>7.63366145531775</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>7.848247900376478</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>6.818402879096901</v>
+        <v>7.280803398995289</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>6.742556917688027</v>
+        <v>7.205640877040231</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>7.017031630170081</v>
+        <v>7.449275362318609</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>6.941199376947289</v>
+        <v>7.287136368029628</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.1978</t>
+          <t>X ≈ 0.1977</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-13.640847113432</v>
+        <v>-9.098182283666233</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-13.97562391178178</v>
+        <v>-9.344089119370025</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>0.5123278898495869</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-0.3556324490580494</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.72457873329459</v>
+        <v>22.02352337916226</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>22.95263004940424</v>
+        <v>21.22844136692954</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>32.67441860465131</v>
+        <v>32.03463203463211</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.71590578656594</v>
+        <v>21.0514498332051</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>21.94299011052945</v>
+        <v>20.2553983379857</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>22.2170497526913</v>
+        <v>20.52763335259003</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.93830034924331</v>
+        <v>20.25105139811873</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.81513828238712</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>10.59405940594074</v>
+        <v>7.776814108123808</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>19.93591610836004</v>
+        <v>18.2057708373498</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>20.53030303030303</v>
+        <v>18.76707485616946</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>20.39638589332556</v>
+        <v>18.66319444444445</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>10.29154518950438</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>10.50743657042877</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>20.6942823803968</v>
+        <v>18.95935901148761</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>20.1517362124307</v>
+        <v>18.39191451010694</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>10.07589025102174</v>
+        <v>7.205640877040544</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>-3.661835748792186</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>20.2745327102803</v>
+        <v>18.39824747914042</v>
       </c>
     </row>
   </sheetData>
@@ -3180,903 +3180,903 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1458</t>
+          <t>X &gt; -0.1457</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.4702606293593234</v>
+        <v>-0.4536524449299861</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3425089624071518</v>
+        <v>-0.2403372302840197</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.4538574380245635</v>
+        <v>-0.3256884761171648</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3757030589205925</v>
+        <v>-0.1622570834491839</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4266199416254395</v>
+        <v>-0.2438307983395589</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.2527617556738022</v>
+        <v>-0.1000211244888121</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.2325772276610749</v>
+        <v>-0.1087086347155832</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1955097963034831</v>
+        <v>-0.04146064572605468</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1966576273404286</v>
+        <v>0.01441279616798141</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1764128745452496</v>
+        <v>0.03541546240114712</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.0940879003394457</v>
+        <v>0.146831560581596</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.08678925649145697</v>
+        <v>0.1541751624524537</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.08716228528535908</v>
+        <v>0.1836559021782165</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.05148751575695343</v>
+        <v>0.2496133168279897</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.03418852542172601</v>
+        <v>0.2973905068857547</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1096491228070136</v>
+        <v>0.2232638242348983</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1360699846283779</v>
+        <v>0.1369759182259145</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.1632722850617512</v>
+        <v>0.08111247832027857</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.07921413295351698</v>
+        <v>0.2537704201515822</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1141008531362004</v>
+        <v>0.1589890815100574</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.00998885495474866</v>
+        <v>0.3227302500216211</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.06790843082382736</v>
+        <v>0.2058391717063444</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1351010239101953</v>
+        <v>0.1994489217753568</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1631171698155498</v>
+        <v>0.1145173204103358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1337</t>
+          <t>X &gt; -0.1336</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3306</v>
+        <v>3331</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.6820006129813834</v>
+        <v>-0.6505575569716626</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.580191219474095</v>
+        <v>-0.4631533073277367</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.6495912625861351</v>
+        <v>-0.5086214604554442</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.4741616224683796</v>
+        <v>-0.279019897340298</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.4924626407727146</v>
+        <v>-0.2992477061061365</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.3488268022048047</v>
+        <v>-0.1854278832378</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.381706393568976</v>
+        <v>-0.2470663989008131</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2515296193103111</v>
+        <v>-0.116880098953601</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1928566343916742</v>
+        <v>-0.001880843556612888</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2558050701935102</v>
+        <v>-0.06348556834216623</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1752370806922485</v>
+        <v>0.04650629251558769</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1352379268266191</v>
+        <v>0.1161093965898274</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1857661493282095</v>
+        <v>0.09566456692368064</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.147798253890528</v>
+        <v>0.1643228380449173</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1244157166776674</v>
+        <v>0.2184122212486557</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2059673378321563</v>
+        <v>0.1387430202904412</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2314438682198698</v>
+        <v>0.05258263431196042</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2277784819932123</v>
+        <v>0.02733028401031135</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1449343145003184</v>
+        <v>0.1996086975237361</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1818505501168701</v>
+        <v>0.1021209638447544</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1323375258588158</v>
+        <v>0.2122171162522974</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1599017683254402</v>
+        <v>0.1249328062333888</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.1999827836992552</v>
+        <v>0.1463541938514652</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2275846520910747</v>
+        <v>0.06207882775118634</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1217</t>
+          <t>X &gt; -0.1216</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3253</v>
+        <v>3278</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.7714942440790935</v>
+        <v>-0.7404455708855195</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.601578110255069</v>
+        <v>-0.4855032607841636</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.7099166321628019</v>
+        <v>-0.5721758318169847</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4895667327761331</v>
+        <v>-0.2990622477768525</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.5332920982795599</v>
+        <v>-0.3455222478650484</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5432292764883471</v>
+        <v>-0.3841087675475663</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.5641895224611986</v>
+        <v>-0.4340101589514305</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5192185932686897</v>
+        <v>-0.3879544863151452</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4603488033974088</v>
+        <v>-0.2732456487938322</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.5730796782676819</v>
+        <v>-0.383861821323066</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5263672711911198</v>
+        <v>-0.3069660599492252</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.4506736170660304</v>
+        <v>-0.2014984161332123</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.4838813254559469</v>
+        <v>-0.2044035381557379</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5337371003419662</v>
+        <v>-0.2219693468641069</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.4993996488441326</v>
+        <v>-0.1561261981097601</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5920520754927381</v>
+        <v>-0.2462476568487446</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.5545343520732118</v>
+        <v>-0.2713565449010673</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.5798877653897634</v>
+        <v>-0.3254211534766682</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.5300097156363677</v>
+        <v>-0.184391138854501</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.601388482360413</v>
+        <v>-0.3175046895077287</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.5116544509599663</v>
+        <v>-0.1661131914746292</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.5692710393009861</v>
+        <v>-0.2841965213335129</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.5838698244496356</v>
+        <v>-0.2359945370407175</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.6108039020774498</v>
+        <v>-0.3191276140735226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1096</t>
+          <t>X &gt; -0.1095</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3218</v>
+        <v>3243</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.9719177706365301</v>
+        <v>-0.9400547746507115</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.7657473685719012</v>
+        <v>-0.6491767491130886</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.9523894875185519</v>
+        <v>-0.8152864892354614</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.7220262575872027</v>
+        <v>-0.5329636064695293</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7317726860434419</v>
+        <v>-0.5463811376608163</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.743900871155347</v>
+        <v>-0.5871277503481167</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.818621882589575</v>
+        <v>-0.6904407053267718</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.7083890638707828</v>
+        <v>-0.5793258938395596</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.6803206285284702</v>
+        <v>-0.4955114927618212</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7240890973914063</v>
+        <v>-0.5374239592885601</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.7417865209082066</v>
+        <v>-0.5241001991435326</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.6932785981251115</v>
+        <v>-0.4453131692135912</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.7457164714065527</v>
+        <v>-0.467064102518556</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.731838983154816</v>
+        <v>-0.4207471174116719</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.6280752148503765</v>
+        <v>-0.2854140744993359</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.7902177384508491</v>
+        <v>-0.44410802772952</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.7509009283798704</v>
+        <v>-0.4684294871794847</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.8064696988330908</v>
+        <v>-0.5524843667805683</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.7894917572163536</v>
+        <v>-0.4431037335166437</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.770646235369874</v>
+        <v>-0.4876519045716705</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.7361867928471639</v>
+        <v>-0.3901762682870569</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.7936749663697071</v>
+        <v>-0.5087915831546965</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.811486543175441</v>
+        <v>-0.4627673832627366</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.8690347229079336</v>
+        <v>-0.5759533637004992</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.09755</t>
+          <t>X &gt; -0.0975</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3165</v>
+        <v>3190</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.9118634245988488</v>
+        <v>-0.881562302340285</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.884943020661602</v>
+        <v>-0.7686082836152153</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.9566435885591602</v>
+        <v>-0.8233584660797675</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.8361731184030816</v>
+        <v>-0.6512061885018099</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.8405281563203744</v>
+        <v>-0.6603310398270636</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.856005621088066</v>
+        <v>-0.704379086894825</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9191487060954486</v>
+        <v>-0.7962961863393545</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7396021435412266</v>
+        <v>-0.6159536727222417</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7432137102894814</v>
+        <v>-0.5640814547131612</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.8063021197317113</v>
+        <v>-0.6247514747483933</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8288910906063691</v>
+        <v>-0.6157391801050238</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.7434749104356371</v>
+        <v>-0.4998681660425603</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.8725191483432866</v>
+        <v>-0.5972573599651838</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9177516176814464</v>
+        <v>-0.6086025585429411</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.7698179811169581</v>
+        <v>-0.4285246021972853</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.9131259013074313</v>
+        <v>-0.5679261861486609</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.9340050272293041</v>
+        <v>-0.6535260921697414</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.083415390754212</v>
+        <v>-0.830696474790301</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.038304754492437</v>
+        <v>-0.691847151881241</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.022347471291496</v>
+        <v>-0.7407731808174205</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.009879949185468</v>
+        <v>-0.6636584446204878</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.00399607673338</v>
+        <v>-0.7204242858668053</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.9951814673238886</v>
+        <v>-0.6464104206123196</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.9260992012520077</v>
+        <v>-0.6334487939350879</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.0855</t>
+          <t>X &gt; -0.08545</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3082</v>
+        <v>3107</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.177078997489936</v>
+        <v>-1.146460593925291</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9794898911632259</v>
+        <v>-0.8642766127118762</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.046901098099262</v>
+        <v>-0.9191867449899362</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.033108908044042</v>
+        <v>-0.854689666241164</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.189894708526751</v>
+        <v>-1.016754223423582</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.178647073157016</v>
+        <v>-1.034254398615523</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.222910447530253</v>
+        <v>-1.10759505361392</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.063476811746511</v>
+        <v>-0.9464758744297654</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.003822983211329</v>
+        <v>-0.8326700329776244</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.080265703424111</v>
+        <v>-0.9059103593691518</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.078588373318389</v>
+        <v>-0.8719392969826316</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-0.681583705725096</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.150590783244887</v>
+        <v>-0.8802329935819202</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.158851331446208</v>
+        <v>-0.8532789300540031</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.9569988059071903</v>
+        <v>-0.6182200341378703</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.023095027949388</v>
+        <v>-0.6800448156693264</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-1.073345411303777</v>
+        <v>-0.7973065189466908</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-1.288765691324642</v>
+        <v>-1.039950573734259</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.183525528696663</v>
+        <v>-0.8389178077501924</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.269424683764001</v>
+        <v>-0.9913535139597371</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.274519865365086</v>
+        <v>-0.9292716277995368</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.234096778809786</v>
+        <v>-0.9534670890793961</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-1.232508860693557</v>
+        <v>-0.8840579710144851</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.159600969148563</v>
+        <v>-0.8664952165645445</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.07344</t>
+          <t>X &gt; -0.0734</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2983</v>
+        <v>3006</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.445238330996837</v>
+        <v>-1.44206437283438</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-1.429866840234368</v>
+        <v>-1.306733431451789</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-1.518836036711569</v>
+        <v>-1.418600058953324</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.481242334900863</v>
+        <v>-1.330994102924869</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.532340817226505</v>
+        <v>-1.356699763474154</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.493681846512146</v>
+        <v>-1.347362417170864</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.580703283929097</v>
+        <v>-1.494646321355368</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.406941848833334</v>
+        <v>-1.28396507706853</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.180024833847746</v>
+        <v>-0.9717674138928203</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.233519732647132</v>
+        <v>-1.019393374762231</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.307649846774652</v>
+        <v>-1.027110903780518</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.267041887818465</v>
+        <v>-0.9198206691676774</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.302430187886692</v>
+        <v>-0.9722957879464715</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.170056865359101</v>
+        <v>-0.8028382775731586</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1.040019720516966</v>
+        <v>-0.6351298640160223</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-1.027704325096501</v>
+        <v>-0.638609898352513</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-1.041741196975444</v>
+        <v>-0.7424903100775211</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.26081345887301</v>
+        <v>-1.008264780687625</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.125762894096063</v>
+        <v>-0.7938025535418518</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-1.254160873704379</v>
+        <v>-1.01110979619051</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-1.241431905452764</v>
+        <v>-0.9279038127024819</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.230642412294991</v>
+        <v>-0.9836321726049206</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.338643079391787</v>
+        <v>-1.019852228857296</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.26083436984031</v>
+        <v>-0.996296765703157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.06138</t>
+          <t>X &gt; -0.06135</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2854</v>
+        <v>2878</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.850788024102805</v>
+        <v>-1.882875690766191</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.645999433339497</v>
+        <v>-1.626651861981188</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.952773395595379</v>
+        <v>-1.894438738370404</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.881642213380083</v>
+        <v>-1.672320761018256</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.059324452454717</v>
+        <v>-1.825315428436319</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.818596754170592</v>
+        <v>-1.649647540285073</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.80529401886465</v>
+        <v>-1.698331559843396</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.437079653188555</v>
+        <v>-1.290998622021156</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.41096768851255</v>
+        <v>-1.178477736528372</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.467051730474807</v>
+        <v>-1.226853945515288</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.38253169132684</v>
+        <v>-1.108576069878943</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.327575435822993</v>
+        <v>-0.9838593196104597</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.348910583232353</v>
+        <v>-0.9533158244267241</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.235549532606896</v>
+        <v>-0.8197380149816667</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.000164925520508</v>
+        <v>-0.564717804711222</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.118893335874468</v>
+        <v>-0.697617187488234</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.232415225164473</v>
+        <v>-0.905628109452735</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.526636628677444</v>
+        <v>-1.246773235093343</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.360349368710857</v>
+        <v>-0.9976008378677363</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.398089907916777</v>
+        <v>-1.130116093607079</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.430342891524496</v>
+        <v>-1.107487703630653</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-1.415706387633861</v>
+        <v>-1.162414678515091</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.471001061014739</v>
+        <v>-1.141670567981024</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-1.386294199320183</v>
+        <v>-1.109898609964603</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.04933</t>
+          <t>X &gt; -0.0493</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2700</v>
+        <v>2722</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.300413767857236</v>
+        <v>-2.390047145234639</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.102001575264516</v>
+        <v>-2.141388615058986</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.234664644017471</v>
+        <v>-2.242055933739735</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.119244039079049</v>
+        <v>-2.009256238140644</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.177723973582488</v>
+        <v>-2.045303065075316</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.933993746469945</v>
+        <v>-1.831967008586197</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.949835905693298</v>
+        <v>-1.910539197793604</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.765934856320847</v>
+        <v>-1.681843061153415</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.924978191334681</v>
+        <v>-1.753850880352573</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.940576580701276</v>
+        <v>-1.758796473565958</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.793270925524695</v>
+        <v>-1.576255332275522</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.645770447216869</v>
+        <v>-1.375422670514723</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.825953565639367</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.6568631032845</v>
+        <v>-1.306305000702316</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.297011171078864</v>
+        <v>-0.923457546377314</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.530258269549265</v>
+        <v>-1.170085955027346</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.531948055695501</v>
+        <v>-1.273966366752354</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.837057914708481</v>
+        <v>-1.59047147815707</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.636740878739509</v>
+        <v>-1.302560848514055</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.798321169899133</v>
+        <v>-1.52866481843855</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.801648915205256</v>
+        <v>-1.471797898592683</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.819002421073144</v>
+        <v>-1.562421821955375</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-1.893248512986546</v>
+        <v>-1.575951186787208</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-1.836578400830732</v>
+        <v>-1.591139409585118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.03727</t>
+          <t>X &gt; -0.03725</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2479</v>
+        <v>2500</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.161230806477533</v>
+        <v>-3.283559370597644</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.636159697467505</v>
+        <v>-2.711978539891028</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.653642960812775</v>
+        <v>-2.709761371330295</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.585180413628862</v>
+        <v>-2.523099936341879</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.779441095717118</v>
+        <v>-2.697615150322193</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-2.530927874634926</v>
+        <v>-2.479494015228944</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.399934053159868</v>
+        <v>-2.414298456393581</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.335601435428991</v>
+        <v>-2.29790193818971</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.432450267965002</v>
+        <v>-2.308095237655515</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.300892761512337</v>
+        <v>-2.16237943979209</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.325486362878515</v>
+        <v>-2.170144425187758</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.060093869945781</v>
+        <v>-1.84672637965906</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.478034408375862</v>
+        <v>-2.201618497109827</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.154032197112841</v>
+        <v>-1.849852558542935</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.945112830546712</v>
+        <v>-1.612006940427989</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.211956720400629</v>
+        <v>-1.890702921608323</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.041264951404933</v>
+        <v>-1.794583333333328</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.163183180716956</v>
+        <v>-1.927467438494929</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.004640724257285</v>
+        <v>-1.673005211349164</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.996011618797787</v>
+        <v>-1.738418766290181</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.991696503121275</v>
+        <v>-1.705863267670914</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-2.044222606697062</v>
+        <v>-1.821025789626198</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-2.068989875206029</v>
+        <v>-1.777391304347816</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.879561682619986</v>
+        <v>-1.659530298637279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02522</t>
+          <t>X &gt; -0.02521</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2212</v>
+        <v>2232</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.244873959069551</v>
+        <v>-4.414329902004205</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.393708065765672</v>
+        <v>-3.453263112316932</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.196894192339862</v>
+        <v>-3.254318900053093</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.900790528642617</v>
+        <v>-2.839209282858789</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.854140030122373</v>
+        <v>-2.777794987603762</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.194703777916168</v>
+        <v>-2.14923872463433</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.404032130945694</v>
+        <v>-2.451709899428621</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.523067930357811</v>
+        <v>-2.508378718056143</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.412069067497896</v>
+        <v>-2.335646940988525</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.351708901150758</v>
+        <v>-2.280443955921129</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.681826651803078</v>
+        <v>-2.590646217302449</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.306303967303457</v>
+        <v>-2.150382293637549</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.639652540824684</v>
+        <v>-2.41401993080158</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.29522952295229</v>
+        <v>-2.035013848865511</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.162237876331538</v>
+        <v>-1.865913750463832</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.172399672399671</v>
+        <v>-1.887047007629832</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.190364895317977</v>
+        <v>-1.99092741935484</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.269320455220601</v>
+        <v>-2.079008657132931</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.937308580676401</v>
+        <v>-1.640532093069588</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.085501013105073</v>
+        <v>-1.873974321845736</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.195893584409028</v>
+        <v>-1.948587282007828</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.290866749881744</v>
+        <v>-2.113355538730147</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-2.306661697138011</v>
+        <v>-2.048932522985815</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.949698754457415</v>
+        <v>-1.763042843440154</v>
       </c>
     </row>
     <row r="17">
@@ -4086,899 +4086,899 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1908</v>
+        <v>1924</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.651733583105376</v>
+        <v>-4.839307226035913</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.768155032113732</v>
+        <v>-3.892268003648496</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.830871813952363</v>
+        <v>-3.927503742509373</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.426700822415427</v>
+        <v>-3.403023426300358</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.527322517737851</v>
+        <v>-3.495603589029194</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.481242472526617</v>
+        <v>-2.531801176162297</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.705196263648276</v>
+        <v>-2.859107720619548</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.955133944776513</v>
+        <v>-3.060078060078069</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.833287342013001</v>
+        <v>-2.880174098418905</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.109093222803956</v>
+        <v>-3.156475073887727</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.535946599575503</v>
+        <v>-3.559915734959063</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.108623529797363</v>
+        <v>-3.056871909804578</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.211987434879369</v>
+        <v>-3.080287935779268</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.620971909299485</v>
+        <v>-2.444946113636497</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.600618338404054</v>
+        <v>-2.347474715895771</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.736920351742896</v>
+        <v>-2.461846372751779</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.945650660199242</v>
+        <v>-2.773626992376997</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.916396294299183</v>
+        <v>-2.750585941613437</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.723091396115997</v>
+        <v>-2.432173610517559</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.349650673996571</v>
+        <v>-2.165612113483526</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.705406644712163</v>
+        <v>-2.473181354988995</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-3.013114984580497</v>
+        <v>-2.860194188794594</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-3.075512459230765</v>
+        <v>-2.824459911416433</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-3.069282803346461</v>
+        <v>-2.882648801755785</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.001107</t>
+          <t>X &gt; -0.001108</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1617</v>
+        <v>1629</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-5.960749433334286</v>
+        <v>-6.087077985008207</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.411176752343785</v>
+        <v>-5.535927800479094</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.230268877683187</v>
+        <v>-5.31913201886362</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.566963952732578</v>
+        <v>-4.592685079238194</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.993599203108786</v>
+        <v>-5.021071368640612</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.856560274666215</v>
+        <v>-4.00471480377206</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.922369950595758</v>
+        <v>-4.185923273954444</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.80013688277986</v>
+        <v>-4.061132237927822</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.909861084599768</v>
+        <v>-4.178752745063854</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.343074960066083</v>
+        <v>-4.66786746925802</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.158871623230077</v>
+        <v>-4.457019808858718</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.790034008470279</v>
+        <v>-3.996953512869617</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.895808827083911</v>
+        <v>-4.006873254629774</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.098248286367095</v>
+        <v>-3.150134940372276</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.571776199332263</v>
+        <v>-3.52535255123216</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-4.023543123543121</v>
+        <v>-3.946246199693036</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-4.431200313570997</v>
+        <v>-4.418450736648246</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-4.255589745800613</v>
+        <v>-4.244398070784683</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-3.943858127475117</v>
+        <v>-3.845773781023809</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-3.722744146438565</v>
+        <v>-3.692574690169856</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-3.613695886334732</v>
+        <v>-3.523370941090185</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-3.654807710683158</v>
+        <v>-3.659920817250509</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.345555926483989</v>
+        <v>-3.293511623562061</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-3.262882255706025</v>
+        <v>-3.271488555236424</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.01095</t>
+          <t>X &gt; 0.01094</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1329</v>
+        <v>1343</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.726348972168026</v>
+        <v>-6.742031490015357</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.910147721305592</v>
+        <v>-5.946271659052563</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.855191732220071</v>
+        <v>-4.745608618087005</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.891127531671309</v>
+        <v>-3.885816014923805</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-5.08281996585275</v>
+        <v>-5.054896120771467</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.738107833869591</v>
+        <v>-3.706599893775611</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.470820286667454</v>
+        <v>-4.650602233633052</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-4.375618736648313</v>
+        <v>-4.508761694167511</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4.444034422701691</v>
+        <v>-4.604213275920479</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-5.027840106374136</v>
+        <v>-5.325804607327463</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.753780464212213</v>
+        <v>-4.979109428910768</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.169484081894417</v>
+        <v>-4.362169417633744</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.829056474167125</v>
+        <v>-4.062318422649653</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.809238944883994</v>
+        <v>-3.119189863085005</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.317457204983285</v>
+        <v>-3.652423917345338</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-3.847508064149736</v>
+        <v>-4.133562191898719</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.506162832311624</v>
+        <v>-4.758663750310255</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.086265904948391</v>
+        <v>-4.221406381160605</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-3.345636892839664</v>
+        <v>-3.485723007328311</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.191689112476496</v>
+        <v>-3.271136562269326</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-3.16658210588762</v>
+        <v>-3.242899753151185</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.19984228090928</v>
+        <v>-3.169141947481748</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.183469622962519</v>
+        <v>-3.148887953640454</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-3.216814167071014</v>
+        <v>-3.236566784117556</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.023</t>
+          <t>X &gt; 0.02299</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1095</v>
+        <v>1110</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-7.257483641460901</v>
+        <v>-7.097982263664157</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-6.554809432143777</v>
+        <v>-6.443799090367122</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.504222670957702</v>
+        <v>-5.358259168856364</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-3.90538211171517</v>
+        <v>-3.743737972622377</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.738249521768303</v>
+        <v>-4.559836653262259</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-3.68686540839478</v>
+        <v>-3.502002146363274</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.229188132413938</v>
+        <v>-4.297084158595993</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.143763213530647</v>
+        <v>-4.241644241644252</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4.28409421343413</v>
+        <v>-4.38398560223041</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.511555344016081</v>
+        <v>-4.639496556909201</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.237495701854158</v>
+        <v>-4.367261542304867</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.607154196211241</v>
+        <v>-3.742942595875277</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.769939060651936</v>
+        <v>-2.965942821434155</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.573518007538453</v>
+        <v>-1.862825531515909</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.958437261403162</v>
+        <v>-2.274709643130691</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.001573108130479</v>
+        <v>-2.25394616485157</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.773013013778268</v>
+        <v>-2.988457207207205</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.149256267690525</v>
+        <v>-2.220440411467912</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.204767436857267</v>
+        <v>-1.285257463601418</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.473295033082323</v>
+        <v>-1.521121468992881</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.560467794855271</v>
+        <v>-1.638115519923169</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.674337643235468</v>
+        <v>-1.62318795178836</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.620437956204377</v>
+        <v>-1.649823736780256</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.825923910724192</v>
+        <v>-1.902052821159806</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.03506</t>
+          <t>X &gt; 0.03504</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>868</v>
+        <v>884</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-7.907058717527534</v>
+        <v>-7.728147090101551</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-6.823004321804561</v>
+        <v>-6.729710034402707</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.128580247015741</v>
+        <v>-4.930105493760344</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.359473692584274</v>
+        <v>-2.128842534197531</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.40524459565993</v>
+        <v>-2.291278502351162</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.8978468959960253</v>
+        <v>-0.6637566610589545</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.7209094694961</v>
+        <v>-1.79820518912878</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.42638322810943</v>
+        <v>-1.53751477280889</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.957633732334472</v>
+        <v>-2.088318894799002</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.928716647775317</v>
+        <v>-2.092515186398423</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.769204542841344</v>
+        <v>-1.933402343739786</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.5588359623260004</v>
+        <v>-0.739396062916974</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4481658053229651</v>
+        <v>0.1819109146548854</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.32884700639984</v>
+        <v>0.9517764007330811</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.5558931462475272</v>
+        <v>0.156499846902328</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.2317955676164587</v>
+        <v>-0.07405133789792018</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5909849447915505</v>
+        <v>-0.856664781297134</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.351393960897461</v>
+        <v>-0.4239380267302266</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.6681713580291557</v>
+        <v>0.58237940403545</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.5105854802819181</v>
+        <v>0.4575993332573347</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.3124710000311524</v>
+        <v>0.2295213477136997</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.4207178372284943</v>
+        <v>0.3806031696498167</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.879709037151521</v>
+        <v>0.7373598268738988</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1823668116628596</v>
+        <v>0.009609972855926685</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.04712</t>
+          <t>X &gt; 0.04709</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.598354195584939</v>
+        <v>-8.394947403216086</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-7.308957245115117</v>
+        <v>-7.234384478019813</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.987506597176406</v>
+        <v>-4.832257201571032</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5078203088472577</v>
+        <v>-0.3613682611387432</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.761532751948081</v>
+        <v>-1.762102209958194</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.7832672010848611</v>
+        <v>-0.620639771330012</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.190227093452897</v>
+        <v>-1.415721783562731</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.468438538205973</v>
+        <v>-0.7361133943412455</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.426951356291269</v>
+        <v>-1.733360293377253</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.342724175184905</v>
+        <v>-2.670058764686608</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.78295024730869</v>
+        <v>-2.116529797902245</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2045567936138326</v>
+        <v>-0.5647010632033513</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.243709710958619</v>
+        <v>-0.1324764436639754</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8797736916548828</v>
+        <v>0.4631713514430018</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>-0.5002769826220828</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.1839826839826841</v>
+        <v>-0.5015608681624784</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.175042678103011</v>
+        <v>-1.449323136427573</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.279883381924193</v>
+        <v>-1.300913289409145</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.06399200099986757</v>
+        <v>-0.1019222296332742</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.02000333388898667</v>
+        <v>-0.02798276066430105</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.2945933552878373</v>
+        <v>0.2484545944950511</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.01866564444076602</v>
+        <v>0.03264509644974822</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.6655512099219933</v>
+        <v>0.5575735339081547</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.2458383056892757</v>
+        <v>0.1141405874386621</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.05917</t>
+          <t>X &gt; 0.05914</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-9.93455340713826</v>
+        <v>-9.716539771588863</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.565816556265148</v>
+        <v>-7.353750955118819</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-4.711888574847855</v>
+        <v>-4.434532013532127</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4148219363187877</v>
+        <v>-0.1573689949490529</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.237035340126724</v>
+        <v>-2.172057569830997</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.01439833901581267</v>
+        <v>0.07183255790621246</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1569105866381548</v>
+        <v>-0.3754233673699758</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4351220313912307</v>
+        <v>-0.6803438107785951</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.63038396608431</v>
+        <v>-1.94371924892058</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.226621196891116</v>
+        <v>-2.565857700661653</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.659275335647919</v>
+        <v>-2.989274859970358</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.347918732028774</v>
+        <v>-1.700639423137318</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.527617901358397</v>
+        <v>-0.9024880623272225</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.1346954483434288</v>
+        <v>-0.28115690636902</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.3467694040074463</v>
+        <v>-0.7893982447758177</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.4590962629831878</v>
+        <v>-0.923746399869195</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.9463702904200275</v>
+        <v>-1.375452898550733</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.8745325490115263</v>
+        <v>-0.986597873277546</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.1286058323981507</v>
+        <v>-0.2503965156969912</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.825152248578533</v>
+        <v>-0.9053752880293047</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.4843061903961541</v>
+        <v>-0.6032545720187414</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.2780920498633606</v>
+        <v>-0.5045040504957683</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.8113578713050629</v>
+        <v>0.6086956521739211</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.4876765823940516</v>
+        <v>0.09873057092792692</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.07123</t>
+          <t>X &gt; 0.07118</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.742842678842166</v>
+        <v>-7.709293394777269</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-5.975623911781781</v>
+        <v>-5.762217774340783</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.075112893997627</v>
+        <v>-2.850245209565699</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1234030197444866</v>
+        <v>0.2854227670646807</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.205116759290483</v>
+        <v>-1.086626601104832</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.02054285885513</v>
+        <v>1.921184197875704</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.37959634153907</v>
+        <v>0.6875056944149094</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.775542200156785</v>
+        <v>1.040479987848407</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4687147753299143</v>
+        <v>-0.3666788217657313</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1452373015406181</v>
+        <v>-0.7241338257570007</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.1945778425789442</v>
+        <v>-0.671197056766708</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.3877385514905</v>
+        <v>1.464501690516386</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.511767495870338</v>
+        <v>2.542592029205963</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.189565023918128</v>
+        <v>3.390849195843039</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.857264422966779</v>
+        <v>2.050800077115866</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.676370446033367</v>
+        <v>2.83140234154957</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.86829600568511</v>
+        <v>2.069627192982452</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.538736200740331</v>
+        <v>2.156041333434892</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.754627581664657</v>
+        <v>2.370503560580666</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.042596987138303</v>
+        <v>1.707897023183506</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.174208122543064</v>
+        <v>1.798347258644874</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.562376737508089</v>
+        <v>1.065289999847487</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.201380764858051</v>
+        <v>1.747520976353933</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.448347608700239</v>
+        <v>0.9274872452223661</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.08328</t>
+          <t>X &gt; 0.08323</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-7.061899745010912</v>
+        <v>-6.545237694168037</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.426811246874131</v>
+        <v>-4.963468289663034</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.974489521659329</v>
+        <v>-1.518423488160359</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.04194089559943137</v>
+        <v>0.5001403704726783</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.151369160953827</v>
+        <v>0.4856788361174651</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.406276346026694</v>
+        <v>3.253578499556795</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.059013028127644</v>
+        <v>2.719593093068205</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.046759030183075</v>
+        <v>2.675769255403715</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.556331318480765</v>
+        <v>2.020408347855451</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.847245429678317</v>
+        <v>2.268743275612607</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.12130507184024</v>
+        <v>2.540978290216941</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.502130136477348</v>
+        <v>4.875362393186904</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.974712750472285</v>
+        <v>5.327049910200877</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.349378554876765</v>
+        <v>6.645395483232527</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>5.361448023253665</v>
+        <v>4.657758072626841</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>5.423920051579628</v>
+        <v>4.696868879958245</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>5.024045467793641</v>
+        <v>4.331891862489115</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.653247317163945</v>
+        <v>4.199007757327514</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>4.603181251279771</v>
+        <v>4.152373378729173</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.726197274013757</v>
+        <v>3.322573400811649</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>3.449608552856233</v>
+        <v>3.016225505175044</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.742556917688269</v>
+        <v>2.157773165987372</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>4.254108279011675</v>
+        <v>3.706890679986387</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.376136988355242</v>
+        <v>2.761461868464544</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.09534</t>
+          <t>X &gt; 0.09528</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-5.786061634884113</v>
+        <v>-5.687841249562744</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.96900139522549</v>
+        <v>-4.613616072065291</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.5963672133044611</v>
+        <v>-0.2577491178512687</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.680711989844156</v>
+        <v>2.450178716343821</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>1.184521566343491</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.391245399961264</v>
+        <v>3.65168619544388</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3.487747106260436</v>
+        <v>3.516670189811833</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.540639340437124</v>
+        <v>2.551683739802542</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.24767836181671</v>
+        <v>2.019546642885992</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.478107167385573</v>
+        <v>2.213594157567648</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.08995945168796</v>
+        <v>3.805961185373292</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.486795332520899</v>
+        <v>6.169643257304649</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.701425907805252</v>
+        <v>6.374883153055187</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.821484155104471</v>
+        <v>8.436880114724396</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5.487755573242985</v>
+        <v>5.114461706436693</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>7.08548697679133</v>
+        <v>6.665864735157342</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>6.951569839813857</v>
+        <v>6.561984323432334</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>6.512280975457557</v>
+        <v>6.099067214970418</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>6.059276035311647</v>
+        <v>5.653463435515519</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5.242777363674321</v>
+        <v>4.877950870673523</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>5.034679356243409</v>
+        <v>4.640539372593111</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.84099092216254</v>
+        <v>4.235343847337504</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>5.67023028336898</v>
+        <v>4.809011335916203</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.594398030145705</v>
+        <v>4.646872341626739</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.1074</t>
+          <t>X &gt; 0.1073</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.974180446765303</v>
+        <v>-7.058251728110598</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.563859205899426</v>
+        <v>-4.179158563814468</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5116821764990434</v>
+        <v>0.03489733429395159</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.128304980528796</v>
+        <v>1.786245135485728</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.184671370726619</v>
+        <v>1.901311995386394</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.779696843530807</v>
+        <v>3.620745601384478</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.426938349799492</v>
+        <v>3.997538589151759</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.939240739038517</v>
+        <v>4.47386814574314</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.585471003957181</v>
+        <v>3.820547055427248</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>3.603069161912778</v>
+        <v>3.80574556020791</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.853413389054936</v>
+        <v>6.031105574812244</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.946205487583228</v>
+        <v>8.098273620340947</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.404071088711298</v>
+        <v>8.545881502890175</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.368762963252848</v>
+        <v>9.469522441457066</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.548564329703915</v>
+        <v>5.66236805957201</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.328722002635047</v>
+        <v>7.395547078391672</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>7.590061782653621</v>
+        <v>7.682291666666664</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>7.485221078832438</v>
+        <v>7.158782561505063</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>6.910598625764671</v>
+        <v>6.591994788650837</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.097444435732697</v>
+        <v>6.806581233709821</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>6.950155184762714</v>
+        <v>6.629761732329086</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>6.163974210373802</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>7.681042254340298</v>
+        <v>6.798233695652179</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>8.003616375619011</v>
+        <v>7.026719701362715</v>
       </c>
     </row>
     <row r="28">
@@ -4988,653 +4988,653 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.601243153035924</v>
+        <v>-7.503022767714555</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4631479113078214</v>
+        <v>-0.09273261620109707</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8040960890514128</v>
+        <v>1.295063204792655</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.4683056165041393</v>
+        <v>1.01950506469332</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.625568832304488</v>
+        <v>4.146735700394373</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>3.843719158315132</v>
+        <v>4.341752698062649</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.555606723463043</v>
+        <v>5.026931264555017</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.121846380625271</v>
+        <v>2.67961264948665</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.824178229341257</v>
+        <v>4.358808679019788</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.573485396255656</v>
+        <v>7.106291218376597</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.265033022510636</v>
+        <v>9.800006293608277</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.131969965555506</v>
+        <v>9.675213186058492</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.910891089108915</v>
+        <v>9.426979124625383</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.272549771726382</v>
+        <v>6.764626722938353</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.866936693669373</v>
+        <v>7.325930741758015</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.228069061642387</v>
+        <v>7.717099834983493</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>5.638079842969731</v>
+        <v>6.099067214970418</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.349020728844543</v>
+        <v>6.808578947066678</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>8.021015053664058</v>
+        <v>8.508313906977151</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>7.478468885698028</v>
+        <v>7.940869405596416</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>6.41252391438794</v>
+        <v>6.875607873740144</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.119242359018521</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>6.957103364729058</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.1315</t>
+          <t>X &gt; 0.1314</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-8.299232206599669</v>
+        <v>-8.48089833304887</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-6.257669366283601</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.997493892489793</v>
+        <v>-1.956807912619624</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2259758622430965</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.922705714899074</v>
+        <v>2.11350335341109</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.215261963108262</v>
+        <v>5.356856712495592</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5.064431291640261</v>
+        <v>5.179058650880151</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>6.028455871731907</v>
+        <v>6.108706108706102</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.448825041224254</v>
+        <v>5.619351067772925</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.160381414877207</v>
+        <v>7.29243537502272</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.813323044616773</v>
+        <v>6.947386439009776</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.019045690858221</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.38035567369153</v>
+        <v>10.49418397202597</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.15927679724494</v>
+        <v>10.24594991059286</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.774425425130225</v>
+        <v>5.860091825004112</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6.989930359495588</v>
+        <v>7.038679794441066</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>7.477131234940472</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.751172518696933</v>
+        <v>6.801915277554457</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>8.209299924465959</v>
+        <v>8.250945405934786</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>9.638381759278715</v>
+        <v>9.70009975222834</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>7.853599566467956</v>
+        <v>7.898087349613036</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>5.914399567791783</v>
+        <v>5.971072975805903</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>6.188874280273836</v>
+        <v>6.214707461084281</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.734160039472933</v>
+        <v>6.669852417412109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.1436</t>
+          <t>X &gt; 0.1435</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>141</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-8.25077619144615</v>
+        <v>-8.152555806124781</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.167113273483906</v>
+        <v>-6.980022925516593</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.512933740954615</v>
+        <v>-1.142518445847891</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.09822818592927263</v>
+        <v>0.3927389298119692</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.112080632303595</v>
+        <v>3.663280080492775</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.426706392869058</v>
+        <v>5.947873260958943</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.363977567134739</v>
+        <v>5.862011106882257</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>5.085766122381663</v>
+        <v>5.557090663473637</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.418033446140335</v>
+        <v>4.975799715001713</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.06355748641591</v>
+        <v>5.59818793609444</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.6283972704218</v>
+        <v>5.161203092542742</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.477307441441894</v>
+        <v>7.012280712539535</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.969945930763288</v>
+        <v>8.486033966279756</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>3.05648348424657</v>
+        <v>3.54856043545854</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>3.650870406189561</v>
+        <v>4.109864454278203</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.226173127368114</v>
+        <v>4.71520390070922</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.121332423546932</v>
+        <v>4.582319795547619</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>6.464883378939341</v>
+        <v>6.924441597161476</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>8.070168905219418</v>
+        <v>8.557467758532511</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.109183020941337</v>
+        <v>6.571583540839725</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.905677485064153</v>
+        <v>4.368761444416357</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>4.180152197546207</v>
+        <v>4.612395929694735</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>5.522759660634996</v>
+        <v>5.868696651717336</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.1556</t>
+          <t>X &gt; 0.1555</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>116</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-10.5373988375699</v>
+        <v>-10.43917845224853</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-8.285968739367988</v>
+        <v>-8.098878391400675</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.82743606426105</v>
+        <v>-2.457020769154326</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.9541831871520685</v>
+        <v>-0.4632160714108267</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.296233236852387</v>
+        <v>1.847432685041568</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.069406319501489</v>
+        <v>4.590573187591374</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>4.159526601128377</v>
+        <v>4.657560140875894</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.467522052927031</v>
+        <v>6.938846594019004</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.646940269324489</v>
+        <v>6.204706538185867</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.59816252432249</v>
+        <v>7.132792974001021</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.148084235449922</v>
+        <v>5.680890057570863</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>7.455541728553655</v>
+        <v>7.990514999651296</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.194448627214776</v>
+        <v>7.737691847717763</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.42164561283715</v>
+        <v>10.93773364835362</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.59108852215315</v>
+        <v>5.083165473365121</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.04754440961338</v>
+        <v>6.506538457702021</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.913627272635907</v>
+        <v>6.402658045977013</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>4.946717603297486</v>
+        <v>5.407704975298174</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.748815880773527</v>
+        <v>8.208374098995662</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>10.52186858729328</v>
+        <v>11.00916744060638</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>8.255184488292763</v>
+        <v>8.717585008191151</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.455200595849185</v>
+        <v>6.918284555201389</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.867606342814</v>
+        <v>6.299850074962528</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.240049951659692</v>
+        <v>9.585986942742032</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.1677</t>
+          <t>X &gt; 0.1676</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>96</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-9.890847113431967</v>
+        <v>-9.792626728110598</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-9.18395724511511</v>
+        <v>-8.996866897147797</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.288642960812773</v>
+        <v>-1.918227665706048</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.165069686411151</v>
+        <v>1.656036802152393</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.870945880530549</v>
+        <v>2.422145328719729</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>5.182912066627928</v>
+        <v>5.704078934717813</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.410963382737577</v>
+        <v>4.908996922485095</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.299418604651166</v>
+        <v>8.77074314574314</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.299239119899212</v>
+        <v>7.857005388760591</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.567990110529379</v>
+        <v>8.10262056020791</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.758716419357967</v>
+        <v>6.291522241478908</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.521633682576649</v>
+        <v>7.05660695367429</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>6.440138282387188</v>
+        <v>6.983381502890175</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.38572607260726</v>
+        <v>10.90181410812372</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.519249441693383</v>
+        <v>5.011326392905353</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>5.113636363636374</v>
+        <v>5.572630411725015</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.979719226658901</v>
+        <v>5.468750000000007</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>4.874878522837719</v>
+        <v>5.335865894838406</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>8.215769903762045</v>
+        <v>8.67532812198418</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>11.52761571373007</v>
+        <v>12.01491456704316</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>10.98506954576404</v>
+        <v>11.44747006566243</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>8.825890251021598</v>
+        <v>9.288974210373802</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>8.058698296836994</v>
+        <v>8.490942028985522</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>12.14953271028038</v>
+        <v>12.49546970136272</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.1797</t>
+          <t>X &gt; 0.1796</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>82</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-13.39694467440757</v>
+        <v>-13.2987242890862</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-12.51220927763544</v>
+        <v>-12.32511892966813</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.194130765690822</v>
+        <v>-3.823715470584098</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.02903600464575362</v>
+        <v>0.4619311110954882</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>2.074197913050867</v>
+        <v>2.625397361240047</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>4.700188489392154</v>
+        <v>5.221355357482039</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.147752000623754</v>
+        <v>5.645785540371271</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.747589336358487</v>
+        <v>10.21891387745046</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.789076518273191</v>
+        <v>10.34684278713457</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.79664864711475</v>
+        <v>8.331279096793281</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.192659508788864</v>
+        <v>3.725465330909806</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.572446690706727</v>
+        <v>7.107419961804368</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.010260233606701</v>
+        <v>3.553503454109688</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>7.66723013764792</v>
+        <v>8.183318173164388</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2.131038059579552</v>
+        <v>2.623115010791523</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>2.725424981522544</v>
+        <v>3.184419029611185</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>2.59150784454507</v>
+        <v>3.080538617886177</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>1.267154945601938</v>
+        <v>1.728142317602625</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.141582911892122</v>
+        <v>5.601141130114257</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>8.986965307226001</v>
+        <v>9.474264160539093</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>9.663931334381907</v>
+        <v>10.12633185428029</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>7.149060982728919</v>
+        <v>7.612144942081123</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>7.423535695210973</v>
+        <v>7.855779427359501</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>12.2257522224755</v>
+        <v>12.57168921355784</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.1918</t>
+          <t>X &gt; 0.1917</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>79</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.40034078431805</v>
+        <v>-14.30212039899668</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-13.46929479785773</v>
+        <v>-13.28220444989041</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.514908783597583</v>
+        <v>-3.144493488490859</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4303944486099454</v>
+        <v>0.0605726671312965</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.765460648463034</v>
+        <v>2.316660096652214</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.484072404180672</v>
+        <v>5.005239272270558</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.977946505100441</v>
+        <v>5.475980044847958</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9.763026199587884</v>
+        <v>10.23435074067986</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.804513381502588</v>
+        <v>10.36227965036397</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.765774920655957</v>
+        <v>8.300405370334488</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.976543423577382</v>
+        <v>3.509349245698324</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.495262374559758</v>
+        <v>7.030235645657399</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.840454738083388</v>
+        <v>3.383697958586374</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.682667000877316</v>
+        <v>8.198755036393784</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>1.961232564056239</v>
+        <v>2.453309515268209</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>2.55561948599923</v>
+        <v>3.014613534087871</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.421702349021757</v>
+        <v>2.910733122362863</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>1.051038860390456</v>
+        <v>1.512026232391143</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>5.064398595745153</v>
+        <v>5.523956813967288</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>9.048712760143559</v>
+        <v>9.536011613456651</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>9.771989376987669</v>
+        <v>10.23438989688606</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>7.164497845958316</v>
+        <v>7.62758180531052</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>7.438972558440369</v>
+        <v>7.871216290588897</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>12.42643144445758</v>
+        <v>12.77236843553992</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.2038</t>
+          <t>X &gt; 0.2037</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-14.51041233082327</v>
+        <v>-14.97119815668202</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-13.39591376685424</v>
+        <v>-13.78853356381447</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-3.239729917334515</v>
+        <v>-3.614656237134625</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.395142150179268</v>
+        <v>0.0786558497714438</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.957902402269674</v>
+        <v>2.66024056681497</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.144868588367054</v>
+        <v>2.817174172813054</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.372919904476703</v>
+        <v>3.450663589151759</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.442534546680143</v>
+        <v>7.431457431457432</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.933297090913698</v>
+        <v>8.987957769712956</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.711106052558357</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1880642454449273</v>
+        <v>1.321284146240821</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4.257140928953447</v>
+        <v>5.330416477483801</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.6847034997785</v>
+        <v>2.786952931461606</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>8.253004584314205</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.643794036567499</v>
+        <v>0.4279930595720103</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.04940711462450764</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1833242516019808</v>
+        <v>0.8854166666666643</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2881649554231629</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>4.275552512457679</v>
+        <v>5.252709074365129</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>8.32443837656696</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.267678241416213</v>
+        <v>9.185565303757656</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.68183135323094</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>8.466306992489166</v>
+        <v>9.354037267080749</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>11.28902546390356</v>
+        <v>12.04904112993415</v>
       </c>
     </row>
   </sheetData>
@@ -5824,903 +5824,903 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1458</t>
+          <t>X &lt; -0.1457</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15.92437027787238</v>
+        <v>16.4573732718894</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.89394130560953</v>
+        <v>7.640037864756962</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.25302370585388</v>
+        <v>12.09962947715109</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.192243599454628</v>
+        <v>5.792941564057159</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>9.803097709672102</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2463178637293737</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>0.5935207320088978</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.253117627232889</v>
+        <v>-2.568542568542576</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.211630445318185</v>
+        <v>-2.440613658858467</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.984546121354676</v>
+        <v>-3.236665154077805</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.058312566149276</v>
+        <v>-7.250144425187756</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-7.337061969597272</v>
+        <v>-6.098154951087629</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.010948674134553</v>
+        <v>-5.784475639966963</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.68130291289998</v>
+        <v>-7.46128112997151</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-9.339446210480538</v>
+        <v>-8.143435511856566</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-5.84650856389986</v>
+        <v>-4.724988635894043</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-4.531150338558497</v>
+        <v>-3.40029761904762</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-3.186715680060843</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-7.31865038609304</v>
+        <v>-6.175862354206302</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.682529213806163</v>
+        <v>-4.532704480575894</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-10.57290146872872</v>
+        <v>-9.385863267670914</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-7.750196705500144</v>
+        <v>-6.603882932483337</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-4.577171268380404</v>
+        <v>-3.503105590062106</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.203728159284843</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1337</t>
+          <t>X &lt; -0.1336</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>99</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>18.07632460373974</v>
+        <v>18.17454498906111</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.69104275488488</v>
+        <v>12.87813310285219</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>14.28332673615693</v>
+        <v>14.65374203126365</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.50976665610812</v>
+        <v>8.000733771849362</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.184077193661864</v>
+        <v>8.735276641851044</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.320538329254184</v>
+        <v>3.841705197344069</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.568791665565854</v>
+        <v>5.066825205313371</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.2501761804087437</v>
+        <v>0.7215007215007176</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.728538657878573</v>
+        <v>-1.170772389017195</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.5288486963879677</v>
+        <v>1.063479146066499</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-1.694588869632199</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-3.516245105302154</v>
+        <v>-2.981271834204513</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.609104141855234</v>
+        <v>-1.065860921352247</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.840284028402841</v>
+        <v>-2.324195992886374</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-3.4984273259834</v>
+        <v>-3.006350374771429</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.8838383838383805</v>
+        <v>-0.4248443357497393</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.00765451071485046</v>
+        <v>0.4813762626262559</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1124952145360325</v>
+        <v>0.3484921574646549</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.926906863914738</v>
+        <v>-2.467348645692603</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.729960043845693</v>
+        <v>-1.242661190532601</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-3.282607221912741</v>
+        <v>-2.820206702014353</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-2.348352173220825</v>
+        <v>-1.885268213868621</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.063776450637761</v>
+        <v>-0.6315327184892325</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1295076937600328</v>
+        <v>0.216429297322307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1217</t>
+          <t>X &lt; -0.1216</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>152</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13.46441604446277</v>
+        <v>13.56263642978414</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8.524376088218219</v>
+        <v>8.711466436185532</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.37583072339776</v>
+        <v>10.74624601850449</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.057613546060274</v>
+        <v>5.548580661801516</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.037612547197213</v>
+        <v>6.588811995386394</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.224578733294592</v>
+        <v>6.745745601384478</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.768419523088454</v>
+        <v>7.266453062835971</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>5.832313341493268</v>
+        <v>6.303637882585242</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.558011049723767</v>
+        <v>5.115777318585145</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.074569057897804</v>
+        <v>7.609199507576335</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.032839226375515</v>
+        <v>6.565645048496457</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.438300349243306</v>
+        <v>4.973273620340947</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>5.288822492913503</v>
+        <v>5.83206571341649</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.383533090151133</v>
+        <v>6.899621125667601</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>5.725389792570574</v>
+        <v>6.217466743782545</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.635566188197771</v>
+        <v>8.094560236286412</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>6.843754314378188</v>
+        <v>7.332785087719294</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>7.396808347399116</v>
+        <v>7.857795719399803</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>6.296910254639236</v>
+        <v>6.756468472861371</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>7.799545538291468</v>
+        <v>8.286844391604561</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.941209896641233</v>
+        <v>6.403610416539621</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>7.181153408916337</v>
+        <v>7.644237368268541</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>7.455628121398391</v>
+        <v>7.887871853546919</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.037690605017225</v>
+        <v>8.383627596099565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1096</t>
+          <t>X &lt; -0.1095</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>187</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.27359138924184</v>
+        <v>14.37181177456321</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.660739724581852</v>
+        <v>9.847830072549165</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.50079554186103</v>
+        <v>12.87121083696776</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.044526014396894</v>
+        <v>8.535493130138136</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.243494900138387</v>
+        <v>8.794694348327567</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>8.430461086235766</v>
+        <v>8.951627954325652</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9.797549835500497</v>
+        <v>10.29558337524801</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.915060315881121</v>
+        <v>8.386384856973095</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.421788139507044</v>
+        <v>7.979554408368422</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>8.253150538336868</v>
+        <v>8.787780988015399</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>8.527210180498791</v>
+        <v>9.060016002619733</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>7.713701418762014</v>
+        <v>8.248674689859655</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.729576785060992</v>
+        <v>9.272820005563979</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>8.508497908614402</v>
+        <v>9.02458594413087</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6.780835894456295</v>
+        <v>7.272912845668266</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>9.514260249554368</v>
+        <v>9.97325429764301</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>8.845583754288114</v>
+        <v>9.334614527629221</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.81026176704448</v>
+        <v>10.27124913904517</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>9.491393789680039</v>
+        <v>9.950952007902174</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>9.143480241359285</v>
+        <v>9.630779094672377</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>8.600934073393255</v>
+        <v>9.063334593291643</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>9.594606828561702</v>
+        <v>10.05769078791391</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>9.869081541043755</v>
+        <v>10.30132527319228</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>10.86276800439803</v>
+        <v>11.20870499548037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.09755</t>
+          <t>X &lt; -0.0975</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>240</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10.10915288656803</v>
+        <v>10.2073732718894</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8.941042754884883</v>
+        <v>9.128133102852196</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.586357039187227</v>
+        <v>9.956772334293952</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.62340301974448</v>
+        <v>8.114370135485721</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.704279213863884</v>
+        <v>8.255478662053065</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.891245399961264</v>
+        <v>8.412412268051149</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.78596338273757</v>
+        <v>9.283996922485088</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.424418604651159</v>
+        <v>6.895743145743133</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.465905786565862</v>
+        <v>7.023672055427241</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>7.359656777196051</v>
+        <v>7.894287226874582</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.633716419357974</v>
+        <v>8.166522241478916</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.521633682576649</v>
+        <v>7.05660695367429</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>8.315138282387188</v>
+        <v>8.858381502890175</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>8.927392739273927</v>
+        <v>9.443480774790395</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>7.019249441693368</v>
+        <v>7.511326392905339</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>8.86363636363636</v>
+        <v>9.322630411725001</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>9.146385893325558</v>
+        <v>9.635416666666664</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>11.12487852283772</v>
+        <v>11.58586589483841</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>10.5074365704287</v>
+        <v>10.96699478865084</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>10.27761571373006</v>
+        <v>10.76491456704315</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.1517362124307</v>
+        <v>10.61413673232909</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>10.0758902510216</v>
+        <v>10.5389742103738</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>9.93369829683698</v>
+        <v>10.36594202898551</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>9.024532710280376</v>
+        <v>9.370469701362715</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.0855</t>
+          <t>X &lt; -0.08545</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>323</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.82664514662995</v>
+        <v>9.924865531951319</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.324685685741436</v>
+        <v>7.511776033708749</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.74425177602933</v>
+        <v>8.114667071136054</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.340895279806404</v>
+        <v>7.831862395547645</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.862689946578016</v>
+        <v>9.413889394767196</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>8.740058609455573</v>
+        <v>9.261225477545459</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.206500018444494</v>
+        <v>9.704533558192011</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>7.689898480812147</v>
+        <v>8.161223021904121</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.112190616287236</v>
+        <v>7.669956885148615</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.88726255634981</v>
+        <v>8.421893006028341</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>7.851724675291926</v>
+        <v>8.384530497412868</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.334585178964673</v>
+        <v>6.869558450062314</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.616995867526505</v>
+        <v>9.160239088029492</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>8.705514514299736</v>
+        <v>9.221602549816204</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6.808981123839907</v>
+        <v>7.301058075051877</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>7.403368045782898</v>
+        <v>7.862362093871539</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>7.888645955245067</v>
+        <v>8.377676728586174</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>9.950987913962592</v>
+        <v>10.41197528596328</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>8.928489202007647</v>
+        <v>9.388047420229782</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>9.734530058415302</v>
+        <v>10.22182891172839</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>9.811178936888915</v>
+        <v>10.2735794567873</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>9.425735452259993</v>
+        <v>9.888819411612197</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>9.390612641522225</v>
+        <v>9.822856373670753</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>8.695585341859321</v>
+        <v>9.041522332941661</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.07344</t>
+          <t>X &lt; -0.0734</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.155361417373719</v>
+        <v>9.248070946308005</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8.583617794379357</v>
+        <v>8.537047831534373</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.041333342504764</v>
+        <v>9.375376985456747</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.565346147706563</v>
+        <v>9.015532926183397</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>8.940456149092952</v>
+        <v>9.205091065153837</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8.653488685901237</v>
+        <v>8.896908392082146</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.303340949878169</v>
+        <v>9.729733356593613</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>8.077262206546905</v>
+        <v>8.262022215510584</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.459981615949751</v>
+        <v>6.529486008915619</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.871900063136025</v>
+        <v>6.896225211370705</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.382926529942488</v>
+        <v>7.168460225975039</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>7.104177126494491</v>
+        <v>6.659320131968855</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>7.40281600750567</v>
+        <v>7.32574747025614</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.470836657125432</v>
+        <v>6.378212709522337</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>5.575726534900319</v>
+        <v>5.462958094537036</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>5.459212982909676</v>
+        <v>5.475278386802884</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.562262670576743</v>
+        <v>5.756611046057778</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>7.116189739267412</v>
+        <v>7.419199228171721</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.147246996968981</v>
+        <v>6.614053612180257</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>7.044993280870656</v>
+        <v>7.691015195973975</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>6.976380762193735</v>
+        <v>7.595268807800778</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>6.900534800784634</v>
+        <v>7.520106285845493</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>7.648943162555781</v>
+        <v>8.235438884331423</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>7.099177260043412</v>
+        <v>7.601601776834407</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.06138</t>
+          <t>X &lt; -0.06135</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>8.79109481034299</v>
+        <v>9.024218191675494</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.367388792392447</v>
+        <v>7.887045758823675</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>8.833180995630066</v>
+        <v>9.306148448375957</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8.301715179454106</v>
+        <v>8.357240010708544</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>9.236342129774343</v>
+        <v>9.15120058718675</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.971402689737431</v>
+        <v>8.060362357177709</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.925406818914219</v>
+        <v>8.156545942092933</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.013801544760057</v>
+        <v>6.069094304388422</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.873800523407972</v>
+        <v>5.84051697521334</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>6.189814066972218</v>
+        <v>6.113984196571543</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>5.737920896066981</v>
+        <v>5.673206733457526</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5.459171492618985</v>
+        <v>5.218371659556631</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.606426848630385</v>
+        <v>5.286952931461599</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.022371565650218</v>
+        <v>4.795299498702143</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.819763658269295</v>
+        <v>3.689641805091725</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>4.414150580212286</v>
+        <v>4.364521494908722</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.006186256301973</v>
+        <v>5.094049760191844</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>6.534739381881877</v>
+        <v>6.698478507451014</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>5.66170154320546</v>
+        <v>5.948944247134591</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>5.848547353173487</v>
+        <v>6.28103873823062</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>6.031953998274624</v>
+        <v>6.556165717836336</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.956108036865523</v>
+        <v>6.481003195881051</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.230582749347576</v>
+        <v>6.724637681159429</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>5.791774089590724</v>
+        <v>6.200179846290247</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.04933</t>
+          <t>X &lt; -0.0493</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.203124517773709</v>
+        <v>8.540706605222738</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7.159127861267862</v>
+        <v>7.73924421396331</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.565080443442547</v>
+        <v>8.151216778738394</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.993970395631017</v>
+        <v>7.419925691041286</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7.225555809608565</v>
+        <v>7.561034217608615</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>6.277770222656294</v>
+        <v>6.606856712495592</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.356885368553179</v>
+        <v>6.783996922485088</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.653142008906485</v>
+        <v>5.923520923520918</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.262005077346018</v>
+        <v>6.468116499871691</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.340153231096764</v>
+        <v>6.505398337985682</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.763149043471451</v>
+        <v>5.944300019256687</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.20071169676104</v>
+        <v>5.338364023678913</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.921521261110591</v>
+        <v>5.982336934645055</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.27491046977039</v>
+        <v>5.405823871024701</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.907547314033799</v>
+        <v>4.115143897560834</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.785622179239212</v>
+        <v>5.045241134335726</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.793549013892942</v>
+        <v>5.171130952380956</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>5.965304054752593</v>
+        <v>6.250428774688785</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>5.188287634258494</v>
+        <v>5.573736361684553</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>5.800665359120131</v>
+        <v>6.160484187296319</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>5.825495077678916</v>
+        <v>6.247939549230495</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.891493087901019</v>
+        <v>6.313622097697753</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>6.165967800383072</v>
+        <v>6.650027595511126</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.948291575528593</v>
+        <v>6.439678740910743</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.03727</t>
+          <t>X &lt; -0.03725</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8.022219841211665</v>
+        <v>8.321780051550419</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>6.391546714568115</v>
+        <v>6.910618978558411</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>6.357415354521997</v>
+        <v>6.927111317344796</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6.076426777843835</v>
+        <v>6.546573525316234</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6.604567190825726</v>
+        <v>7.012540808945715</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>5.927602491393941</v>
+        <v>6.322016787825156</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.587619250268176</v>
+        <v>6.056595792541593</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>5.417399166206238</v>
+        <v>5.751675349132974</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.674869069503231</v>
+        <v>5.985536462206909</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.333918836231327</v>
+        <v>5.613213780546893</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>5.391995757010953</v>
+        <v>5.740311566328678</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.681280910798378</v>
+        <v>4.999812898472577</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.825937418456313</v>
+        <v>6.076766200020892</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.95691037786284</v>
+        <v>5.25908361166983</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4.406758440973427</v>
+        <v>4.751741728368593</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>5.109136723607563</v>
+        <v>5.488230980310647</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.651245504556655</v>
+        <v>5.026291800071142</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.978370243500052</v>
+        <v>5.282447091419598</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.546313460277524</v>
+        <v>4.924214039987731</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>4.517176548863254</v>
+        <v>4.88607802171839</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.514587184352941</v>
+        <v>5.029999540474847</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.654723944326129</v>
+        <v>5.131248888485381</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.713215935425893</v>
+        <v>5.229440059776785</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.205418239438039</v>
+        <v>4.706491206739067</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02522</t>
+          <t>X &lt; -0.02521</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>7.549429500147241</v>
+        <v>7.806057482415717</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.789673657371615</v>
+        <v>6.129161909436561</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.357522169111789</v>
+        <v>5.77981760178367</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4.728390446399978</v>
+        <v>5.105110876226469</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.644066864045492</v>
+        <v>4.994161789625075</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.40605400571706</v>
+        <v>3.751918440890655</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.807617476059733</v>
+        <v>4.241437888987022</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.032339811692246</v>
+        <v>4.348379060075921</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.822360103414148</v>
+        <v>4.197002640752892</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.720022801225099</v>
+        <v>4.111283926544544</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.329371630310753</v>
+        <v>4.764719323780042</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.631510743208096</v>
+        <v>4.043521554225237</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.268616907701521</v>
+        <v>4.633815746066354</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.628426547600284</v>
+        <v>4.02405472622528</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3.389394733674372</v>
+        <v>3.808274749712858</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>3.397025578500852</v>
+        <v>3.841701721841098</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.430753034985244</v>
+        <v>3.872968533886578</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>3.57737922135685</v>
+        <v>3.958512627950242</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.955047634971876</v>
+        <v>3.394259959058154</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.225715741670832</v>
+        <v>3.660782564824629</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.437570244283172</v>
+        <v>3.978000179456473</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.613191173066859</v>
+        <v>4.122307543707137</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.636198995356125</v>
+        <v>4.168763824926572</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.973610665016338</v>
+        <v>3.475227631245858</v>
       </c>
     </row>
     <row r="17">
@@ -6730,899 +6730,899 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1497</v>
+        <v>1506</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>5.665357022658753</v>
+        <v>5.867209337463173</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>4.396624253661848</v>
+        <v>4.741650163219653</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.42625030136201</v>
+        <v>4.799292019333329</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.846718563440277</v>
+        <v>4.206889820525106</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.977906076216563</v>
+        <v>4.325032467827342</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.630516024822278</v>
+        <v>3.038396520019646</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.925945593100032</v>
+        <v>3.39813568370198</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.248134415191529</v>
+        <v>3.658226719987553</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.089488174824709</v>
+        <v>3.562955421633696</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.450661891716834</v>
+        <v>3.92498898126054</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.991566096920792</v>
+        <v>4.501007648544963</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.445972130430761</v>
+        <v>3.935724213226322</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.590321738024286</v>
+        <v>4.047900289969945</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.835553735493633</v>
+        <v>3.31331366837</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.81976123519582</v>
+        <v>3.266276887954845</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.988552863302367</v>
+        <v>3.406734330703429</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.255437329531304</v>
+        <v>3.674577274730119</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>3.217396892911182</v>
+        <v>3.583220392192892</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.965686403428037</v>
+        <v>3.37599545046421</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.484529541385371</v>
+        <v>2.903435538345583</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.943987381435377</v>
+        <v>3.437198362547775</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.335743290433761</v>
+        <v>3.801573679869819</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.409817201312606</v>
+        <v>3.888116326707262</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>3.400785215290391</v>
+        <v>3.834281122345452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.001107</t>
+          <t>X &lt; -0.001108</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1788</v>
+        <v>1801</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5.185968529026127</v>
+        <v>5.238931998563388</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>4.57186212173778</v>
+        <v>4.805645458700631</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.362893352036387</v>
+        <v>4.627102004623623</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.70580525438136</v>
+        <v>4.0346998058154</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.096271765074313</v>
+        <v>4.418482325056722</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.05418767184208</v>
+        <v>3.454101841076614</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.120227814767368</v>
+        <v>3.571675690361886</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.009614135377426</v>
+        <v>3.464950630608307</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.106967239079829</v>
+        <v>3.681161042211393</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.507235920585245</v>
+        <v>4.130513122191388</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.334368188445488</v>
+        <v>3.995721065440691</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.999752863209793</v>
+        <v>3.642606218244971</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.105641075683273</v>
+        <v>3.720412407967437</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.381768903147297</v>
+        <v>3.009650478453203</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2.820209009422086</v>
+        <v>3.411418473936642</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>3.226052471018917</v>
+        <v>3.786422562084326</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.595491038739425</v>
+        <v>4.104443215339231</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>3.434721923285139</v>
+        <v>3.895864050160291</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.147257599511477</v>
+        <v>3.702321477465901</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.942604528047731</v>
+        <v>3.453049377754141</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>2.847485653146585</v>
+        <v>3.419014781109574</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.883496515003706</v>
+        <v>3.434148919192438</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.598687111154653</v>
+        <v>3.213241326062835</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.522854857931378</v>
+        <v>3.085766758553163</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.01095</t>
+          <t>X &lt; 0.01094</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2076</v>
+        <v>2087</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.112393405050994</v>
+        <v>4.115030929547061</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.489570519327195</v>
+        <v>3.659284272997674</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.771666688731152</v>
+        <v>2.906463838802736</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.106720350517413</v>
+        <v>2.408983329600588</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.875106546237063</v>
+        <v>3.158137731378801</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.005903745296507</v>
+        <v>2.250496195208704</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.482154773360072</v>
+        <v>2.813781459874193</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.42465875834953</v>
+        <v>2.727293312172051</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.466145940264234</v>
+        <v>2.883567393200792</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.845968016389122</v>
+        <v>3.353394001426381</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.668755663311195</v>
+        <v>3.178427003383675</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.293898619305779</v>
+        <v>2.835350799950291</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.08375913774519</v>
+        <v>2.702518776484077</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.430195878790187</v>
+        <v>2.149727794342134</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.76283918528312</v>
+        <v>2.546313670259039</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.098364598364604</v>
+        <v>2.850872257389291</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.523431129129214</v>
+        <v>3.158578080229226</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.255916879441791</v>
+        <v>2.768777186445341</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.779112871006738</v>
+        <v>2.439270123258865</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.676941339934302</v>
+        <v>2.205014997459223</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>1.664260297209118</v>
+        <v>2.288777880654443</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.684753449480169</v>
+        <v>2.147399294145949</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.67021082092176</v>
+        <v>2.228968848908885</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.690717681378636</v>
+        <v>2.19210362565596</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.023</t>
+          <t>X &lt; 0.02299</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.24976442834236</v>
+        <v>3.203743895288206</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.828854985720369</v>
+        <v>2.939360498552048</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.295228701547266</v>
+        <v>2.435404812926429</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.496142037832342</v>
+        <v>1.714797485913074</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.892479041598591</v>
+        <v>2.105058254471473</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.390384073518533</v>
+        <v>1.559689142872934</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.652027120894331</v>
+        <v>1.901669151838966</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.614530625331909</v>
+        <v>1.8786198580719</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.681423027945172</v>
+        <v>2.031702034013968</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.796375190305149</v>
+        <v>2.160568289428134</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.664849580128745</v>
+        <v>2.072615969154292</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.368598148121166</v>
+        <v>1.821472591181433</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9791434614981114</v>
+        <v>1.504241648750316</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4127905237653735</v>
+        <v>1.024310531585826</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.600855659309957</v>
+        <v>1.269555962105287</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.6166961188559483</v>
+        <v>1.255620102446649</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.9841127731872703</v>
+        <v>1.521428699326748</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.6892970269449279</v>
+        <v>1.113667557205837</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.2392704804633041</v>
+        <v>0.7949517778981487</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.3654204158791998</v>
+        <v>0.8201354505772898</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.4114764721709534</v>
+        <v>0.9671285532503049</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.4655006406319941</v>
+        <v>0.874891523035302</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.436945050083736</v>
+        <v>0.9721821553678183</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.5342729700206306</v>
+        <v>1.00840073584547</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.03506</t>
+          <t>X &lt; 0.03504</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2537</v>
+        <v>2546</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.538046570365601</v>
+        <v>2.510312158615754</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.085576558991072</v>
+        <v>2.208351171388024</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.471410001133087</v>
+        <v>1.598766880456786</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4838384846326704</v>
+        <v>0.677698272664216</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.5011276511595497</v>
+        <v>0.7359854846651501</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.01806544089136253</v>
+        <v>0.1349811708072579</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2692247924407312</v>
+        <v>0.4931918763152439</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1704939578693754</v>
+        <v>0.4056963073356457</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3523408081599015</v>
+        <v>0.6731253939668775</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3483318230195565</v>
+        <v>0.6807455602079102</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.2917059412964136</v>
+        <v>0.6631029370631154</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.1214480784296512</v>
+        <v>0.2918819080657329</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4584466232731899</v>
+        <v>0.02087661434892141</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7581418519210317</v>
+        <v>-0.2044065491532621</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.4887791334803069</v>
+        <v>0.1148815135837538</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.3823641608850181</v>
+        <v>0.1905500149617509</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.0994818752694826</v>
+        <v>0.3840457305131153</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1808957553775201</v>
+        <v>0.1961062292166673</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.5323428702959987</v>
+        <v>-0.03653323957338728</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.4798704958838087</v>
+        <v>-0.07332072707449555</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4079799878057955</v>
+        <v>0.08844038081868888</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4444093153954327</v>
+        <v>-0.04187351333106903</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6035175749275652</v>
+        <v>-0.08900496748091768</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.364016757595067</v>
+        <v>0.08629845234464284</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.04712</t>
+          <t>X &lt; 0.04709</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2708</v>
+        <v>2719</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.053495281865615</v>
+        <v>2.037241980860962</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.64524309777002</v>
+        <v>1.77512933293854</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.015453291942556</v>
+        <v>1.161151896337742</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1750907348477213</v>
+        <v>0.04162460792093015</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1503972643169789</v>
+        <v>0.4072926381913646</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1034888640602958</v>
+        <v>0.07329401205308983</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.006267080998661356</v>
+        <v>0.2489092031868481</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1774740818611491</v>
+        <v>0.07444515671206631</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.06884696303645654</v>
+        <v>0.4060787854930794</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3100368188780394</v>
+        <v>0.6554471244230626</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1640696202409657</v>
+        <v>0.5463416655882298</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2405734085778164</v>
+        <v>0.1810729612417177</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3483374171709812</v>
+        <v>0.1129602574689343</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5109129697500094</v>
+        <v>-0.003813716476244622</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.2630522040939027</v>
+        <v>0.2886968718887246</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.2363759228853226</v>
+        <v>0.2852266713509692</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.02027969863529222</v>
+        <v>0.4598847517730462</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.04809258898796287</v>
+        <v>0.38556008444084</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.2674711786487904</v>
+        <v>0.1813853907066374</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.2802469662256399</v>
+        <v>0.08720003650086028</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.3578649692531997</v>
+        <v>0.09246149353408128</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.2860004432176879</v>
+        <v>0.0759091607596929</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.4546571930694583</v>
+        <v>0.01054987212276615</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.345851336986982</v>
+        <v>0.05408500110526404</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.05917</t>
+          <t>X &lt; 0.05914</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2842</v>
+        <v>2855</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.821337760517615</v>
+        <v>1.808311423383493</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.276476928554359</v>
+        <v>1.373093130658944</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.6787940139771464</v>
+        <v>0.7982187877014582</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2092300334767998</v>
+        <v>-0.01823856016644498</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1552596060207421</v>
+        <v>0.3866547232917483</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2880263087222161</v>
+        <v>-0.09814580133045325</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.2546528637610237</v>
+        <v>-0.0381943495669006</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.197735510935523</v>
+        <v>0.02487933522415631</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.03896114746285662</v>
+        <v>0.3468427871345625</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1624082668560547</v>
+        <v>0.4769234532019837</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2465027681190719</v>
+        <v>0.5950438593310778</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.0118925655234392</v>
+        <v>0.3735177779970371</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1673178579636883</v>
+        <v>0.2557995070771923</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2974814856002936</v>
+        <v>0.1677390644937233</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.1975108579320874</v>
+        <v>0.3092779757731279</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.1792157614075407</v>
+        <v>0.3326432188038311</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.08147777498083286</v>
+        <v>0.3543195317959444</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.09509804423903745</v>
+        <v>0.2422214814631261</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.2450247516528776</v>
+        <v>0.1977640194200703</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.1076873698670795</v>
+        <v>0.258181443573406</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.1719794807431256</v>
+        <v>0.2712396014683449</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.212638953763765</v>
+        <v>0.1819563594812621</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.4307750787201314</v>
+        <v>0.02630617464377849</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3658613783895746</v>
+        <v>0.06004938612629473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.07123</t>
+          <t>X &lt; 0.07118</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2962</v>
+        <v>2974</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.011487451566353</v>
+        <v>1.045294526477328</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.6767106532165386</v>
+        <v>0.7842301210987515</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2128266394559546</v>
+        <v>0.3490928685176584</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2985822002756606</v>
+        <v>-0.09120768682555536</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.09691886025995444</v>
+        <v>0.1195503849620678</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.5817699398663052</v>
+        <v>-0.3732383558347721</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4803561783418075</v>
+        <v>-0.2136627231183823</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5379469867466824</v>
+        <v>-0.2656280917150582</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.3429177428458914</v>
+        <v>0.01505713404885967</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2896931443462094</v>
+        <v>0.0746754464194197</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2989273747893648</v>
+        <v>0.09836578572620169</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.6256296642156443</v>
+        <v>-0.1924999898399022</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.7870158744623552</v>
+        <v>-0.3166603731567292</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8874220755408899</v>
+        <v>-0.4113002797225604</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.6838211769212066</v>
+        <v>-0.1687216571561123</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8106673201012882</v>
+        <v>-0.2917223716418533</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.6888854245038942</v>
+        <v>-0.2417218774460537</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.6390010006507154</v>
+        <v>-0.287735894870778</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.6730018781379101</v>
+        <v>-0.2213234389423206</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.5675259866748021</v>
+        <v>-0.1884657777072363</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.5840045908092648</v>
+        <v>-0.1315804326020498</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.4911026615669982</v>
+        <v>-0.08602578962619845</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.5878733085179491</v>
+        <v>-0.1249543295579016</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.4749608751348902</v>
+        <v>-0.06547515405086557</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.08328</t>
+          <t>X &lt; 0.08323</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3031</v>
+        <v>3047</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7226699469354827</v>
+        <v>0.6919009591858227</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4535099464859371</v>
+        <v>0.5288336567785592</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.0002571340411208212</v>
+        <v>0.1067071452457142</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2683757790740202</v>
+        <v>-0.1090566659488985</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.2903585624547844</v>
+        <v>-0.1055780894146423</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.6943313126673232</v>
+        <v>-0.4850863725143739</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6455314739050095</v>
+        <v>-0.4462032515793126</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.6424943674342174</v>
+        <v>-0.4389777161569555</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5823859348533134</v>
+        <v>-0.2926244827830757</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6136973689316747</v>
+        <v>-0.3188511810531125</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6494854215361769</v>
+        <v>-0.3220398500243604</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9423310220161554</v>
+        <v>-0.5800117670405527</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9940722439285992</v>
+        <v>-0.5971449850104094</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.163097553585565</v>
+        <v>-0.7282562222655358</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.9133268146155942</v>
+        <v>-0.4424257885955356</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.9250805719360145</v>
+        <v>-0.450964787402107</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.8750238563450594</v>
+        <v>-0.4701825474787142</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.8287184019289029</v>
+        <v>-0.4855938715116466</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.8241389074882335</v>
+        <v>-0.3829396805496827</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.7168617013704974</v>
+        <v>-0.345786842330817</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.6793983522131057</v>
+        <v>-0.2383222840643526</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.5903366619071662</v>
+        <v>-0.1956928935947104</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.777603374227219</v>
+        <v>-0.3263151888622602</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.669050265635164</v>
+        <v>-0.2722116245316073</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.09534</t>
+          <t>X &lt; 0.09528</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3108</v>
+        <v>3127</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4071528865680278</v>
+        <v>0.4256272401433705</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2643760882182207</v>
+        <v>0.355639189440538</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1816429608127663</v>
+        <v>-0.05593414601100477</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4287736767984072</v>
+        <v>-0.2813241765574901</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3304630211665369</v>
+        <v>-0.1578504330942181</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5917837386874822</v>
+        <v>-0.428340249171967</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.5952405878035663</v>
+        <v>-0.4424661818406079</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5030317476870749</v>
+        <v>-0.3477344234582631</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.475379058035216</v>
+        <v>-0.2336481228031744</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4929073253680585</v>
+        <v>-0.2476261765001482</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6492535496491882</v>
+        <v>-0.3711635334680139</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.8776072838548288</v>
+        <v>-0.5659108333067167</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8916310470962827</v>
+        <v>-0.5472908999141666</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.094002211517683</v>
+        <v>-0.7132507096427148</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.7703439237426863</v>
+        <v>-0.3564457159381931</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.9276288900566385</v>
+        <v>-0.5099054734424655</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.9142469367419039</v>
+        <v>-0.5632112848330166</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.871693885045751</v>
+        <v>-0.5497336370266908</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.8297540435218025</v>
+        <v>-0.4123155561767575</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.7526629572238477</v>
+        <v>-0.4025771821317647</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.7295761066429591</v>
+        <v>-0.3123808395558925</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.7089280185184492</v>
+        <v>-0.3367049203388817</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.7882648209929783</v>
+        <v>-0.3299232736572861</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.7808083450606773</v>
+        <v>-0.3772917313203621</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.1074</t>
+          <t>X &lt; 0.1073</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3154</v>
+        <v>3174</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4089480331170421</v>
+        <v>0.4454871286300985</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1542625951539094</v>
+        <v>0.2477618053970474</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1944691985926497</v>
+        <v>-0.08235129637897387</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3537263177949441</v>
+        <v>-0.1879153998931073</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3563603149043928</v>
+        <v>-0.1955600685033616</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.4849510868379383</v>
+        <v>-0.3657832206706573</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.531118767257162</v>
+        <v>-0.4227303312493689</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.570530890298329</v>
+        <v>-0.4592725282380528</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5426985708701864</v>
+        <v>-0.3450171888499511</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5396378111383342</v>
+        <v>-0.3391924887255868</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.7213388729011143</v>
+        <v>-0.4882994298943828</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.887236945320538</v>
+        <v>-0.6215160846182428</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9173941235565337</v>
+        <v>-0.6196404751317957</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9935433771081037</v>
+        <v>-0.6612093424625343</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.6841408356450174</v>
+        <v>-0.3197292150117192</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.8304564633678524</v>
+        <v>-0.4626199549207044</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.850844242793471</v>
+        <v>-0.5480948077124594</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.8420836895329913</v>
+        <v>-0.5367756145955624</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.7975998565589464</v>
+        <v>-0.3982143966275444</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.8139558959023887</v>
+        <v>-0.4798410444525416</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.7991354198989313</v>
+        <v>-0.3993980489110811</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.7798942180750714</v>
+        <v>-0.4245018601551678</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.8540724374472148</v>
+        <v>-0.4142416980486132</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.8795573341077088</v>
+        <v>-0.4948422079000494</v>
       </c>
     </row>
     <row r="28">
@@ -7632,653 +7632,653 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3204</v>
+        <v>3228</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3269148208519752</v>
+        <v>0.3484836994501563</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.03987996418721451</v>
+        <v>0.1499279746470705</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2027248466688505</v>
+        <v>-0.07246743178792059</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3090357019433796</v>
+        <v>-0.1245461206719085</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2860994329393449</v>
+        <v>-0.1058292118818542</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4852939770438098</v>
+        <v>-0.3321964811786842</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.4945749195398577</v>
+        <v>-0.37059989312867</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5377590902851495</v>
+        <v>-0.4115934757118467</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3853993719176572</v>
+        <v>-0.2045888141379706</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4878460722496101</v>
+        <v>-0.3046126291813493</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.6623034811395385</v>
+        <v>-0.4466887016456411</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.8299733677084831</v>
+        <v>-0.5822819352146098</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8152288613589178</v>
+        <v>-0.5372653016791347</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8002761060419772</v>
+        <v>-0.4896054924527533</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.6307090473062047</v>
+        <v>-0.2887199462976184</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.6718146900333082</v>
+        <v>-0.3271429710520835</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.6939567858021647</v>
+        <v>-0.412883178773825</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.5934657173201856</v>
+        <v>-0.3420871045431753</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.639695599147359</v>
+        <v>-0.2949909830782147</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.7463163099681012</v>
+        <v>-0.4644583702505756</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.7091496266210768</v>
+        <v>-0.3638886468104943</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.6417384541266031</v>
+        <v>-0.3588586069636648</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.6792762221437769</v>
+        <v>-0.3137059528458082</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.6742812722414726</v>
+        <v>-0.3646604101614415</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.1315</t>
+          <t>X &lt; 0.1314</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3244</v>
+        <v>3268</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2618158801401123</v>
+        <v>0.3011897410477147</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.09663573304369066</v>
+        <v>0.2236244908967748</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1303351507055766</v>
+        <v>0.01910130966640367</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.2442440390790424</v>
+        <v>-0.03952280855319401</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3483819364068239</v>
+        <v>-0.1460526228064865</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5120858896361256</v>
+        <v>-0.3373341308127138</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.5002985001204436</v>
+        <v>-0.3545114488999843</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5464402910543527</v>
+        <v>-0.3987148323323737</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5182151094144984</v>
+        <v>-0.3145094858459814</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5984463535590194</v>
+        <v>-0.3925805366842283</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5830730597127456</v>
+        <v>-0.3467613102837603</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.6906922797493138</v>
+        <v>-0.4230678430736887</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.7516819941105055</v>
+        <v>-0.4531464019588682</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7396836794927211</v>
+        <v>-0.4090715945404924</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.5190485396571702</v>
+        <v>-0.1579086798237839</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.5828581013082896</v>
+        <v>-0.2194941303995321</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.6063824856347608</v>
+        <v>-0.3054230279898249</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.5699932720340826</v>
+        <v>-0.2981699430764877</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.6436868521628583</v>
+        <v>-0.279567997783623</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7158161417707518</v>
+        <v>-0.4137732895175574</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.6243648038920639</v>
+        <v>-0.2602136192453557</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.5279298352384174</v>
+        <v>-0.2255517835099923</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.5433176250941969</v>
+        <v>-0.1779296952930665</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.5701035412609343</v>
+        <v>-0.2608032484536906</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.1436</t>
+          <t>X &lt; 0.1435</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3264</v>
+        <v>3289</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.2076469541068207</v>
+        <v>0.2315278612613838</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1022823572383018</v>
+        <v>0.213278577532563</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1625014083013525</v>
+        <v>-0.0281219255247791</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2496176867110549</v>
+        <v>-0.05992723532115463</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3856283909690958</v>
+        <v>-0.1977659973584664</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4862683111904786</v>
+        <v>-0.326374144608863</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.4792504748261734</v>
+        <v>-0.3484894658996609</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.465825297787859</v>
+        <v>-0.3338332536517186</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4374946403935738</v>
+        <v>-0.2493303658802617</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4609147094828288</v>
+        <v>-0.2713954858108636</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4439206470645658</v>
+        <v>-0.2240996038673444</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.522017111074156</v>
+        <v>-0.2713492212222164</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.5589075191395239</v>
+        <v>-0.2779821334734649</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.5788178084760176</v>
+        <v>-0.2660271569060697</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.3635033844600031</v>
+        <v>-0.02076376274454361</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3926798547825499</v>
+        <v>-0.04800956401051337</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4168210770199039</v>
+        <v>-0.1340008090614973</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.4118187248687164</v>
+        <v>-0.1579378482066218</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5142826097487259</v>
+        <v>-0.1684029041239086</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.5847873870451252</v>
+        <v>-0.3003501358620042</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.4971771637554028</v>
+        <v>-0.1513553697365282</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.4017582486722233</v>
+        <v>-0.1173612499726033</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.415331820569854</v>
+        <v>-0.06845513413505699</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.4730163093274697</v>
+        <v>-0.1822058839215615</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.1556</t>
+          <t>X &lt; 0.1555</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3289</v>
+        <v>3314</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.2238871860849372</v>
+        <v>0.2482033587938091</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.08659294113274285</v>
+        <v>0.1982769877442792</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.12663389736867</v>
+        <v>0.009246097412386689</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.2184676360427602</v>
+        <v>-0.02675164015914078</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2955192544956589</v>
+        <v>-0.105607446557805</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3939577045644995</v>
+        <v>-0.2320455150620973</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3928024974802113</v>
+        <v>-0.2599338290409747</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.4723287478450544</v>
+        <v>-0.3377403377403496</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4439005088336501</v>
+        <v>-0.2529125045006566</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4729953572272123</v>
+        <v>-0.2807929013305497</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.4237739904946523</v>
+        <v>-0.2017524804928357</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5033839888360632</v>
+        <v>-0.250719163784126</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4878920206431232</v>
+        <v>-0.2055282715459157</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6002418974846861</v>
+        <v>-0.2857611024659192</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.3915550863033914</v>
+        <v>-0.04748090973283325</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.4463424049411344</v>
+        <v>-0.1004079185980871</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.4409927474511406</v>
+        <v>-0.1564381963264125</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.4064821246079191</v>
+        <v>-0.1510818963262608</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.5065282140278882</v>
+        <v>-0.1598506467212601</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.6054443125883893</v>
+        <v>-0.3193229254221919</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.522625877484252</v>
+        <v>-0.1757336324583747</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.4589016055569459</v>
+        <v>-0.1727266340170317</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.4399085927273561</v>
+        <v>-0.09220276739457489</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.5585472532343729</v>
+        <v>-0.2666757422100119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.1677</t>
+          <t>X &lt; 0.1676</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3309</v>
+        <v>3334</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1406654916100507</v>
+        <v>0.1660417258661653</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.06220256675320002</v>
+        <v>0.1745176876753973</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1583877055575229</v>
+        <v>-0.02087297122020715</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.2840016062693351</v>
+        <v>-0.09001269099012177</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3025316835720133</v>
+        <v>-0.1104125796210624</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3992565537507957</v>
+        <v>-0.235161319856573</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3726856451237239</v>
+        <v>-0.2377876194426918</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.483476132190944</v>
+        <v>-0.3467941676896942</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4549726731212544</v>
+        <v>-0.261711641198616</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.4584543673520542</v>
+        <v>-0.2643149236630506</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4078749914387387</v>
+        <v>-0.184115145235566</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.428456651660035</v>
+        <v>-0.174664215881414</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4198014766489635</v>
+        <v>-0.1363868080216335</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5327860294314988</v>
+        <v>-0.2176037547151779</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.359442541428983</v>
+        <v>-0.01472306367058707</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.3801582298718245</v>
+        <v>-0.03404223938211715</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.375628581945854</v>
+        <v>-0.09033909508131188</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.372104885910403</v>
+        <v>-0.1157309115488232</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4702339184065494</v>
+        <v>-0.123151961873269</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.5674139673243701</v>
+        <v>-0.2803720317185778</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.5487468793567416</v>
+        <v>-0.2009666539460113</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4858735665561724</v>
+        <v>-0.1984358615686475</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4653450062848634</v>
+        <v>-0.1169415292353833</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.5837326266794349</v>
+        <v>-0.2913479351099895</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.1797</t>
+          <t>X &lt; 0.1796</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3323</v>
+        <v>3348</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1846161262572181</v>
+        <v>0.2099689408303718</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1050935770074588</v>
+        <v>0.2174011542864207</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1205807598558408</v>
+        <v>0.01762125088641397</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2486430466629272</v>
+        <v>-0.05368212104634296</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2984137843407879</v>
+        <v>-0.104832198257796</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.364017495379457</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.3707232440089285</v>
+        <v>-0.2343289814277369</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4822151180202923</v>
+        <v>-0.3441498387990691</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4836148844946493</v>
+        <v>-0.2886235140048043</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4303991612716445</v>
+        <v>-0.2350504689414095</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.318921470330281</v>
+        <v>-0.09453597532164082</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4005302354643376</v>
+        <v>-0.1457739987066731</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3066373624838405</v>
+        <v>-0.02298199815180624</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4200420042004112</v>
+        <v>-0.1048614924321498</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.2801703262137849</v>
+        <v>0.06457333958393008</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.298276975701171</v>
+        <v>0.0476999389399495</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2943047973651289</v>
+        <v>-0.008771112767014699</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.2611733445899489</v>
+        <v>-0.004772149288022831</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3579480449559114</v>
+        <v>-0.01123366348157617</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.4538991645386545</v>
+        <v>-0.166867453641018</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4676263852842695</v>
+        <v>-0.1199724887989362</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.4053127564971959</v>
+        <v>-0.1177422075366437</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4137746273507332</v>
+        <v>-0.0654056369844298</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.5319674401860723</v>
+        <v>-0.2397453524007247</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.1918</t>
+          <t>X &lt; 0.1917</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3326</v>
+        <v>3351</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1961191451526858</v>
+        <v>0.2214515172954492</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1163713092456931</v>
+        <v>0.2286618112225938</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1402638153093392</v>
+        <v>-0.00170927899193174</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2389699629213808</v>
+        <v>-0.04381734597377829</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2889943287370116</v>
+        <v>-0.09516426574120374</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3543686351264554</v>
+        <v>-0.1888047102806993</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.3617582246011466</v>
+        <v>-0.2251083823446791</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4733970745828273</v>
+        <v>-0.3351003351003357</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4747556920333551</v>
+        <v>-0.2795067918692453</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4222793505484717</v>
+        <v>-0.2266885036851107</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3106531523700937</v>
+        <v>-0.08605405657895915</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.3924366190011455</v>
+        <v>-0.1374905782912279</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2996354664890433</v>
+        <v>-0.01580053161309536</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.4131348386637157</v>
+        <v>-0.0978263758592135</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.273978944113729</v>
+        <v>0.07085020242914908</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.291532602570399</v>
+        <v>0.05449505397964316</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2876825135151222</v>
+        <v>-0.002016329164185038</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2546732978905837</v>
+        <v>0.001862320218194213</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3511644502858005</v>
+        <v>-0.004399728631639732</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.4468587607444192</v>
+        <v>-0.1597004354406977</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.4610604231956117</v>
+        <v>-0.1133528323697846</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.3988693643630157</v>
+        <v>-0.111189821836156</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4070741708516294</v>
+        <v>-0.05868008716405626</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.5252267605554621</v>
+        <v>-0.2330068727942489</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.2038</t>
+          <t>X &lt; 0.2037</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.154925437922607</v>
+        <v>0.1966579304764551</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.07440586784895231</v>
+        <v>0.2031873114072908</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1559724216408966</v>
+        <v>-0.00034094580070132</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2565135475975922</v>
+        <v>-0.04391388818291375</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3073949043676194</v>
+        <v>-0.0958580253297967</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3123920478622324</v>
+        <v>-0.1296244400601623</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.2922253040106142</v>
+        <v>-0.1679327981742631</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3745074096686452</v>
+        <v>-0.2488066172900361</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4055504951410782</v>
+        <v>-0.2226242408690524</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3555173521571859</v>
+        <v>-0.1720534172669019</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.243386198338861</v>
+        <v>-0.03105162945694673</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3257378825368562</v>
+        <v>-0.08307276162820898</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2664272987302283</v>
+        <v>0.005667174797622465</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.380238262917743</v>
+        <v>-0.07679617872097566</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2135607227311382</v>
+        <v>0.1192961168590401</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2292663476873997</v>
+        <v>0.1044989786292092</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2258097393397094</v>
+        <v>0.04787582912582167</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.2231166896099239</v>
+        <v>0.02169477184374102</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.3186633996401369</v>
+        <v>0.01602896398516407</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.3835619309805125</v>
+        <v>-0.1085495629608104</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.3993269801419217</v>
+        <v>-0.06382936936583405</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.3674890180017769</v>
+        <v>-0.09160282710388401</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4048043502512186</v>
+        <v>-0.06832852541298706</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4628773616620734</v>
+        <v>-0.1831017272087152</v>
       </c>
     </row>
   </sheetData>
